--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19936" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19942" uniqueCount="205">
   <si>
     <t>pull_item</t>
   </si>
@@ -673,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3322"/>
+  <dimension ref="A1:J3323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17944,16 +17944,16 @@
         <v>198</v>
       </c>
       <c r="G540" s="1">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H540" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I540" s="1">
         <v>2</v>
       </c>
       <c r="J540" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -18395,7 +18395,7 @@
         <v>250</v>
       </c>
       <c r="H554" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I554" s="1">
         <v>2</v>
@@ -45528,10 +45528,10 @@
         <v>198</v>
       </c>
       <c r="G1402" s="1">
-        <v>255</v>
+        <v>64.5</v>
       </c>
       <c r="H1402" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1402" s="1">
         <v>2</v>
@@ -75160,7 +75160,7 @@
         <v>200</v>
       </c>
       <c r="G2328" s="1">
-        <v>2500</v>
+        <v>25000</v>
       </c>
       <c r="H2328" s="1">
         <v>3</v>
@@ -88344,10 +88344,10 @@
         <v>199</v>
       </c>
       <c r="G2740" s="1">
-        <v>906.52812967528394</v>
+        <v>838.96081566221938</v>
       </c>
       <c r="H2740" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2740" s="1">
         <v>2</v>
@@ -89819,7 +89819,7 @@
         <v>416.6651030805653</v>
       </c>
       <c r="H2786" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2786" s="1">
         <v>2</v>
@@ -89880,10 +89880,10 @@
         <v>198</v>
       </c>
       <c r="G2788" s="1">
-        <v>128.27749955223297</v>
+        <v>123.14639957014366</v>
       </c>
       <c r="H2788" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I2788" s="1">
         <v>2</v>
@@ -89912,10 +89912,10 @@
         <v>198</v>
       </c>
       <c r="G2789" s="1">
-        <v>184.71959935521548</v>
+        <v>192.41624932834947</v>
       </c>
       <c r="H2789" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2789" s="1">
         <v>2</v>
@@ -90232,10 +90232,10 @@
         <v>198</v>
       </c>
       <c r="G2799" s="1">
-        <v>709.71294445986223</v>
+        <v>655.87265212152784</v>
       </c>
       <c r="H2799" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2799" s="1">
         <v>2</v>
@@ -90264,16 +90264,16 @@
         <v>198</v>
       </c>
       <c r="G2800" s="1">
-        <v>230.04488544561053</v>
+        <v>119.91701475356294</v>
       </c>
       <c r="H2800" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2800" s="1">
         <v>2</v>
       </c>
       <c r="J2800" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2801">
@@ -90680,10 +90680,10 @@
         <v>197</v>
       </c>
       <c r="G2813" s="1">
-        <v>99.709665720906543</v>
+        <v>104.69514900695188</v>
       </c>
       <c r="H2813" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2813" s="1">
         <v>2</v>
@@ -90712,10 +90712,10 @@
         <v>198</v>
       </c>
       <c r="G2814" s="1">
-        <v>286.66528894760631</v>
+        <v>294.14351387667432</v>
       </c>
       <c r="H2814" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2814" s="1">
         <v>2</v>
@@ -90744,10 +90744,10 @@
         <v>199</v>
       </c>
       <c r="G2815" s="1">
-        <v>560.8668696800994</v>
+        <v>423.76607931385286</v>
       </c>
       <c r="H2815" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2815" s="1">
         <v>2</v>
@@ -91576,10 +91576,10 @@
         <v>198</v>
       </c>
       <c r="G2841" s="1">
-        <v>142.58921827904061</v>
+        <v>139.99668703760349</v>
       </c>
       <c r="H2841" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2841" s="1">
         <v>2</v>
@@ -96495,22 +96495,22 @@
         <v>116</v>
       </c>
       <c r="D2995" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E2995" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F2995" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G2995" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H2995" s="1">
         <v>1</v>
       </c>
       <c r="I2995" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2995" s="1">
         <v>1</v>
@@ -96530,7 +96530,7 @@
         <v>142</v>
       </c>
       <c r="E2996" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F2996" t="s">
         <v>197</v>
@@ -96539,7 +96539,7 @@
         <v>100</v>
       </c>
       <c r="H2996" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2996" s="1">
         <v>3</v>
@@ -96550,7 +96550,7 @@
     </row>
     <row r="2997">
       <c r="A2997" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2997" t="s">
         <v>25</v>
@@ -96559,22 +96559,22 @@
         <v>116</v>
       </c>
       <c r="D2997" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E2997" t="s">
         <v>195</v>
       </c>
       <c r="F2997" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2997" s="1">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="H2997" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2997" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2997" s="1">
         <v>1</v>
@@ -96582,7 +96582,7 @@
     </row>
     <row r="2998">
       <c r="A2998" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2998" t="s">
         <v>25</v>
@@ -96591,25 +96591,25 @@
         <v>116</v>
       </c>
       <c r="D2998" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E2998" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F2998" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G2998" s="1">
-        <v>220</v>
+        <v>375</v>
       </c>
       <c r="H2998" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2998" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2998" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2999">
@@ -96629,13 +96629,13 @@
         <v>194</v>
       </c>
       <c r="F2999" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2999" s="1">
-        <v>545</v>
+        <v>220</v>
       </c>
       <c r="H2999" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2999" s="1">
         <v>3</v>
@@ -96655,7 +96655,7 @@
         <v>116</v>
       </c>
       <c r="D3000" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3000" t="s">
         <v>194</v>
@@ -96664,16 +96664,16 @@
         <v>198</v>
       </c>
       <c r="G3000" s="1">
-        <v>400</v>
+        <v>545</v>
       </c>
       <c r="H3000" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3000" s="1">
         <v>3</v>
       </c>
       <c r="J3000" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3001">
@@ -96687,16 +96687,16 @@
         <v>116</v>
       </c>
       <c r="D3001" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3001" t="s">
         <v>194</v>
       </c>
       <c r="F3001" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3001" s="1">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="H3001" s="1">
         <v>2</v>
@@ -96710,7 +96710,7 @@
     </row>
     <row r="3002">
       <c r="A3002" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3002" t="s">
         <v>25</v>
@@ -96719,22 +96719,22 @@
         <v>116</v>
       </c>
       <c r="D3002" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E3002" t="s">
         <v>194</v>
       </c>
       <c r="F3002" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3002" s="1">
-        <v>62.5</v>
+        <v>220</v>
       </c>
       <c r="H3002" s="1">
         <v>2</v>
       </c>
       <c r="I3002" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3002" s="1">
         <v>1</v>
@@ -96751,7 +96751,7 @@
         <v>116</v>
       </c>
       <c r="D3003" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E3003" t="s">
         <v>194</v>
@@ -96760,16 +96760,16 @@
         <v>198</v>
       </c>
       <c r="G3003" s="1">
-        <v>150.43635697798297</v>
+        <v>62.5</v>
       </c>
       <c r="H3003" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3003" s="1">
         <v>2</v>
       </c>
       <c r="J3003" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3004">
@@ -96783,7 +96783,7 @@
         <v>116</v>
       </c>
       <c r="D3004" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E3004" t="s">
         <v>194</v>
@@ -96792,48 +96792,48 @@
         <v>198</v>
       </c>
       <c r="G3004" s="1">
-        <v>215</v>
+        <v>150.43635697798297</v>
       </c>
       <c r="H3004" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3004" s="1">
         <v>2</v>
       </c>
       <c r="J3004" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3005">
       <c r="A3005" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3005" t="s">
         <v>25</v>
       </c>
       <c r="C3005" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3005" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3005" t="s">
         <v>194</v>
       </c>
       <c r="F3005" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3005" s="1">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="H3005" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3005" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3005" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3006">
@@ -96853,13 +96853,13 @@
         <v>194</v>
       </c>
       <c r="F3006" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3006" s="1">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="H3006" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3006" s="1">
         <v>3</v>
@@ -96885,13 +96885,13 @@
         <v>194</v>
       </c>
       <c r="F3007" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3007" s="1">
-        <v>870</v>
+        <v>500</v>
       </c>
       <c r="H3007" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3007" s="1">
         <v>3</v>
@@ -96902,7 +96902,7 @@
     </row>
     <row r="3008">
       <c r="A3008" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3008" t="s">
         <v>25</v>
@@ -96911,30 +96911,30 @@
         <v>117</v>
       </c>
       <c r="D3008" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3008" t="s">
         <v>194</v>
       </c>
       <c r="F3008" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3008" s="1">
-        <v>112.5</v>
+        <v>870</v>
       </c>
       <c r="H3008" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3008" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3008" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3009">
       <c r="A3009" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3009" t="s">
         <v>25</v>
@@ -96943,22 +96943,22 @@
         <v>117</v>
       </c>
       <c r="D3009" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3009" t="s">
         <v>194</v>
       </c>
       <c r="F3009" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3009" s="1">
-        <v>230</v>
+        <v>112.5</v>
       </c>
       <c r="H3009" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3009" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3009" s="1">
         <v>1</v>
@@ -96981,10 +96981,10 @@
         <v>194</v>
       </c>
       <c r="F3010" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3010" s="1">
-        <v>305</v>
+        <v>230</v>
       </c>
       <c r="H3010" s="1">
         <v>1</v>
@@ -96998,7 +96998,7 @@
     </row>
     <row r="3011">
       <c r="A3011" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3011" t="s">
         <v>25</v>
@@ -97007,7 +97007,7 @@
         <v>117</v>
       </c>
       <c r="D3011" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3011" t="s">
         <v>194</v>
@@ -97016,21 +97016,21 @@
         <v>198</v>
       </c>
       <c r="G3011" s="1">
-        <v>140</v>
+        <v>305</v>
       </c>
       <c r="H3011" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3011" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3011" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3012">
       <c r="A3012" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3012" t="s">
         <v>25</v>
@@ -97039,19 +97039,19 @@
         <v>117</v>
       </c>
       <c r="D3012" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3012" t="s">
         <v>194</v>
       </c>
       <c r="F3012" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3012" s="1">
-        <v>855</v>
+        <v>140</v>
       </c>
       <c r="H3012" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3012" s="1">
         <v>2</v>
@@ -97077,10 +97077,10 @@
         <v>194</v>
       </c>
       <c r="F3013" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3013" s="1">
-        <v>1090</v>
+        <v>855</v>
       </c>
       <c r="H3013" s="1">
         <v>3</v>
@@ -97103,7 +97103,7 @@
         <v>117</v>
       </c>
       <c r="D3014" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E3014" t="s">
         <v>194</v>
@@ -97112,21 +97112,21 @@
         <v>198</v>
       </c>
       <c r="G3014" s="1">
-        <v>1055</v>
+        <v>1090</v>
       </c>
       <c r="H3014" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3014" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3014" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3015">
       <c r="A3015" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3015" t="s">
         <v>25</v>
@@ -97135,16 +97135,16 @@
         <v>117</v>
       </c>
       <c r="D3015" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E3015" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3015" t="s">
         <v>198</v>
       </c>
       <c r="G3015" s="1">
-        <v>990</v>
+        <v>1055</v>
       </c>
       <c r="H3015" s="1">
         <v>1</v>
@@ -97158,7 +97158,7 @@
     </row>
     <row r="3016">
       <c r="A3016" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3016" t="s">
         <v>25</v>
@@ -97167,16 +97167,16 @@
         <v>117</v>
       </c>
       <c r="D3016" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3016" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3016" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3016" s="1">
-        <v>375</v>
+        <v>990</v>
       </c>
       <c r="H3016" s="1">
         <v>1</v>
@@ -97205,13 +97205,13 @@
         <v>194</v>
       </c>
       <c r="F3017" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3017" s="1">
-        <v>607.5</v>
+        <v>375</v>
       </c>
       <c r="H3017" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3017" s="1">
         <v>3</v>
@@ -97222,7 +97222,7 @@
     </row>
     <row r="3018">
       <c r="A3018" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3018" t="s">
         <v>25</v>
@@ -97237,13 +97237,13 @@
         <v>194</v>
       </c>
       <c r="F3018" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3018" s="1">
-        <v>43</v>
+        <v>607.5</v>
       </c>
       <c r="H3018" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3018" s="1">
         <v>3</v>
@@ -97266,13 +97266,13 @@
         <v>130</v>
       </c>
       <c r="E3019" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3019" t="s">
         <v>197</v>
       </c>
       <c r="G3019" s="1">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="H3019" s="1">
         <v>1</v>
@@ -97295,7 +97295,7 @@
         <v>117</v>
       </c>
       <c r="D3020" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3020" t="s">
         <v>195</v>
@@ -97304,7 +97304,7 @@
         <v>197</v>
       </c>
       <c r="G3020" s="1">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="H3020" s="1">
         <v>1</v>
@@ -97327,7 +97327,7 @@
         <v>117</v>
       </c>
       <c r="D3021" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3021" t="s">
         <v>195</v>
@@ -97336,10 +97336,10 @@
         <v>197</v>
       </c>
       <c r="G3021" s="1">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="H3021" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3021" s="1">
         <v>3</v>
@@ -97359,7 +97359,7 @@
         <v>117</v>
       </c>
       <c r="D3022" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E3022" t="s">
         <v>195</v>
@@ -97368,10 +97368,10 @@
         <v>197</v>
       </c>
       <c r="G3022" s="1">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="H3022" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3022" s="1">
         <v>3</v>
@@ -97397,10 +97397,10 @@
         <v>195</v>
       </c>
       <c r="F3023" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3023" s="1">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="H3023" s="1">
         <v>1</v>
@@ -97414,7 +97414,7 @@
     </row>
     <row r="3024">
       <c r="A3024" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3024" t="s">
         <v>25</v>
@@ -97423,7 +97423,7 @@
         <v>117</v>
       </c>
       <c r="D3024" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="E3024" t="s">
         <v>195</v>
@@ -97432,13 +97432,13 @@
         <v>198</v>
       </c>
       <c r="G3024" s="1">
-        <v>375</v>
+        <v>700</v>
       </c>
       <c r="H3024" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3024" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3024" s="1">
         <v>1</v>
@@ -97446,7 +97446,7 @@
     </row>
     <row r="3025">
       <c r="A3025" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3025" t="s">
         <v>25</v>
@@ -97455,22 +97455,22 @@
         <v>117</v>
       </c>
       <c r="D3025" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3025" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3025" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3025" s="1">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="H3025" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3025" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3025" s="1">
         <v>1</v>
@@ -97487,19 +97487,19 @@
         <v>117</v>
       </c>
       <c r="D3026" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3026" t="s">
         <v>194</v>
       </c>
       <c r="F3026" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3026" s="1">
-        <v>575</v>
+        <v>415</v>
       </c>
       <c r="H3026" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3026" s="1">
         <v>3</v>
@@ -97519,16 +97519,16 @@
         <v>117</v>
       </c>
       <c r="D3027" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3027" t="s">
         <v>194</v>
       </c>
       <c r="F3027" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3027" s="1">
-        <v>385</v>
+        <v>575</v>
       </c>
       <c r="H3027" s="1">
         <v>2</v>
@@ -97542,7 +97542,7 @@
     </row>
     <row r="3028">
       <c r="A3028" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3028" t="s">
         <v>25</v>
@@ -97551,30 +97551,30 @@
         <v>117</v>
       </c>
       <c r="D3028" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E3028" t="s">
         <v>194</v>
       </c>
       <c r="F3028" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3028" s="1">
-        <v>215</v>
+        <v>385</v>
       </c>
       <c r="H3028" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3028" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3028" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3029">
       <c r="A3029" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3029" t="s">
         <v>25</v>
@@ -97583,7 +97583,7 @@
         <v>117</v>
       </c>
       <c r="D3029" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E3029" t="s">
         <v>194</v>
@@ -97592,21 +97592,21 @@
         <v>198</v>
       </c>
       <c r="G3029" s="1">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="H3029" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3029" s="1">
         <v>2</v>
       </c>
       <c r="J3029" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3030">
       <c r="A3030" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3030" t="s">
         <v>25</v>
@@ -97615,7 +97615,7 @@
         <v>117</v>
       </c>
       <c r="D3030" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3030" t="s">
         <v>194</v>
@@ -97624,16 +97624,16 @@
         <v>198</v>
       </c>
       <c r="G3030" s="1">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="H3030" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3030" s="1">
         <v>2</v>
       </c>
       <c r="J3030" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3031">
@@ -97647,7 +97647,7 @@
         <v>117</v>
       </c>
       <c r="D3031" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3031" t="s">
         <v>194</v>
@@ -97656,7 +97656,7 @@
         <v>198</v>
       </c>
       <c r="G3031" s="1">
-        <v>237.5</v>
+        <v>250</v>
       </c>
       <c r="H3031" s="1">
         <v>4</v>
@@ -97670,31 +97670,31 @@
     </row>
     <row r="3032">
       <c r="A3032" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3032" t="s">
         <v>25</v>
       </c>
       <c r="C3032" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3032" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E3032" t="s">
         <v>194</v>
       </c>
       <c r="F3032" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3032" s="1">
-        <v>265</v>
+        <v>237.5</v>
       </c>
       <c r="H3032" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3032" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3032" s="1">
         <v>0</v>
@@ -97702,7 +97702,7 @@
     </row>
     <row r="3033">
       <c r="A3033" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3033" t="s">
         <v>25</v>
@@ -97711,7 +97711,7 @@
         <v>118</v>
       </c>
       <c r="D3033" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E3033" t="s">
         <v>194</v>
@@ -97720,7 +97720,7 @@
         <v>197</v>
       </c>
       <c r="G3033" s="1">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="H3033" s="1">
         <v>3</v>
@@ -97743,7 +97743,7 @@
         <v>118</v>
       </c>
       <c r="D3034" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3034" t="s">
         <v>194</v>
@@ -97766,7 +97766,7 @@
     </row>
     <row r="3035">
       <c r="A3035" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3035" t="s">
         <v>25</v>
@@ -97775,22 +97775,22 @@
         <v>118</v>
       </c>
       <c r="D3035" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3035" t="s">
         <v>194</v>
       </c>
       <c r="F3035" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3035" s="1">
-        <v>100.42676715827429</v>
+        <v>290</v>
       </c>
       <c r="H3035" s="1">
         <v>3</v>
       </c>
       <c r="I3035" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3035" s="1">
         <v>0</v>
@@ -97798,7 +97798,7 @@
     </row>
     <row r="3036">
       <c r="A3036" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3036" t="s">
         <v>25</v>
@@ -97807,25 +97807,25 @@
         <v>118</v>
       </c>
       <c r="D3036" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3036" t="s">
         <v>194</v>
       </c>
       <c r="F3036" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3036" s="1">
-        <v>906.92425295826229</v>
+        <v>100.42676715827429</v>
       </c>
       <c r="H3036" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3036" s="1">
         <v>2</v>
       </c>
       <c r="J3036" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3037">
@@ -97845,13 +97845,13 @@
         <v>194</v>
       </c>
       <c r="F3037" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3037" s="1">
-        <v>1048.9426112511769</v>
+        <v>906.92425295826229</v>
       </c>
       <c r="H3037" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3037" s="1">
         <v>2</v>
@@ -97877,13 +97877,13 @@
         <v>194</v>
       </c>
       <c r="F3038" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3038" s="1">
-        <v>1131.1637660523381</v>
+        <v>1048.9426112511769</v>
       </c>
       <c r="H3038" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3038" s="1">
         <v>2</v>
@@ -97894,7 +97894,7 @@
     </row>
     <row r="3039">
       <c r="A3039" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3039" t="s">
         <v>25</v>
@@ -97903,22 +97903,22 @@
         <v>118</v>
       </c>
       <c r="D3039" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E3039" t="s">
         <v>194</v>
       </c>
       <c r="F3039" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3039" s="1">
-        <v>780</v>
+        <v>1131.1637660523381</v>
       </c>
       <c r="H3039" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3039" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3039" s="1">
         <v>1</v>
@@ -97926,7 +97926,7 @@
     </row>
     <row r="3040">
       <c r="A3040" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3040" t="s">
         <v>25</v>
@@ -97935,7 +97935,7 @@
         <v>118</v>
       </c>
       <c r="D3040" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3040" t="s">
         <v>194</v>
@@ -97944,7 +97944,7 @@
         <v>197</v>
       </c>
       <c r="G3040" s="1">
-        <v>71</v>
+        <v>780</v>
       </c>
       <c r="H3040" s="1">
         <v>2</v>
@@ -97970,16 +97970,16 @@
         <v>130</v>
       </c>
       <c r="E3041" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3041" t="s">
         <v>197</v>
       </c>
       <c r="G3041" s="1">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="H3041" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3041" s="1">
         <v>3</v>
@@ -97999,25 +97999,25 @@
         <v>118</v>
       </c>
       <c r="D3042" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3042" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3042" t="s">
         <v>197</v>
       </c>
       <c r="G3042" s="1">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="H3042" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3042" s="1">
         <v>3</v>
       </c>
       <c r="J3042" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3043">
@@ -98034,22 +98034,22 @@
         <v>134</v>
       </c>
       <c r="E3043" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3043" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3043" s="1">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H3043" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3043" s="1">
         <v>3</v>
       </c>
       <c r="J3043" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3044">
@@ -98063,19 +98063,19 @@
         <v>118</v>
       </c>
       <c r="D3044" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3044" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3044" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3044" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H3044" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3044" s="1">
         <v>3</v>
@@ -98098,7 +98098,7 @@
         <v>142</v>
       </c>
       <c r="E3045" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3045" t="s">
         <v>197</v>
@@ -98107,7 +98107,7 @@
         <v>100</v>
       </c>
       <c r="H3045" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3045" s="1">
         <v>3</v>
@@ -98118,7 +98118,7 @@
     </row>
     <row r="3046">
       <c r="A3046" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3046" t="s">
         <v>25</v>
@@ -98127,22 +98127,22 @@
         <v>118</v>
       </c>
       <c r="D3046" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3046" t="s">
         <v>195</v>
       </c>
       <c r="F3046" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3046" s="1">
-        <v>379.3140661960025</v>
+        <v>100</v>
       </c>
       <c r="H3046" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3046" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3046" s="1">
         <v>1</v>
@@ -98159,7 +98159,7 @@
         <v>118</v>
       </c>
       <c r="D3047" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3047" t="s">
         <v>195</v>
@@ -98168,7 +98168,7 @@
         <v>198</v>
       </c>
       <c r="G3047" s="1">
-        <v>758.628132392005</v>
+        <v>379.3140661960025</v>
       </c>
       <c r="H3047" s="1">
         <v>2</v>
@@ -98182,7 +98182,7 @@
     </row>
     <row r="3048">
       <c r="A3048" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3048" t="s">
         <v>25</v>
@@ -98191,25 +98191,25 @@
         <v>118</v>
       </c>
       <c r="D3048" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3048" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3048" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3048" s="1">
-        <v>640</v>
+        <v>758.628132392005</v>
       </c>
       <c r="H3048" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3048" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3048" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3049">
@@ -98223,16 +98223,16 @@
         <v>118</v>
       </c>
       <c r="D3049" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3049" t="s">
         <v>194</v>
       </c>
       <c r="F3049" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3049" s="1">
-        <v>450</v>
+        <v>640</v>
       </c>
       <c r="H3049" s="1">
         <v>6</v>
@@ -98255,19 +98255,19 @@
         <v>118</v>
       </c>
       <c r="D3050" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3050" t="s">
         <v>194</v>
       </c>
       <c r="F3050" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3050" s="1">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="H3050" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3050" s="1">
         <v>3</v>
@@ -98278,7 +98278,7 @@
     </row>
     <row r="3051">
       <c r="A3051" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3051" t="s">
         <v>25</v>
@@ -98287,25 +98287,25 @@
         <v>118</v>
       </c>
       <c r="D3051" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E3051" t="s">
         <v>194</v>
       </c>
       <c r="F3051" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3051" s="1">
-        <v>250.72726162997162</v>
+        <v>220</v>
       </c>
       <c r="H3051" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3051" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3051" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3052">
@@ -98319,7 +98319,7 @@
         <v>118</v>
       </c>
       <c r="D3052" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E3052" t="s">
         <v>194</v>
@@ -98331,42 +98331,42 @@
         <v>250.72726162997162</v>
       </c>
       <c r="H3052" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3052" s="1">
         <v>2</v>
       </c>
       <c r="J3052" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3053">
       <c r="A3053" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3053" t="s">
         <v>25</v>
       </c>
       <c r="C3053" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3053" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3053" t="s">
         <v>194</v>
       </c>
       <c r="F3053" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3053" s="1">
-        <v>355</v>
+        <v>250.72726162997162</v>
       </c>
       <c r="H3053" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3053" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3053" s="1">
         <v>0</v>
@@ -98389,13 +98389,13 @@
         <v>194</v>
       </c>
       <c r="F3054" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3054" s="1">
-        <v>620</v>
+        <v>355</v>
       </c>
       <c r="H3054" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3054" s="1">
         <v>3</v>
@@ -98421,24 +98421,24 @@
         <v>194</v>
       </c>
       <c r="F3055" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3055" s="1">
-        <v>775</v>
+        <v>620</v>
       </c>
       <c r="H3055" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3055" s="1">
         <v>3</v>
       </c>
       <c r="J3055" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3056">
       <c r="A3056" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3056" t="s">
         <v>25</v>
@@ -98447,25 +98447,25 @@
         <v>119</v>
       </c>
       <c r="D3056" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E3056" t="s">
         <v>194</v>
       </c>
       <c r="F3056" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3056" s="1">
-        <v>375</v>
+        <v>775</v>
       </c>
       <c r="H3056" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3056" s="1">
         <v>3</v>
       </c>
       <c r="J3056" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3057">
@@ -98479,22 +98479,22 @@
         <v>119</v>
       </c>
       <c r="D3057" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3057" t="s">
         <v>194</v>
       </c>
       <c r="F3057" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3057" s="1">
-        <v>270</v>
+        <v>375</v>
       </c>
       <c r="H3057" s="1">
         <v>3</v>
       </c>
       <c r="I3057" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3057" s="1">
         <v>0</v>
@@ -98502,7 +98502,7 @@
     </row>
     <row r="3058">
       <c r="A3058" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3058" t="s">
         <v>25</v>
@@ -98511,7 +98511,7 @@
         <v>119</v>
       </c>
       <c r="D3058" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3058" t="s">
         <v>194</v>
@@ -98520,7 +98520,7 @@
         <v>198</v>
       </c>
       <c r="G3058" s="1">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="H3058" s="1">
         <v>3</v>
@@ -98534,7 +98534,7 @@
     </row>
     <row r="3059">
       <c r="A3059" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3059" t="s">
         <v>25</v>
@@ -98543,16 +98543,16 @@
         <v>119</v>
       </c>
       <c r="D3059" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3059" t="s">
         <v>194</v>
       </c>
       <c r="F3059" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3059" s="1">
-        <v>1125</v>
+        <v>100</v>
       </c>
       <c r="H3059" s="1">
         <v>3</v>
@@ -98581,10 +98581,10 @@
         <v>194</v>
       </c>
       <c r="F3060" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3060" s="1">
-        <v>1325</v>
+        <v>1125</v>
       </c>
       <c r="H3060" s="1">
         <v>3</v>
@@ -98613,10 +98613,10 @@
         <v>194</v>
       </c>
       <c r="F3061" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3061" s="1">
-        <v>1580</v>
+        <v>1325</v>
       </c>
       <c r="H3061" s="1">
         <v>3</v>
@@ -98639,22 +98639,22 @@
         <v>119</v>
       </c>
       <c r="D3062" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E3062" t="s">
         <v>194</v>
       </c>
       <c r="F3062" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3062" s="1">
-        <v>1070</v>
+        <v>1580</v>
       </c>
       <c r="H3062" s="1">
         <v>3</v>
       </c>
       <c r="I3062" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3062" s="1">
         <v>0</v>
@@ -98677,19 +98677,19 @@
         <v>194</v>
       </c>
       <c r="F3063" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3063" s="1">
-        <v>1115</v>
+        <v>1070</v>
       </c>
       <c r="H3063" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3063" s="1">
         <v>3</v>
       </c>
       <c r="J3063" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3064">
@@ -98709,10 +98709,10 @@
         <v>194</v>
       </c>
       <c r="F3064" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3064" s="1">
-        <v>1245</v>
+        <v>1115</v>
       </c>
       <c r="H3064" s="1">
         <v>2</v>
@@ -98726,7 +98726,7 @@
     </row>
     <row r="3065">
       <c r="A3065" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3065" t="s">
         <v>25</v>
@@ -98735,25 +98735,25 @@
         <v>119</v>
       </c>
       <c r="D3065" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E3065" t="s">
         <v>194</v>
       </c>
       <c r="F3065" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3065" s="1">
-        <v>110</v>
+        <v>1245</v>
       </c>
       <c r="H3065" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3065" s="1">
         <v>3</v>
       </c>
       <c r="J3065" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3066">
@@ -98770,22 +98770,22 @@
         <v>130</v>
       </c>
       <c r="E3066" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3066" t="s">
         <v>197</v>
       </c>
       <c r="G3066" s="1">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="H3066" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3066" s="1">
         <v>3</v>
       </c>
       <c r="J3066" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3067">
@@ -98799,25 +98799,25 @@
         <v>119</v>
       </c>
       <c r="D3067" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3067" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3067" t="s">
         <v>197</v>
       </c>
       <c r="G3067" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H3067" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3067" s="1">
         <v>3</v>
       </c>
       <c r="J3067" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3068">
@@ -98834,22 +98834,22 @@
         <v>134</v>
       </c>
       <c r="E3068" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3068" t="s">
         <v>197</v>
       </c>
       <c r="G3068" s="1">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="H3068" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3068" s="1">
         <v>3</v>
       </c>
       <c r="J3068" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3069">
@@ -98863,30 +98863,30 @@
         <v>119</v>
       </c>
       <c r="D3069" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3069" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3069" t="s">
         <v>197</v>
       </c>
       <c r="G3069" s="1">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H3069" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3069" s="1">
         <v>3</v>
       </c>
       <c r="J3069" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3070">
       <c r="A3070" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3070" t="s">
         <v>25</v>
@@ -98895,30 +98895,30 @@
         <v>119</v>
       </c>
       <c r="D3070" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3070" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3070" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3070" s="1">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="H3070" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3070" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3070" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3071">
       <c r="A3071" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3071" t="s">
         <v>25</v>
@@ -98927,25 +98927,25 @@
         <v>119</v>
       </c>
       <c r="D3071" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3071" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3071" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3071" s="1">
-        <v>640</v>
+        <v>375</v>
       </c>
       <c r="H3071" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3071" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3071" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3072">
@@ -98959,16 +98959,16 @@
         <v>119</v>
       </c>
       <c r="D3072" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3072" t="s">
         <v>194</v>
       </c>
       <c r="F3072" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3072" s="1">
-        <v>450</v>
+        <v>640</v>
       </c>
       <c r="H3072" s="1">
         <v>3</v>
@@ -98991,16 +98991,16 @@
         <v>119</v>
       </c>
       <c r="D3073" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3073" t="s">
         <v>194</v>
       </c>
       <c r="F3073" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3073" s="1">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="H3073" s="1">
         <v>3</v>
@@ -99014,7 +99014,7 @@
     </row>
     <row r="3074">
       <c r="A3074" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3074" t="s">
         <v>25</v>
@@ -99023,22 +99023,22 @@
         <v>119</v>
       </c>
       <c r="D3074" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E3074" t="s">
         <v>194</v>
       </c>
       <c r="F3074" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3074" s="1">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="H3074" s="1">
         <v>3</v>
       </c>
       <c r="I3074" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3074" s="1">
         <v>0</v>
@@ -99055,7 +99055,7 @@
         <v>119</v>
       </c>
       <c r="D3075" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3075" t="s">
         <v>194</v>
@@ -99064,7 +99064,7 @@
         <v>198</v>
       </c>
       <c r="G3075" s="1">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="H3075" s="1">
         <v>3</v>
@@ -99078,31 +99078,31 @@
     </row>
     <row r="3076">
       <c r="A3076" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3076" t="s">
         <v>25</v>
       </c>
       <c r="C3076" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3076" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3076" t="s">
         <v>194</v>
       </c>
       <c r="F3076" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3076" s="1">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="H3076" s="1">
         <v>3</v>
       </c>
       <c r="I3076" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3076" s="1">
         <v>0</v>
@@ -99125,13 +99125,13 @@
         <v>194</v>
       </c>
       <c r="F3077" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3077" s="1">
-        <v>517.5</v>
+        <v>280</v>
       </c>
       <c r="H3077" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3077" s="1">
         <v>3</v>
@@ -99157,24 +99157,24 @@
         <v>194</v>
       </c>
       <c r="F3078" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3078" s="1">
-        <v>910</v>
+        <v>517.5</v>
       </c>
       <c r="H3078" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3078" s="1">
         <v>3</v>
       </c>
       <c r="J3078" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3079">
       <c r="A3079" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3079" t="s">
         <v>25</v>
@@ -99183,30 +99183,30 @@
         <v>120</v>
       </c>
       <c r="D3079" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3079" t="s">
         <v>194</v>
       </c>
       <c r="F3079" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3079" s="1">
-        <v>120</v>
+        <v>910</v>
       </c>
       <c r="H3079" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3079" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3079" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3080">
       <c r="A3080" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3080" t="s">
         <v>25</v>
@@ -99215,22 +99215,22 @@
         <v>120</v>
       </c>
       <c r="D3080" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3080" t="s">
         <v>194</v>
       </c>
       <c r="F3080" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3080" s="1">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="H3080" s="1">
         <v>3</v>
       </c>
       <c r="I3080" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3080" s="1">
         <v>0</v>
@@ -99253,13 +99253,13 @@
         <v>194</v>
       </c>
       <c r="F3081" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3081" s="1">
-        <v>377.5</v>
+        <v>175</v>
       </c>
       <c r="H3081" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3081" s="1">
         <v>3</v>
@@ -99285,24 +99285,24 @@
         <v>194</v>
       </c>
       <c r="F3082" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3082" s="1">
-        <v>727.5</v>
+        <v>377.5</v>
       </c>
       <c r="H3082" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3082" s="1">
         <v>3</v>
       </c>
       <c r="J3082" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3083">
       <c r="A3083" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3083" t="s">
         <v>25</v>
@@ -99311,30 +99311,30 @@
         <v>120</v>
       </c>
       <c r="D3083" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3083" t="s">
         <v>194</v>
       </c>
       <c r="F3083" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3083" s="1">
-        <v>135</v>
+        <v>727.5</v>
       </c>
       <c r="H3083" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3083" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3083" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3084">
       <c r="A3084" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3084" t="s">
         <v>25</v>
@@ -99343,16 +99343,16 @@
         <v>120</v>
       </c>
       <c r="D3084" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E3084" t="s">
         <v>194</v>
       </c>
       <c r="F3084" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3084" s="1">
-        <v>1035</v>
+        <v>135</v>
       </c>
       <c r="H3084" s="1">
         <v>3</v>
@@ -99381,10 +99381,10 @@
         <v>194</v>
       </c>
       <c r="F3085" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3085" s="1">
-        <v>1140</v>
+        <v>1035</v>
       </c>
       <c r="H3085" s="1">
         <v>3</v>
@@ -99413,10 +99413,10 @@
         <v>194</v>
       </c>
       <c r="F3086" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3086" s="1">
-        <v>1505</v>
+        <v>1140</v>
       </c>
       <c r="H3086" s="1">
         <v>3</v>
@@ -99430,7 +99430,7 @@
     </row>
     <row r="3087">
       <c r="A3087" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3087" t="s">
         <v>25</v>
@@ -99439,22 +99439,22 @@
         <v>120</v>
       </c>
       <c r="D3087" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E3087" t="s">
         <v>194</v>
       </c>
       <c r="F3087" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3087" s="1">
-        <v>205</v>
+        <v>1505</v>
       </c>
       <c r="H3087" s="1">
         <v>3</v>
       </c>
       <c r="I3087" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3087" s="1">
         <v>0</v>
@@ -99477,13 +99477,13 @@
         <v>194</v>
       </c>
       <c r="F3088" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3088" s="1">
-        <v>330</v>
+        <v>205</v>
       </c>
       <c r="H3088" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3088" s="1">
         <v>3</v>
@@ -99509,24 +99509,24 @@
         <v>194</v>
       </c>
       <c r="F3089" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3089" s="1">
-        <v>537.5</v>
+        <v>330</v>
       </c>
       <c r="H3089" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3089" s="1">
         <v>3</v>
       </c>
       <c r="J3089" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3090">
       <c r="A3090" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3090" t="s">
         <v>25</v>
@@ -99535,16 +99535,16 @@
         <v>120</v>
       </c>
       <c r="D3090" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3090" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3090" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3090" s="1">
-        <v>49</v>
+        <v>537.5</v>
       </c>
       <c r="H3090" s="1">
         <v>2</v>
@@ -99573,10 +99573,10 @@
         <v>195</v>
       </c>
       <c r="F3091" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3091" s="1">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H3091" s="1">
         <v>2</v>
@@ -99599,30 +99599,30 @@
         <v>120</v>
       </c>
       <c r="D3092" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3092" t="s">
         <v>195</v>
       </c>
       <c r="F3092" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3092" s="1">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H3092" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3092" s="1">
         <v>3</v>
       </c>
       <c r="J3092" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3093">
       <c r="A3093" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3093" t="s">
         <v>25</v>
@@ -99631,22 +99631,22 @@
         <v>120</v>
       </c>
       <c r="D3093" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3093" t="s">
         <v>195</v>
       </c>
       <c r="F3093" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3093" s="1">
-        <v>379.3140661960025</v>
+        <v>110</v>
       </c>
       <c r="H3093" s="1">
         <v>3</v>
       </c>
       <c r="I3093" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3093" s="1">
         <v>0</v>
@@ -99663,7 +99663,7 @@
         <v>120</v>
       </c>
       <c r="D3094" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3094" t="s">
         <v>195</v>
@@ -99672,10 +99672,10 @@
         <v>198</v>
       </c>
       <c r="G3094" s="1">
-        <v>758.628132392005</v>
+        <v>379.3140661960025</v>
       </c>
       <c r="H3094" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3094" s="1">
         <v>2</v>
@@ -99686,7 +99686,7 @@
     </row>
     <row r="3095">
       <c r="A3095" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3095" t="s">
         <v>25</v>
@@ -99695,22 +99695,22 @@
         <v>120</v>
       </c>
       <c r="D3095" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3095" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3095" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3095" s="1">
-        <v>650</v>
+        <v>758.628132392005</v>
       </c>
       <c r="H3095" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3095" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3095" s="1">
         <v>0</v>
@@ -99727,16 +99727,16 @@
         <v>120</v>
       </c>
       <c r="D3096" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3096" t="s">
         <v>194</v>
       </c>
       <c r="F3096" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3096" s="1">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="H3096" s="1">
         <v>3</v>
@@ -99759,30 +99759,30 @@
         <v>120</v>
       </c>
       <c r="D3097" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3097" t="s">
         <v>194</v>
       </c>
       <c r="F3097" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3097" s="1">
-        <v>290</v>
+        <v>450</v>
       </c>
       <c r="H3097" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3097" s="1">
         <v>3</v>
       </c>
       <c r="J3097" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3098">
       <c r="A3098" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3098" t="s">
         <v>25</v>
@@ -99791,30 +99791,30 @@
         <v>120</v>
       </c>
       <c r="D3098" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E3098" t="s">
         <v>194</v>
       </c>
       <c r="F3098" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3098" s="1">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="H3098" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3098" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3098" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3099">
       <c r="A3099" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3099" t="s">
         <v>25</v>
@@ -99823,7 +99823,7 @@
         <v>120</v>
       </c>
       <c r="D3099" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3099" t="s">
         <v>194</v>
@@ -99832,7 +99832,7 @@
         <v>198</v>
       </c>
       <c r="G3099" s="1">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="H3099" s="1">
         <v>3</v>
@@ -99855,7 +99855,7 @@
         <v>120</v>
       </c>
       <c r="D3100" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3100" t="s">
         <v>194</v>
@@ -99864,7 +99864,7 @@
         <v>198</v>
       </c>
       <c r="G3100" s="1">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="H3100" s="1">
         <v>3</v>
@@ -99878,31 +99878,31 @@
     </row>
     <row r="3101">
       <c r="A3101" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3101" t="s">
         <v>25</v>
       </c>
       <c r="C3101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3101" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3101" t="s">
         <v>194</v>
       </c>
       <c r="F3101" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3101" s="1">
-        <v>355</v>
+        <v>250</v>
       </c>
       <c r="H3101" s="1">
         <v>3</v>
       </c>
       <c r="I3101" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3101" s="1">
         <v>0</v>
@@ -99925,13 +99925,13 @@
         <v>194</v>
       </c>
       <c r="F3102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3102" s="1">
-        <v>560</v>
+        <v>355</v>
       </c>
       <c r="H3102" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3102" s="1">
         <v>3</v>
@@ -99957,24 +99957,24 @@
         <v>194</v>
       </c>
       <c r="F3103" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3103" s="1">
-        <v>1400</v>
+        <v>560</v>
       </c>
       <c r="H3103" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3103" s="1">
         <v>3</v>
       </c>
       <c r="J3103" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3104">
       <c r="A3104" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3104" t="s">
         <v>25</v>
@@ -99983,30 +99983,30 @@
         <v>121</v>
       </c>
       <c r="D3104" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3104" t="s">
         <v>194</v>
       </c>
       <c r="F3104" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3104" s="1">
-        <v>140</v>
+        <v>1400</v>
       </c>
       <c r="H3104" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3104" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3105">
       <c r="A3105" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3105" t="s">
         <v>25</v>
@@ -100015,30 +100015,30 @@
         <v>121</v>
       </c>
       <c r="D3105" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3105" t="s">
         <v>194</v>
       </c>
       <c r="F3105" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3105" s="1">
-        <v>187.5</v>
+        <v>140</v>
       </c>
       <c r="H3105" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3105" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3106">
       <c r="A3106" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3106" t="s">
         <v>25</v>
@@ -100047,30 +100047,30 @@
         <v>121</v>
       </c>
       <c r="D3106" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3106" t="s">
         <v>194</v>
       </c>
       <c r="F3106" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3106" s="1">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="H3106" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3106" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3106" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3107">
       <c r="A3107" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3107" t="s">
         <v>25</v>
@@ -100079,25 +100079,25 @@
         <v>121</v>
       </c>
       <c r="D3107" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3107" t="s">
         <v>194</v>
       </c>
       <c r="F3107" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3107" s="1">
-        <v>1080</v>
+        <v>175</v>
       </c>
       <c r="H3107" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3107" s="1">
         <v>2</v>
       </c>
       <c r="J3107" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3108">
@@ -100117,10 +100117,10 @@
         <v>194</v>
       </c>
       <c r="F3108" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3108" s="1">
-        <v>774</v>
+        <v>1080</v>
       </c>
       <c r="H3108" s="1">
         <v>2</v>
@@ -100134,7 +100134,7 @@
     </row>
     <row r="3109">
       <c r="A3109" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3109" t="s">
         <v>25</v>
@@ -100143,22 +100143,22 @@
         <v>121</v>
       </c>
       <c r="D3109" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E3109" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3109" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3109" s="1">
-        <v>500</v>
+        <v>774</v>
       </c>
       <c r="H3109" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3109" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3109" s="1">
         <v>1</v>
@@ -100166,7 +100166,7 @@
     </row>
     <row r="3110">
       <c r="A3110" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3110" t="s">
         <v>25</v>
@@ -100175,7 +100175,7 @@
         <v>121</v>
       </c>
       <c r="D3110" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3110" t="s">
         <v>195</v>
@@ -100184,16 +100184,16 @@
         <v>197</v>
       </c>
       <c r="G3110" s="1">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="H3110" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3110" s="1">
         <v>3</v>
       </c>
       <c r="J3110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3111">
@@ -100207,7 +100207,7 @@
         <v>121</v>
       </c>
       <c r="D3111" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3111" t="s">
         <v>195</v>
@@ -100216,16 +100216,16 @@
         <v>197</v>
       </c>
       <c r="G3111" s="1">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="H3111" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3111" s="1">
         <v>3</v>
       </c>
       <c r="J3111" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3112">
@@ -100239,7 +100239,7 @@
         <v>121</v>
       </c>
       <c r="D3112" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3112" t="s">
         <v>195</v>
@@ -100248,10 +100248,10 @@
         <v>197</v>
       </c>
       <c r="G3112" s="1">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="H3112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3112" s="1">
         <v>3</v>
@@ -100262,7 +100262,7 @@
     </row>
     <row r="3113">
       <c r="A3113" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3113" t="s">
         <v>25</v>
@@ -100271,25 +100271,25 @@
         <v>121</v>
       </c>
       <c r="D3113" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3113" t="s">
         <v>195</v>
       </c>
       <c r="F3113" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3113" s="1">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="H3113" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3113" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3113" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3114">
@@ -100303,7 +100303,7 @@
         <v>121</v>
       </c>
       <c r="D3114" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3114" t="s">
         <v>195</v>
@@ -100312,10 +100312,10 @@
         <v>198</v>
       </c>
       <c r="G3114" s="1">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="H3114" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3114" s="1">
         <v>2</v>
@@ -100326,7 +100326,7 @@
     </row>
     <row r="3115">
       <c r="A3115" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3115" t="s">
         <v>25</v>
@@ -100335,25 +100335,25 @@
         <v>121</v>
       </c>
       <c r="D3115" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3115" s="1">
-        <v>620</v>
+        <v>750</v>
       </c>
       <c r="H3115" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3115" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3115" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3116">
@@ -100367,19 +100367,19 @@
         <v>121</v>
       </c>
       <c r="D3116" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3116" t="s">
         <v>194</v>
       </c>
       <c r="F3116" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3116" s="1">
-        <v>400</v>
+        <v>620</v>
       </c>
       <c r="H3116" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3116" s="1">
         <v>3</v>
@@ -100399,19 +100399,19 @@
         <v>121</v>
       </c>
       <c r="D3117" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3117" t="s">
         <v>194</v>
       </c>
       <c r="F3117" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3117" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H3117" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3117" s="1">
         <v>3</v>
@@ -100422,7 +100422,7 @@
     </row>
     <row r="3118">
       <c r="A3118" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3118" t="s">
         <v>25</v>
@@ -100431,22 +100431,22 @@
         <v>121</v>
       </c>
       <c r="D3118" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E3118" t="s">
         <v>194</v>
       </c>
       <c r="F3118" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3118" s="1">
-        <v>155</v>
+        <v>380</v>
       </c>
       <c r="H3118" s="1">
         <v>2</v>
       </c>
       <c r="I3118" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3118" s="1">
         <v>1</v>
@@ -100463,7 +100463,7 @@
         <v>121</v>
       </c>
       <c r="D3119" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3119" t="s">
         <v>194</v>
@@ -100472,7 +100472,7 @@
         <v>198</v>
       </c>
       <c r="G3119" s="1">
-        <v>225</v>
+        <v>155</v>
       </c>
       <c r="H3119" s="1">
         <v>2</v>
@@ -100486,34 +100486,34 @@
     </row>
     <row r="3120">
       <c r="A3120" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3120" t="s">
         <v>25</v>
       </c>
       <c r="C3120" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3120" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3120" t="s">
         <v>194</v>
       </c>
       <c r="F3120" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3120" s="1">
-        <v>420</v>
+        <v>225</v>
       </c>
       <c r="H3120" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3120" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3120" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3121">
@@ -100533,13 +100533,13 @@
         <v>194</v>
       </c>
       <c r="F3121" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3121" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="H3121" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3121" s="1">
         <v>3</v>
@@ -100565,13 +100565,13 @@
         <v>194</v>
       </c>
       <c r="F3122" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3122" s="1">
-        <v>710</v>
+        <v>520</v>
       </c>
       <c r="H3122" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3122" s="1">
         <v>3</v>
@@ -100582,7 +100582,7 @@
     </row>
     <row r="3123">
       <c r="A3123" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3123" t="s">
         <v>25</v>
@@ -100591,16 +100591,16 @@
         <v>122</v>
       </c>
       <c r="D3123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E3123" t="s">
         <v>194</v>
       </c>
       <c r="F3123" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3123" s="1">
-        <v>120</v>
+        <v>710</v>
       </c>
       <c r="H3123" s="1">
         <v>3</v>
@@ -100629,13 +100629,13 @@
         <v>194</v>
       </c>
       <c r="F3124" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3124" s="1">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="H3124" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3124" s="1">
         <v>3</v>
@@ -100661,24 +100661,24 @@
         <v>194</v>
       </c>
       <c r="F3125" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3125" s="1">
-        <v>557.5</v>
+        <v>310</v>
       </c>
       <c r="H3125" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3125" s="1">
         <v>3</v>
       </c>
       <c r="J3125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3126">
       <c r="A3126" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3126" t="s">
         <v>25</v>
@@ -100687,30 +100687,30 @@
         <v>122</v>
       </c>
       <c r="D3126" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3126" t="s">
         <v>194</v>
       </c>
       <c r="F3126" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3126" s="1">
-        <v>125</v>
+        <v>557.5</v>
       </c>
       <c r="H3126" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3126" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3126" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3127">
       <c r="A3127" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3127" t="s">
         <v>25</v>
@@ -100719,7 +100719,7 @@
         <v>122</v>
       </c>
       <c r="D3127" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E3127" t="s">
         <v>194</v>
@@ -100728,7 +100728,7 @@
         <v>198</v>
       </c>
       <c r="G3127" s="1">
-        <v>1217.5</v>
+        <v>125</v>
       </c>
       <c r="H3127" s="1">
         <v>4</v>
@@ -100742,7 +100742,7 @@
     </row>
     <row r="3128">
       <c r="A3128" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3128" t="s">
         <v>25</v>
@@ -100751,7 +100751,7 @@
         <v>122</v>
       </c>
       <c r="D3128" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E3128" t="s">
         <v>194</v>
@@ -100760,16 +100760,16 @@
         <v>198</v>
       </c>
       <c r="G3128" s="1">
-        <v>495</v>
+        <v>1217.5</v>
       </c>
       <c r="H3128" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3128" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3129">
@@ -100789,10 +100789,10 @@
         <v>194</v>
       </c>
       <c r="F3129" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3129" s="1">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H3129" s="1">
         <v>1</v>
@@ -100806,7 +100806,7 @@
     </row>
     <row r="3130">
       <c r="A3130" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3130" t="s">
         <v>25</v>
@@ -100815,25 +100815,25 @@
         <v>122</v>
       </c>
       <c r="D3130" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3130" t="s">
         <v>194</v>
       </c>
       <c r="F3130" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3130" s="1">
-        <v>415</v>
+        <v>600</v>
       </c>
       <c r="H3130" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3130" s="1">
         <v>3</v>
       </c>
       <c r="J3130" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3131">
@@ -100853,13 +100853,13 @@
         <v>194</v>
       </c>
       <c r="F3131" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3131" s="1">
-        <v>585</v>
+        <v>415</v>
       </c>
       <c r="H3131" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3131" s="1">
         <v>3</v>
@@ -100885,24 +100885,24 @@
         <v>194</v>
       </c>
       <c r="F3132" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3132" s="1">
-        <v>645</v>
+        <v>585</v>
       </c>
       <c r="H3132" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3132" s="1">
         <v>3</v>
       </c>
       <c r="J3132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3133">
       <c r="A3133" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3133" t="s">
         <v>25</v>
@@ -100911,25 +100911,25 @@
         <v>122</v>
       </c>
       <c r="D3133" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3133" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3133" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3133" s="1">
-        <v>60</v>
+        <v>645</v>
       </c>
       <c r="H3133" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3133" s="1">
         <v>3</v>
       </c>
       <c r="J3133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3134">
@@ -100943,25 +100943,25 @@
         <v>122</v>
       </c>
       <c r="D3134" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3134" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3134" t="s">
         <v>197</v>
       </c>
       <c r="G3134" s="1">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="H3134" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3134" s="1">
         <v>3</v>
       </c>
       <c r="J3134" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3135">
@@ -100978,27 +100978,27 @@
         <v>142</v>
       </c>
       <c r="E3135" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3135" t="s">
         <v>197</v>
       </c>
       <c r="G3135" s="1">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H3135" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3135" s="1">
         <v>3</v>
       </c>
       <c r="J3135" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3136">
       <c r="A3136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3136" t="s">
         <v>25</v>
@@ -101007,22 +101007,22 @@
         <v>122</v>
       </c>
       <c r="D3136" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3136" t="s">
         <v>195</v>
       </c>
       <c r="F3136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3136" s="1">
-        <v>375</v>
+        <v>120</v>
       </c>
       <c r="H3136" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3136" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3136" s="1">
         <v>0</v>
@@ -101030,7 +101030,7 @@
     </row>
     <row r="3137">
       <c r="A3137" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3137" t="s">
         <v>25</v>
@@ -101039,22 +101039,22 @@
         <v>122</v>
       </c>
       <c r="D3137" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3137" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3137" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3137" s="1">
-        <v>640</v>
+        <v>375</v>
       </c>
       <c r="H3137" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3137" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3137" s="1">
         <v>0</v>
@@ -101071,19 +101071,19 @@
         <v>122</v>
       </c>
       <c r="D3138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3138" t="s">
         <v>194</v>
       </c>
       <c r="F3138" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3138" s="1">
-        <v>450</v>
+        <v>640</v>
       </c>
       <c r="H3138" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3138" s="1">
         <v>3</v>
@@ -101103,30 +101103,30 @@
         <v>122</v>
       </c>
       <c r="D3139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3139" t="s">
         <v>194</v>
       </c>
       <c r="F3139" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3139" s="1">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="H3139" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3139" s="1">
         <v>3</v>
       </c>
       <c r="J3139" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3140">
       <c r="A3140" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3140" t="s">
         <v>25</v>
@@ -101135,7 +101135,7 @@
         <v>122</v>
       </c>
       <c r="D3140" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E3140" t="s">
         <v>194</v>
@@ -101144,16 +101144,16 @@
         <v>197</v>
       </c>
       <c r="G3140" s="1">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="H3140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3140" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3140" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3141">
@@ -101173,10 +101173,10 @@
         <v>194</v>
       </c>
       <c r="F3141" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3141" s="1">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="H3141" s="1">
         <v>3</v>
@@ -101205,10 +101205,10 @@
         <v>194</v>
       </c>
       <c r="F3142" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3142" s="1">
-        <v>280</v>
+        <v>205</v>
       </c>
       <c r="H3142" s="1">
         <v>3</v>
@@ -101222,7 +101222,7 @@
     </row>
     <row r="3143">
       <c r="A3143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3143" t="s">
         <v>25</v>
@@ -101231,16 +101231,16 @@
         <v>122</v>
       </c>
       <c r="D3143" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3143" t="s">
         <v>194</v>
       </c>
       <c r="F3143" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3143" s="1">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="H3143" s="1">
         <v>3</v>
@@ -101263,7 +101263,7 @@
         <v>122</v>
       </c>
       <c r="D3144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3144" t="s">
         <v>194</v>
@@ -101272,16 +101272,16 @@
         <v>198</v>
       </c>
       <c r="G3144" s="1">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="H3144" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3144" s="1">
         <v>2</v>
       </c>
       <c r="J3144" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3145">
@@ -101295,7 +101295,7 @@
         <v>122</v>
       </c>
       <c r="D3145" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E3145" t="s">
         <v>194</v>
@@ -101304,45 +101304,45 @@
         <v>198</v>
       </c>
       <c r="G3145" s="1">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H3145" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3145" s="1">
         <v>2</v>
       </c>
       <c r="J3145" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3146">
       <c r="A3146" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3146" t="s">
         <v>25</v>
       </c>
       <c r="C3146" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D3146" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3146" t="s">
         <v>194</v>
       </c>
       <c r="F3146" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3146" s="1">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="H3146" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3146" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3146" s="1">
         <v>0</v>
@@ -101365,13 +101365,13 @@
         <v>194</v>
       </c>
       <c r="F3147" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3147" s="1">
-        <v>437.5</v>
+        <v>285</v>
       </c>
       <c r="H3147" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3147" s="1">
         <v>3</v>
@@ -101397,13 +101397,13 @@
         <v>194</v>
       </c>
       <c r="F3148" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3148" s="1">
-        <v>857.5</v>
+        <v>437.5</v>
       </c>
       <c r="H3148" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3148" s="1">
         <v>3</v>
@@ -101414,7 +101414,7 @@
     </row>
     <row r="3149">
       <c r="A3149" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3149" t="s">
         <v>25</v>
@@ -101423,22 +101423,22 @@
         <v>123</v>
       </c>
       <c r="D3149" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3149" t="s">
         <v>194</v>
       </c>
       <c r="F3149" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3149" s="1">
-        <v>75</v>
+        <v>857.5</v>
       </c>
       <c r="H3149" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3149" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3149" s="1">
         <v>0</v>
@@ -101446,7 +101446,7 @@
     </row>
     <row r="3150">
       <c r="A3150" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3150" t="s">
         <v>25</v>
@@ -101455,25 +101455,25 @@
         <v>123</v>
       </c>
       <c r="D3150" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3150" t="s">
         <v>194</v>
       </c>
       <c r="F3150" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3150" s="1">
-        <v>365</v>
+        <v>75</v>
       </c>
       <c r="H3150" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3150" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3151">
@@ -101493,10 +101493,10 @@
         <v>194</v>
       </c>
       <c r="F3151" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3151" s="1">
-        <v>707.5</v>
+        <v>365</v>
       </c>
       <c r="H3151" s="1">
         <v>2</v>
@@ -101525,13 +101525,13 @@
         <v>194</v>
       </c>
       <c r="F3152" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3152" s="1">
-        <v>1280</v>
+        <v>707.5</v>
       </c>
       <c r="H3152" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3152" s="1">
         <v>3</v>
@@ -101542,7 +101542,7 @@
     </row>
     <row r="3153">
       <c r="A3153" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3153" t="s">
         <v>25</v>
@@ -101551,30 +101551,30 @@
         <v>123</v>
       </c>
       <c r="D3153" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3153" t="s">
         <v>194</v>
       </c>
       <c r="F3153" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3153" s="1">
-        <v>150</v>
+        <v>1280</v>
       </c>
       <c r="H3153" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3153" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3153" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3154">
       <c r="A3154" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3154" t="s">
         <v>25</v>
@@ -101583,25 +101583,25 @@
         <v>123</v>
       </c>
       <c r="D3154" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3154" t="s">
         <v>194</v>
       </c>
       <c r="F3154" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3154" s="1">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="H3154" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3154" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3154" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3155">
@@ -101621,13 +101621,13 @@
         <v>194</v>
       </c>
       <c r="F3155" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3155" s="1">
-        <v>327.5</v>
+        <v>185</v>
       </c>
       <c r="H3155" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3155" s="1">
         <v>3</v>
@@ -101647,7 +101647,7 @@
         <v>123</v>
       </c>
       <c r="D3156" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E3156" t="s">
         <v>194</v>
@@ -101656,13 +101656,13 @@
         <v>198</v>
       </c>
       <c r="G3156" s="1">
-        <v>1090</v>
+        <v>327.5</v>
       </c>
       <c r="H3156" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3156" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3156" s="1">
         <v>1</v>
@@ -101685,10 +101685,10 @@
         <v>194</v>
       </c>
       <c r="F3157" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3157" s="1">
-        <v>1305</v>
+        <v>1090</v>
       </c>
       <c r="H3157" s="1">
         <v>1</v>
@@ -101702,7 +101702,7 @@
     </row>
     <row r="3158">
       <c r="A3158" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3158" t="s">
         <v>25</v>
@@ -101711,22 +101711,22 @@
         <v>123</v>
       </c>
       <c r="D3158" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E3158" t="s">
         <v>194</v>
       </c>
       <c r="F3158" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3158" s="1">
-        <v>480</v>
+        <v>1305</v>
       </c>
       <c r="H3158" s="1">
         <v>1</v>
       </c>
       <c r="I3158" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3158" s="1">
         <v>1</v>
@@ -101749,10 +101749,10 @@
         <v>194</v>
       </c>
       <c r="F3159" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3159" s="1">
-        <v>610</v>
+        <v>480</v>
       </c>
       <c r="H3159" s="1">
         <v>1</v>
@@ -101778,13 +101778,13 @@
         <v>151</v>
       </c>
       <c r="E3160" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3160" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3160" s="1">
-        <v>320</v>
+        <v>610</v>
       </c>
       <c r="H3160" s="1">
         <v>1</v>
@@ -101798,7 +101798,7 @@
     </row>
     <row r="3161">
       <c r="A3161" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3161" t="s">
         <v>25</v>
@@ -101807,16 +101807,16 @@
         <v>123</v>
       </c>
       <c r="D3161" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3161" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3161" t="s">
         <v>198</v>
       </c>
       <c r="G3161" s="1">
-        <v>585</v>
+        <v>320</v>
       </c>
       <c r="H3161" s="1">
         <v>1</v>
@@ -101845,10 +101845,10 @@
         <v>194</v>
       </c>
       <c r="F3162" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3162" s="1">
-        <v>695</v>
+        <v>585</v>
       </c>
       <c r="H3162" s="1">
         <v>1</v>
@@ -101871,19 +101871,19 @@
         <v>123</v>
       </c>
       <c r="D3163" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3163" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3163" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3163" s="1">
-        <v>40</v>
+        <v>695</v>
       </c>
       <c r="H3163" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3163" s="1">
         <v>3</v>
@@ -101909,13 +101909,13 @@
         <v>195</v>
       </c>
       <c r="F3164" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3164" s="1">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="H3164" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3164" s="1">
         <v>3</v>
@@ -101926,7 +101926,7 @@
     </row>
     <row r="3165">
       <c r="A3165" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3165" t="s">
         <v>25</v>
@@ -101935,7 +101935,7 @@
         <v>123</v>
       </c>
       <c r="D3165" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3165" t="s">
         <v>195</v>
@@ -101944,16 +101944,16 @@
         <v>198</v>
       </c>
       <c r="G3165" s="1">
-        <v>375</v>
+        <v>110</v>
       </c>
       <c r="H3165" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3165" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3165" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3166">
@@ -101967,7 +101967,7 @@
         <v>123</v>
       </c>
       <c r="D3166" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3166" t="s">
         <v>195</v>
@@ -101976,7 +101976,7 @@
         <v>198</v>
       </c>
       <c r="G3166" s="1">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="H3166" s="1">
         <v>6</v>
@@ -101990,7 +101990,7 @@
     </row>
     <row r="3167">
       <c r="A3167" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3167" t="s">
         <v>25</v>
@@ -101999,25 +101999,25 @@
         <v>123</v>
       </c>
       <c r="D3167" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3167" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3167" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3167" s="1">
-        <v>610</v>
+        <v>750</v>
       </c>
       <c r="H3167" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3167" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3167" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3168">
@@ -102031,16 +102031,16 @@
         <v>123</v>
       </c>
       <c r="D3168" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3168" t="s">
         <v>194</v>
       </c>
       <c r="F3168" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3168" s="1">
-        <v>435</v>
+        <v>610</v>
       </c>
       <c r="H3168" s="1">
         <v>2</v>
@@ -102063,16 +102063,16 @@
         <v>123</v>
       </c>
       <c r="D3169" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3169" t="s">
         <v>194</v>
       </c>
       <c r="F3169" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3169" s="1">
-        <v>275</v>
+        <v>435</v>
       </c>
       <c r="H3169" s="1">
         <v>2</v>
@@ -102086,7 +102086,7 @@
     </row>
     <row r="3170">
       <c r="A3170" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3170" t="s">
         <v>25</v>
@@ -102095,22 +102095,22 @@
         <v>123</v>
       </c>
       <c r="D3170" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E3170" t="s">
         <v>194</v>
       </c>
       <c r="F3170" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3170" s="1">
-        <v>250.36363081498581</v>
+        <v>275</v>
       </c>
       <c r="H3170" s="1">
         <v>2</v>
       </c>
       <c r="I3170" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3170" s="1">
         <v>1</v>
@@ -102118,16 +102118,16 @@
     </row>
     <row r="3171">
       <c r="A3171" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3171" t="s">
         <v>25</v>
       </c>
       <c r="C3171" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3171" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3171" t="s">
         <v>194</v>
@@ -102136,21 +102136,21 @@
         <v>198</v>
       </c>
       <c r="G3171" s="1">
-        <v>405</v>
+        <v>250.36363081498581</v>
       </c>
       <c r="H3171" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3171" s="1">
         <v>2</v>
       </c>
       <c r="J3171" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3172">
       <c r="A3172" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3172" t="s">
         <v>25</v>
@@ -102159,22 +102159,22 @@
         <v>124</v>
       </c>
       <c r="D3172" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E3172" t="s">
         <v>194</v>
       </c>
       <c r="F3172" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3172" s="1">
-        <v>320</v>
+        <v>405</v>
       </c>
       <c r="H3172" s="1">
         <v>3</v>
       </c>
       <c r="I3172" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3172" s="1">
         <v>0</v>
@@ -102182,7 +102182,7 @@
     </row>
     <row r="3173">
       <c r="A3173" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3173" t="s">
         <v>25</v>
@@ -102191,22 +102191,22 @@
         <v>124</v>
       </c>
       <c r="D3173" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3173" t="s">
         <v>194</v>
       </c>
       <c r="F3173" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3173" s="1">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="H3173" s="1">
         <v>3</v>
       </c>
       <c r="I3173" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3173" s="1">
         <v>0</v>
@@ -102214,7 +102214,7 @@
     </row>
     <row r="3174">
       <c r="A3174" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3174" t="s">
         <v>25</v>
@@ -102223,25 +102223,25 @@
         <v>124</v>
       </c>
       <c r="D3174" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3174" t="s">
         <v>194</v>
       </c>
       <c r="F3174" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3174" s="1">
-        <v>1140</v>
+        <v>150</v>
       </c>
       <c r="H3174" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3174" s="1">
         <v>2</v>
       </c>
       <c r="J3174" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3175">
@@ -102261,10 +102261,10 @@
         <v>194</v>
       </c>
       <c r="F3175" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3175" s="1">
-        <v>1185</v>
+        <v>1140</v>
       </c>
       <c r="H3175" s="1">
         <v>2</v>
@@ -102278,7 +102278,7 @@
     </row>
     <row r="3176">
       <c r="A3176" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3176" t="s">
         <v>25</v>
@@ -102287,22 +102287,22 @@
         <v>124</v>
       </c>
       <c r="D3176" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E3176" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3176" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3176" s="1">
-        <v>100</v>
+        <v>1185</v>
       </c>
       <c r="H3176" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3176" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3176" s="1">
         <v>1</v>
@@ -102319,7 +102319,7 @@
         <v>124</v>
       </c>
       <c r="D3177" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3177" t="s">
         <v>195</v>
@@ -102328,7 +102328,7 @@
         <v>197</v>
       </c>
       <c r="G3177" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H3177" s="1">
         <v>1</v>
@@ -102342,7 +102342,7 @@
     </row>
     <row r="3178">
       <c r="A3178" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3178" t="s">
         <v>25</v>
@@ -102351,22 +102351,22 @@
         <v>124</v>
       </c>
       <c r="D3178" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3178" t="s">
         <v>195</v>
       </c>
       <c r="F3178" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3178" s="1">
-        <v>375</v>
+        <v>75</v>
       </c>
       <c r="H3178" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3178" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3178" s="1">
         <v>1</v>
@@ -102374,7 +102374,7 @@
     </row>
     <row r="3179">
       <c r="A3179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3179" t="s">
         <v>25</v>
@@ -102383,22 +102383,22 @@
         <v>124</v>
       </c>
       <c r="D3179" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3179" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3179" s="1">
-        <v>700</v>
+        <v>375</v>
       </c>
       <c r="H3179" s="1">
         <v>2</v>
       </c>
       <c r="I3179" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3179" s="1">
         <v>1</v>
@@ -102415,19 +102415,19 @@
         <v>124</v>
       </c>
       <c r="D3180" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3180" t="s">
         <v>194</v>
       </c>
       <c r="F3180" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3180" s="1">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="H3180" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3180" s="1">
         <v>3</v>
@@ -102438,7 +102438,7 @@
     </row>
     <row r="3181">
       <c r="A3181" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3181" t="s">
         <v>25</v>
@@ -102447,7 +102447,7 @@
         <v>124</v>
       </c>
       <c r="D3181" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E3181" t="s">
         <v>194</v>
@@ -102456,16 +102456,16 @@
         <v>198</v>
       </c>
       <c r="G3181" s="1">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="H3181" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3181" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3181" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3182">
@@ -102479,7 +102479,7 @@
         <v>124</v>
       </c>
       <c r="D3182" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3182" t="s">
         <v>194</v>
@@ -102488,10 +102488,10 @@
         <v>198</v>
       </c>
       <c r="G3182" s="1">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="H3182" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3182" s="1">
         <v>2</v>
@@ -102502,16 +102502,16 @@
     </row>
     <row r="3183">
       <c r="A3183" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3183" t="s">
         <v>25</v>
       </c>
       <c r="C3183" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D3183" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3183" t="s">
         <v>194</v>
@@ -102520,10 +102520,10 @@
         <v>198</v>
       </c>
       <c r="G3183" s="1">
-        <v>445</v>
+        <v>250</v>
       </c>
       <c r="H3183" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3183" s="1">
         <v>2</v>
@@ -102534,7 +102534,7 @@
     </row>
     <row r="3184">
       <c r="A3184" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3184" t="s">
         <v>25</v>
@@ -102543,22 +102543,22 @@
         <v>66</v>
       </c>
       <c r="D3184" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3184" t="s">
         <v>194</v>
       </c>
       <c r="F3184" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3184" s="1">
-        <v>140</v>
+        <v>445</v>
       </c>
       <c r="H3184" s="1">
         <v>3</v>
       </c>
       <c r="I3184" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3184" s="1">
         <v>0</v>
@@ -102581,13 +102581,13 @@
         <v>194</v>
       </c>
       <c r="F3185" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3185" s="1">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="H3185" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3185" s="1">
         <v>3</v>
@@ -102613,24 +102613,24 @@
         <v>194</v>
       </c>
       <c r="F3186" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3186" s="1">
-        <v>432.5</v>
+        <v>230</v>
       </c>
       <c r="H3186" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3186" s="1">
         <v>3</v>
       </c>
       <c r="J3186" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3187">
       <c r="A3187" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3187" t="s">
         <v>25</v>
@@ -102639,16 +102639,16 @@
         <v>66</v>
       </c>
       <c r="D3187" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3187" t="s">
         <v>194</v>
       </c>
       <c r="F3187" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3187" s="1">
-        <v>310</v>
+        <v>432.5</v>
       </c>
       <c r="H3187" s="1">
         <v>2</v>
@@ -102677,13 +102677,13 @@
         <v>194</v>
       </c>
       <c r="F3188" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G3188" s="1">
-        <v>485</v>
+        <v>310</v>
       </c>
       <c r="H3188" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3188" s="1">
         <v>3</v>
@@ -102694,7 +102694,7 @@
     </row>
     <row r="3189">
       <c r="A3189" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3189" t="s">
         <v>25</v>
@@ -102703,25 +102703,25 @@
         <v>66</v>
       </c>
       <c r="D3189" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3189" t="s">
         <v>194</v>
       </c>
       <c r="F3189" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3189" s="1">
-        <v>95</v>
+        <v>485</v>
       </c>
       <c r="H3189" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3189" s="1">
         <v>3</v>
       </c>
       <c r="J3189" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3190">
@@ -102741,13 +102741,13 @@
         <v>194</v>
       </c>
       <c r="F3190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3190" s="1">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="H3190" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3190" s="1">
         <v>3</v>
@@ -102773,24 +102773,24 @@
         <v>194</v>
       </c>
       <c r="F3191" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3191" s="1">
-        <v>277.5</v>
+        <v>140</v>
       </c>
       <c r="H3191" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3191" s="1">
         <v>3</v>
       </c>
       <c r="J3191" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3192">
       <c r="A3192" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3192" t="s">
         <v>25</v>
@@ -102799,25 +102799,25 @@
         <v>66</v>
       </c>
       <c r="D3192" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3192" t="s">
         <v>194</v>
       </c>
       <c r="F3192" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3192" s="1">
-        <v>745</v>
+        <v>277.5</v>
       </c>
       <c r="H3192" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3192" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3192" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3193">
@@ -102837,10 +102837,10 @@
         <v>194</v>
       </c>
       <c r="F3193" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3193" s="1">
-        <v>1240</v>
+        <v>745</v>
       </c>
       <c r="H3193" s="1">
         <v>3</v>
@@ -102863,22 +102863,22 @@
         <v>66</v>
       </c>
       <c r="D3194" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E3194" t="s">
         <v>194</v>
       </c>
       <c r="F3194" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3194" s="1">
-        <v>820</v>
+        <v>1240</v>
       </c>
       <c r="H3194" s="1">
         <v>3</v>
       </c>
       <c r="I3194" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3194" s="1">
         <v>0</v>
@@ -102901,13 +102901,13 @@
         <v>194</v>
       </c>
       <c r="F3195" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3195" s="1">
-        <v>1237.5</v>
+        <v>820</v>
       </c>
       <c r="H3195" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3195" s="1">
         <v>3</v>
@@ -102933,24 +102933,24 @@
         <v>194</v>
       </c>
       <c r="F3196" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3196" s="1">
-        <v>1522.5</v>
+        <v>1237.5</v>
       </c>
       <c r="H3196" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3196" s="1">
         <v>3</v>
       </c>
       <c r="J3196" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3197">
       <c r="A3197" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3197" t="s">
         <v>25</v>
@@ -102959,25 +102959,25 @@
         <v>66</v>
       </c>
       <c r="D3197" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E3197" t="s">
         <v>194</v>
       </c>
       <c r="F3197" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3197" s="1">
-        <v>205</v>
+        <v>1522.5</v>
       </c>
       <c r="H3197" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3197" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3197" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3198">
@@ -102997,10 +102997,10 @@
         <v>194</v>
       </c>
       <c r="F3198" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3198" s="1">
-        <v>410</v>
+        <v>205</v>
       </c>
       <c r="H3198" s="1">
         <v>3</v>
@@ -103014,7 +103014,7 @@
     </row>
     <row r="3199">
       <c r="A3199" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3199" t="s">
         <v>25</v>
@@ -103029,19 +103029,19 @@
         <v>194</v>
       </c>
       <c r="F3199" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3199" s="1">
-        <v>85</v>
+        <v>410</v>
       </c>
       <c r="H3199" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3199" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3199" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3200">
@@ -103058,16 +103058,16 @@
         <v>130</v>
       </c>
       <c r="E3200" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3200" t="s">
         <v>197</v>
       </c>
       <c r="G3200" s="1">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H3200" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3200" s="1">
         <v>3</v>
@@ -103093,10 +103093,10 @@
         <v>195</v>
       </c>
       <c r="F3201" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3201" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H3201" s="1">
         <v>1</v>
@@ -103119,19 +103119,19 @@
         <v>66</v>
       </c>
       <c r="D3202" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3202" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3202" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3202" s="1">
-        <v>47.5</v>
+        <v>60</v>
       </c>
       <c r="H3202" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3202" s="1">
         <v>3</v>
@@ -103154,16 +103154,16 @@
         <v>134</v>
       </c>
       <c r="E3203" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3203" t="s">
         <v>197</v>
       </c>
       <c r="G3203" s="1">
-        <v>60</v>
+        <v>47.5</v>
       </c>
       <c r="H3203" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3203" s="1">
         <v>3</v>
@@ -103183,19 +103183,19 @@
         <v>66</v>
       </c>
       <c r="D3204" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3204" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3204" t="s">
         <v>197</v>
       </c>
       <c r="G3204" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H3204" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3204" s="1">
         <v>3</v>
@@ -103221,13 +103221,13 @@
         <v>194</v>
       </c>
       <c r="F3205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3205" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H3205" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3205" s="1">
         <v>3</v>
@@ -103253,10 +103253,10 @@
         <v>194</v>
       </c>
       <c r="F3206" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3206" s="1">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="H3206" s="1">
         <v>1</v>
@@ -103282,13 +103282,13 @@
         <v>142</v>
       </c>
       <c r="E3207" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3207" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3207" s="1">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="H3207" s="1">
         <v>1</v>
@@ -103317,13 +103317,13 @@
         <v>195</v>
       </c>
       <c r="F3208" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3208" s="1">
-        <v>425</v>
+        <v>100</v>
       </c>
       <c r="H3208" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3208" s="1">
         <v>3</v>
@@ -103334,7 +103334,7 @@
     </row>
     <row r="3209">
       <c r="A3209" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3209" t="s">
         <v>25</v>
@@ -103343,7 +103343,7 @@
         <v>66</v>
       </c>
       <c r="D3209" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3209" t="s">
         <v>195</v>
@@ -103352,16 +103352,16 @@
         <v>198</v>
       </c>
       <c r="G3209" s="1">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="H3209" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3209" s="1">
         <v>3</v>
       </c>
       <c r="J3209" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3210">
@@ -103381,10 +103381,10 @@
         <v>195</v>
       </c>
       <c r="F3210" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3210" s="1">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="H3210" s="1">
         <v>4</v>
@@ -103407,30 +103407,30 @@
         <v>66</v>
       </c>
       <c r="D3211" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3211" t="s">
         <v>195</v>
       </c>
       <c r="F3211" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3211" s="1">
         <v>750</v>
       </c>
       <c r="H3211" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3211" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3211" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3212">
       <c r="A3212" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3212" t="s">
         <v>25</v>
@@ -103439,22 +103439,22 @@
         <v>66</v>
       </c>
       <c r="D3212" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3212" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3212" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3212" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="H3212" s="1">
         <v>2</v>
       </c>
       <c r="I3212" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3212" s="1">
         <v>1</v>
@@ -103477,10 +103477,10 @@
         <v>194</v>
       </c>
       <c r="F3213" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3213" s="1">
-        <v>640</v>
+        <v>500</v>
       </c>
       <c r="H3213" s="1">
         <v>2</v>
@@ -103503,7 +103503,7 @@
         <v>66</v>
       </c>
       <c r="D3214" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3214" t="s">
         <v>194</v>
@@ -103512,10 +103512,10 @@
         <v>198</v>
       </c>
       <c r="G3214" s="1">
-        <v>450</v>
+        <v>640</v>
       </c>
       <c r="H3214" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3214" s="1">
         <v>3</v>
@@ -103535,19 +103535,19 @@
         <v>66</v>
       </c>
       <c r="D3215" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3215" t="s">
         <v>194</v>
       </c>
       <c r="F3215" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3215" s="1">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="H3215" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3215" s="1">
         <v>3</v>
@@ -103573,13 +103573,13 @@
         <v>194</v>
       </c>
       <c r="F3216" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3216" s="1">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="H3216" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3216" s="1">
         <v>3</v>
@@ -103590,7 +103590,7 @@
     </row>
     <row r="3217">
       <c r="A3217" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3217" t="s">
         <v>25</v>
@@ -103599,7 +103599,7 @@
         <v>66</v>
       </c>
       <c r="D3217" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E3217" t="s">
         <v>194</v>
@@ -103608,21 +103608,21 @@
         <v>198</v>
       </c>
       <c r="G3217" s="1">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="H3217" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3217" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3217" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3218">
       <c r="A3218" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3218" t="s">
         <v>25</v>
@@ -103631,25 +103631,25 @@
         <v>66</v>
       </c>
       <c r="D3218" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3218" t="s">
         <v>194</v>
       </c>
       <c r="F3218" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3218" s="1">
-        <v>127.5</v>
+        <v>225</v>
       </c>
       <c r="H3218" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3218" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3218" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3219">
@@ -103669,13 +103669,13 @@
         <v>194</v>
       </c>
       <c r="F3219" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3219" s="1">
-        <v>225</v>
+        <v>127.5</v>
       </c>
       <c r="H3219" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3219" s="1">
         <v>3</v>
@@ -103701,10 +103701,10 @@
         <v>194</v>
       </c>
       <c r="F3220" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3220" s="1">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H3220" s="1">
         <v>1</v>
@@ -103727,25 +103727,25 @@
         <v>66</v>
       </c>
       <c r="D3221" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3221" t="s">
         <v>194</v>
       </c>
       <c r="F3221" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3221" s="1">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="H3221" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3221" s="1">
         <v>3</v>
       </c>
       <c r="J3221" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3222">
@@ -103765,13 +103765,13 @@
         <v>194</v>
       </c>
       <c r="F3222" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3222" s="1">
-        <v>257.5</v>
+        <v>170</v>
       </c>
       <c r="H3222" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3222" s="1">
         <v>3</v>
@@ -103797,56 +103797,56 @@
         <v>194</v>
       </c>
       <c r="F3223" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3223" s="1">
-        <v>490</v>
+        <v>257.5</v>
       </c>
       <c r="H3223" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3223" s="1">
         <v>3</v>
       </c>
       <c r="J3223" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3224">
       <c r="A3224" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3224" t="s">
         <v>25</v>
       </c>
       <c r="C3224" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="D3224" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3224" t="s">
         <v>194</v>
       </c>
       <c r="F3224" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3224" s="1">
-        <v>472.5</v>
+        <v>490</v>
       </c>
       <c r="H3224" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3224" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3224" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3225">
       <c r="A3225" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3225" t="s">
         <v>25</v>
@@ -103855,7 +103855,7 @@
         <v>125</v>
       </c>
       <c r="D3225" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3225" t="s">
         <v>194</v>
@@ -103864,10 +103864,10 @@
         <v>198</v>
       </c>
       <c r="G3225" s="1">
-        <v>100</v>
+        <v>472.5</v>
       </c>
       <c r="H3225" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3225" s="1">
         <v>2</v>
@@ -103878,7 +103878,7 @@
     </row>
     <row r="3226">
       <c r="A3226" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3226" t="s">
         <v>25</v>
@@ -103887,30 +103887,30 @@
         <v>125</v>
       </c>
       <c r="D3226" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3226" t="s">
         <v>194</v>
       </c>
       <c r="F3226" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3226" s="1">
-        <v>215.5</v>
+        <v>100</v>
       </c>
       <c r="H3226" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3226" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3226" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3227">
       <c r="A3227" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3227" t="s">
         <v>25</v>
@@ -103919,30 +103919,30 @@
         <v>125</v>
       </c>
       <c r="D3227" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3227" t="s">
         <v>194</v>
       </c>
       <c r="F3227" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3227" s="1">
-        <v>137.5</v>
+        <v>215.5</v>
       </c>
       <c r="H3227" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3227" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3227" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3228">
       <c r="A3228" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3228" t="s">
         <v>25</v>
@@ -103951,7 +103951,7 @@
         <v>125</v>
       </c>
       <c r="D3228" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3228" t="s">
         <v>194</v>
@@ -103960,21 +103960,21 @@
         <v>198</v>
       </c>
       <c r="G3228" s="1">
-        <v>1117.5</v>
+        <v>137.5</v>
       </c>
       <c r="H3228" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3228" s="1">
         <v>2</v>
       </c>
       <c r="J3228" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3229">
       <c r="A3229" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3229" t="s">
         <v>25</v>
@@ -103983,22 +103983,22 @@
         <v>125</v>
       </c>
       <c r="D3229" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E3229" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3229" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3229" s="1">
-        <v>355</v>
+        <v>1117.5</v>
       </c>
       <c r="H3229" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3229" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3229" s="1">
         <v>1</v>
@@ -104006,7 +104006,7 @@
     </row>
     <row r="3230">
       <c r="A3230" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3230" t="s">
         <v>25</v>
@@ -104015,22 +104015,22 @@
         <v>125</v>
       </c>
       <c r="D3230" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3230" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3230" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3230" s="1">
-        <v>507.5</v>
+        <v>355</v>
       </c>
       <c r="H3230" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3230" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3230" s="1">
         <v>1</v>
@@ -104038,7 +104038,7 @@
     </row>
     <row r="3231">
       <c r="A3231" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3231" t="s">
         <v>25</v>
@@ -104053,16 +104053,16 @@
         <v>194</v>
       </c>
       <c r="F3231" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3231" s="1">
-        <v>65</v>
+        <v>507.5</v>
       </c>
       <c r="H3231" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3231" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3231" s="1">
         <v>1</v>
@@ -104082,16 +104082,16 @@
         <v>130</v>
       </c>
       <c r="E3232" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3232" t="s">
         <v>197</v>
       </c>
       <c r="G3232" s="1">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H3232" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3232" s="1">
         <v>3</v>
@@ -104111,7 +104111,7 @@
         <v>125</v>
       </c>
       <c r="D3233" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E3233" t="s">
         <v>195</v>
@@ -104120,10 +104120,10 @@
         <v>197</v>
       </c>
       <c r="G3233" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H3233" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3233" s="1">
         <v>3</v>
@@ -104134,7 +104134,7 @@
     </row>
     <row r="3234">
       <c r="A3234" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3234" t="s">
         <v>25</v>
@@ -104143,30 +104143,30 @@
         <v>125</v>
       </c>
       <c r="D3234" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3234" t="s">
         <v>195</v>
       </c>
       <c r="F3234" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3234" s="1">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="H3234" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3234" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3234" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3235">
       <c r="A3235" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3235" t="s">
         <v>25</v>
@@ -104175,22 +104175,22 @@
         <v>125</v>
       </c>
       <c r="D3235" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3235" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3235" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3235" s="1">
-        <v>640</v>
+        <v>375</v>
       </c>
       <c r="H3235" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3235" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3235" s="1">
         <v>0</v>
@@ -104207,25 +104207,25 @@
         <v>125</v>
       </c>
       <c r="D3236" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3236" t="s">
         <v>194</v>
       </c>
       <c r="F3236" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3236" s="1">
-        <v>475</v>
+        <v>640</v>
       </c>
       <c r="H3236" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3236" s="1">
         <v>3</v>
       </c>
       <c r="J3236" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3237">
@@ -104239,30 +104239,30 @@
         <v>125</v>
       </c>
       <c r="D3237" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3237" t="s">
         <v>194</v>
       </c>
       <c r="F3237" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3237" s="1">
-        <v>220</v>
+        <v>475</v>
       </c>
       <c r="H3237" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3237" s="1">
         <v>3</v>
       </c>
       <c r="J3237" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3238">
       <c r="A3238" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3238" t="s">
         <v>25</v>
@@ -104271,30 +104271,30 @@
         <v>125</v>
       </c>
       <c r="D3238" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E3238" t="s">
         <v>194</v>
       </c>
       <c r="F3238" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3238" s="1">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="H3238" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3238" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3238" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3239">
       <c r="A3239" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3239" t="s">
         <v>25</v>
@@ -104303,7 +104303,7 @@
         <v>125</v>
       </c>
       <c r="D3239" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3239" t="s">
         <v>194</v>
@@ -104312,16 +104312,16 @@
         <v>198</v>
       </c>
       <c r="G3239" s="1">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H3239" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3239" s="1">
         <v>2</v>
       </c>
       <c r="J3239" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3240">
@@ -104335,7 +104335,7 @@
         <v>125</v>
       </c>
       <c r="D3240" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3240" t="s">
         <v>194</v>
@@ -104344,10 +104344,10 @@
         <v>198</v>
       </c>
       <c r="G3240" s="1">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="H3240" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3240" s="1">
         <v>2</v>
@@ -104358,31 +104358,31 @@
     </row>
     <row r="3241">
       <c r="A3241" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3241" t="s">
         <v>25</v>
       </c>
       <c r="C3241" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3241" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3241" t="s">
         <v>194</v>
       </c>
       <c r="F3241" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3241" s="1">
-        <v>365</v>
+        <v>215</v>
       </c>
       <c r="H3241" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3241" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3241" s="1">
         <v>0</v>
@@ -104405,13 +104405,13 @@
         <v>194</v>
       </c>
       <c r="F3242" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3242" s="1">
-        <v>592.5</v>
+        <v>365</v>
       </c>
       <c r="H3242" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3242" s="1">
         <v>3</v>
@@ -104437,13 +104437,13 @@
         <v>194</v>
       </c>
       <c r="F3243" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3243" s="1">
-        <v>710</v>
+        <v>592.5</v>
       </c>
       <c r="H3243" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3243" s="1">
         <v>3</v>
@@ -104454,7 +104454,7 @@
     </row>
     <row r="3244">
       <c r="A3244" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3244" t="s">
         <v>25</v>
@@ -104463,16 +104463,16 @@
         <v>126</v>
       </c>
       <c r="D3244" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E3244" t="s">
         <v>194</v>
       </c>
       <c r="F3244" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3244" s="1">
-        <v>310</v>
+        <v>710</v>
       </c>
       <c r="H3244" s="1">
         <v>3</v>
@@ -104486,7 +104486,7 @@
     </row>
     <row r="3245">
       <c r="A3245" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3245" t="s">
         <v>25</v>
@@ -104495,22 +104495,22 @@
         <v>126</v>
       </c>
       <c r="D3245" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3245" t="s">
         <v>194</v>
       </c>
       <c r="F3245" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3245" s="1">
-        <v>76.515632120589927</v>
+        <v>310</v>
       </c>
       <c r="H3245" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3245" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3245" s="1">
         <v>0</v>
@@ -104518,7 +104518,7 @@
     </row>
     <row r="3246">
       <c r="A3246" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3246" t="s">
         <v>25</v>
@@ -104527,25 +104527,25 @@
         <v>126</v>
       </c>
       <c r="D3246" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3246" t="s">
         <v>194</v>
       </c>
       <c r="F3246" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3246" s="1">
-        <v>946.78905528609801</v>
+        <v>76.515632120589927</v>
       </c>
       <c r="H3246" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3246" s="1">
         <v>2</v>
       </c>
       <c r="J3246" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3247">
@@ -104565,10 +104565,10 @@
         <v>194</v>
       </c>
       <c r="F3247" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3247" s="1">
-        <v>981.67075732295427</v>
+        <v>946.78905528609801</v>
       </c>
       <c r="H3247" s="1">
         <v>1</v>
@@ -104582,7 +104582,7 @@
     </row>
     <row r="3248">
       <c r="A3248" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3248" t="s">
         <v>25</v>
@@ -104591,22 +104591,22 @@
         <v>126</v>
       </c>
       <c r="D3248" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E3248" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3248" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3248" s="1">
-        <v>110</v>
+        <v>981.67075732295427</v>
       </c>
       <c r="H3248" s="1">
         <v>1</v>
       </c>
       <c r="I3248" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3248" s="1">
         <v>1</v>
@@ -104623,7 +104623,7 @@
         <v>126</v>
       </c>
       <c r="D3249" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E3249" t="s">
         <v>195</v>
@@ -104632,7 +104632,7 @@
         <v>197</v>
       </c>
       <c r="G3249" s="1">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="H3249" s="1">
         <v>1</v>
@@ -104646,7 +104646,7 @@
     </row>
     <row r="3250">
       <c r="A3250" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3250" t="s">
         <v>25</v>
@@ -104655,22 +104655,22 @@
         <v>126</v>
       </c>
       <c r="D3250" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3250" t="s">
         <v>195</v>
       </c>
       <c r="F3250" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3250" s="1">
-        <v>379.3140661960025</v>
+        <v>180</v>
       </c>
       <c r="H3250" s="1">
         <v>1</v>
       </c>
       <c r="I3250" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3250" s="1">
         <v>1</v>
@@ -104678,7 +104678,7 @@
     </row>
     <row r="3251">
       <c r="A3251" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3251" t="s">
         <v>25</v>
@@ -104687,22 +104687,22 @@
         <v>126</v>
       </c>
       <c r="D3251" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E3251" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3251" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3251" s="1">
-        <v>670</v>
+        <v>379.3140661960025</v>
       </c>
       <c r="H3251" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3251" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3251" s="1">
         <v>1</v>
@@ -104719,16 +104719,16 @@
         <v>126</v>
       </c>
       <c r="D3252" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3252" t="s">
         <v>194</v>
       </c>
       <c r="F3252" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3252" s="1">
-        <v>475</v>
+        <v>670</v>
       </c>
       <c r="H3252" s="1">
         <v>2</v>
@@ -104751,16 +104751,16 @@
         <v>126</v>
       </c>
       <c r="D3253" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3253" t="s">
         <v>194</v>
       </c>
       <c r="F3253" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3253" s="1">
-        <v>310</v>
+        <v>475</v>
       </c>
       <c r="H3253" s="1">
         <v>2</v>
@@ -104774,7 +104774,7 @@
     </row>
     <row r="3254">
       <c r="A3254" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3254" t="s">
         <v>25</v>
@@ -104783,22 +104783,22 @@
         <v>126</v>
       </c>
       <c r="D3254" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E3254" t="s">
         <v>194</v>
       </c>
       <c r="F3254" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3254" s="1">
-        <v>250.72726162997162</v>
+        <v>310</v>
       </c>
       <c r="H3254" s="1">
         <v>2</v>
       </c>
       <c r="I3254" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3254" s="1">
         <v>1</v>
@@ -104815,7 +104815,7 @@
         <v>126</v>
       </c>
       <c r="D3255" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E3255" t="s">
         <v>194</v>
@@ -104824,10 +104824,10 @@
         <v>198</v>
       </c>
       <c r="G3255" s="1">
-        <v>175.50908314098012</v>
+        <v>250.72726162997162</v>
       </c>
       <c r="H3255" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3255" s="1">
         <v>2</v>
@@ -104847,7 +104847,7 @@
         <v>126</v>
       </c>
       <c r="D3256" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E3256" t="s">
         <v>194</v>
@@ -104856,10 +104856,10 @@
         <v>198</v>
       </c>
       <c r="G3256" s="1">
-        <v>215.62544500177558</v>
+        <v>175.50908314098012</v>
       </c>
       <c r="H3256" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3256" s="1">
         <v>2</v>
@@ -104870,34 +104870,34 @@
     </row>
     <row r="3257">
       <c r="A3257" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3257" t="s">
         <v>25</v>
       </c>
       <c r="C3257" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D3257" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3257" t="s">
         <v>194</v>
       </c>
       <c r="F3257" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3257" s="1">
-        <v>450</v>
+        <v>215.62544500177558</v>
       </c>
       <c r="H3257" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3257" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3257" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3258">
@@ -104917,13 +104917,13 @@
         <v>194</v>
       </c>
       <c r="F3258" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3258" s="1">
-        <v>685</v>
+        <v>450</v>
       </c>
       <c r="H3258" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3258" s="1">
         <v>3</v>
@@ -104949,13 +104949,13 @@
         <v>194</v>
       </c>
       <c r="F3259" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3259" s="1">
-        <v>870</v>
+        <v>685</v>
       </c>
       <c r="H3259" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3259" s="1">
         <v>3</v>
@@ -104966,7 +104966,7 @@
     </row>
     <row r="3260">
       <c r="A3260" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3260" t="s">
         <v>25</v>
@@ -104975,22 +104975,22 @@
         <v>103</v>
       </c>
       <c r="D3260" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3260" t="s">
         <v>194</v>
       </c>
       <c r="F3260" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3260" s="1">
-        <v>185</v>
+        <v>870</v>
       </c>
       <c r="H3260" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3260" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3260" s="1">
         <v>0</v>
@@ -104998,7 +104998,7 @@
     </row>
     <row r="3261">
       <c r="A3261" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3261" t="s">
         <v>25</v>
@@ -105007,22 +105007,22 @@
         <v>103</v>
       </c>
       <c r="D3261" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3261" t="s">
         <v>194</v>
       </c>
       <c r="F3261" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3261" s="1">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="H3261" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3261" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3261" s="1">
         <v>0</v>
@@ -105045,13 +105045,13 @@
         <v>194</v>
       </c>
       <c r="F3262" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3262" s="1">
-        <v>447.5</v>
+        <v>250</v>
       </c>
       <c r="H3262" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3262" s="1">
         <v>3</v>
@@ -105077,13 +105077,13 @@
         <v>194</v>
       </c>
       <c r="F3263" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3263" s="1">
-        <v>972.5</v>
+        <v>447.5</v>
       </c>
       <c r="H3263" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3263" s="1">
         <v>3</v>
@@ -105094,7 +105094,7 @@
     </row>
     <row r="3264">
       <c r="A3264" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3264" t="s">
         <v>25</v>
@@ -105103,16 +105103,16 @@
         <v>103</v>
       </c>
       <c r="D3264" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3264" t="s">
         <v>194</v>
       </c>
       <c r="F3264" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3264" s="1">
-        <v>67.5</v>
+        <v>972.5</v>
       </c>
       <c r="H3264" s="1">
         <v>4</v>
@@ -105141,13 +105141,13 @@
         <v>194</v>
       </c>
       <c r="F3265" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3265" s="1">
-        <v>110</v>
+        <v>67.5</v>
       </c>
       <c r="H3265" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3265" s="1">
         <v>3</v>
@@ -105173,13 +105173,13 @@
         <v>194</v>
       </c>
       <c r="F3266" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3266" s="1">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="H3266" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3266" s="1">
         <v>3</v>
@@ -105190,7 +105190,7 @@
     </row>
     <row r="3267">
       <c r="A3267" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3267" t="s">
         <v>25</v>
@@ -105199,19 +105199,19 @@
         <v>103</v>
       </c>
       <c r="D3267" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E3267" t="s">
         <v>194</v>
       </c>
       <c r="F3267" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3267" s="1">
-        <v>870</v>
+        <v>270</v>
       </c>
       <c r="H3267" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3267" s="1">
         <v>3</v>
@@ -105237,13 +105237,13 @@
         <v>194</v>
       </c>
       <c r="F3268" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3268" s="1">
-        <v>1100</v>
+        <v>870</v>
       </c>
       <c r="H3268" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3268" s="1">
         <v>3</v>
@@ -105269,10 +105269,10 @@
         <v>194</v>
       </c>
       <c r="F3269" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3269" s="1">
-        <v>1275</v>
+        <v>1100</v>
       </c>
       <c r="H3269" s="1">
         <v>3</v>
@@ -105286,7 +105286,7 @@
     </row>
     <row r="3270">
       <c r="A3270" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3270" t="s">
         <v>25</v>
@@ -105295,16 +105295,16 @@
         <v>103</v>
       </c>
       <c r="D3270" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E3270" t="s">
         <v>194</v>
       </c>
       <c r="F3270" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3270" s="1">
-        <v>175</v>
+        <v>1275</v>
       </c>
       <c r="H3270" s="1">
         <v>3</v>
@@ -105333,13 +105333,13 @@
         <v>194</v>
       </c>
       <c r="F3271" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3271" s="1">
-        <v>197.5</v>
+        <v>175</v>
       </c>
       <c r="H3271" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3271" s="1">
         <v>3</v>
@@ -105365,24 +105365,24 @@
         <v>194</v>
       </c>
       <c r="F3272" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3272" s="1">
-        <v>267.5</v>
+        <v>197.5</v>
       </c>
       <c r="H3272" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3272" s="1">
         <v>3</v>
       </c>
       <c r="J3272" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3273">
       <c r="A3273" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3273" t="s">
         <v>25</v>
@@ -105394,22 +105394,22 @@
         <v>130</v>
       </c>
       <c r="E3273" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3273" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3273" s="1">
-        <v>60</v>
+        <v>267.5</v>
       </c>
       <c r="H3273" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3273" s="1">
         <v>3</v>
       </c>
       <c r="J3273" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3274">
@@ -105429,19 +105429,19 @@
         <v>195</v>
       </c>
       <c r="F3274" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3274" s="1">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H3274" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3274" s="1">
         <v>3</v>
       </c>
       <c r="J3274" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3275">
@@ -105455,30 +105455,30 @@
         <v>103</v>
       </c>
       <c r="D3275" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E3275" t="s">
         <v>195</v>
       </c>
       <c r="F3275" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3275" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H3275" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3275" s="1">
         <v>3</v>
       </c>
       <c r="J3275" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3276">
       <c r="A3276" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3276" t="s">
         <v>25</v>
@@ -105487,19 +105487,19 @@
         <v>103</v>
       </c>
       <c r="D3276" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3276" t="s">
         <v>195</v>
       </c>
       <c r="F3276" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3276" s="1">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="H3276" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3276" s="1">
         <v>3</v>
@@ -105525,19 +105525,19 @@
         <v>195</v>
       </c>
       <c r="F3277" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3277" s="1">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="H3277" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3277" s="1">
         <v>3</v>
       </c>
       <c r="J3277" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3278">
@@ -105551,30 +105551,30 @@
         <v>103</v>
       </c>
       <c r="D3278" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3278" t="s">
         <v>195</v>
       </c>
       <c r="F3278" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3278" s="1">
         <v>750</v>
       </c>
       <c r="H3278" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3278" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3278" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3279">
       <c r="A3279" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3279" t="s">
         <v>25</v>
@@ -105583,22 +105583,22 @@
         <v>103</v>
       </c>
       <c r="D3279" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3279" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3279" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3279" s="1">
-        <v>645</v>
+        <v>750</v>
       </c>
       <c r="H3279" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3279" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3279" s="1">
         <v>0</v>
@@ -105615,19 +105615,19 @@
         <v>103</v>
       </c>
       <c r="D3280" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3280" t="s">
         <v>194</v>
       </c>
       <c r="F3280" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3280" s="1">
-        <v>450</v>
+        <v>645</v>
       </c>
       <c r="H3280" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3280" s="1">
         <v>3</v>
@@ -105647,30 +105647,30 @@
         <v>103</v>
       </c>
       <c r="D3281" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3281" t="s">
         <v>194</v>
       </c>
       <c r="F3281" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3281" s="1">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="H3281" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3281" s="1">
         <v>3</v>
       </c>
       <c r="J3281" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3282">
       <c r="A3282" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3282" t="s">
         <v>25</v>
@@ -105679,22 +105679,22 @@
         <v>103</v>
       </c>
       <c r="D3282" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E3282" t="s">
         <v>194</v>
       </c>
       <c r="F3282" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3282" s="1">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="H3282" s="1">
         <v>2</v>
       </c>
       <c r="I3282" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3282" s="1">
         <v>1</v>
@@ -105702,7 +105702,7 @@
     </row>
     <row r="3283">
       <c r="A3283" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3283" t="s">
         <v>25</v>
@@ -105711,7 +105711,7 @@
         <v>103</v>
       </c>
       <c r="D3283" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3283" t="s">
         <v>194</v>
@@ -105720,16 +105720,16 @@
         <v>198</v>
       </c>
       <c r="G3283" s="1">
-        <v>62.5</v>
+        <v>115</v>
       </c>
       <c r="H3283" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3283" s="1">
         <v>2</v>
       </c>
       <c r="J3283" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3284">
@@ -105743,22 +105743,22 @@
         <v>103</v>
       </c>
       <c r="D3284" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E3284" t="s">
         <v>194</v>
       </c>
       <c r="F3284" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3284" s="1">
-        <v>245</v>
+        <v>62.5</v>
       </c>
       <c r="H3284" s="1">
         <v>4</v>
       </c>
       <c r="I3284" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3284" s="1">
         <v>0</v>
@@ -105781,10 +105781,10 @@
         <v>194</v>
       </c>
       <c r="F3285" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3285" s="1">
-        <v>1000</v>
+        <v>245</v>
       </c>
       <c r="H3285" s="1">
         <v>4</v>
@@ -105798,28 +105798,28 @@
     </row>
     <row r="3286">
       <c r="A3286" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3286" t="s">
         <v>25</v>
       </c>
       <c r="C3286" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D3286" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3286" t="s">
         <v>194</v>
       </c>
       <c r="F3286" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3286" s="1">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="H3286" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3286" s="1">
         <v>3</v>
@@ -105845,13 +105845,13 @@
         <v>194</v>
       </c>
       <c r="F3287" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3287" s="1">
-        <v>610</v>
+        <v>320</v>
       </c>
       <c r="H3287" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3287" s="1">
         <v>3</v>
@@ -105877,24 +105877,24 @@
         <v>194</v>
       </c>
       <c r="F3288" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3288" s="1">
-        <v>757.5</v>
+        <v>610</v>
       </c>
       <c r="H3288" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3288" s="1">
         <v>3</v>
       </c>
       <c r="J3288" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3289">
       <c r="A3289" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3289" t="s">
         <v>25</v>
@@ -105909,24 +105909,24 @@
         <v>194</v>
       </c>
       <c r="F3289" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3289" s="1">
-        <v>100.42676715827429</v>
+        <v>757.5</v>
       </c>
       <c r="H3289" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3289" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3289" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3290">
       <c r="A3290" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3290" t="s">
         <v>25</v>
@@ -105935,7 +105935,7 @@
         <v>127</v>
       </c>
       <c r="D3290" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3290" t="s">
         <v>194</v>
@@ -105944,16 +105944,16 @@
         <v>198</v>
       </c>
       <c r="G3290" s="1">
-        <v>899.44960252179317</v>
+        <v>100.42676715827429</v>
       </c>
       <c r="H3290" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3290" s="1">
         <v>2</v>
       </c>
       <c r="J3290" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3291">
@@ -105973,10 +105973,10 @@
         <v>194</v>
       </c>
       <c r="F3291" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3291" s="1">
-        <v>1235.8088721629069</v>
+        <v>899.44960252179317</v>
       </c>
       <c r="H3291" s="1">
         <v>2</v>
@@ -105990,7 +105990,7 @@
     </row>
     <row r="3292">
       <c r="A3292" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B3292" t="s">
         <v>25</v>
@@ -105999,22 +105999,22 @@
         <v>127</v>
       </c>
       <c r="D3292" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E3292" t="s">
         <v>194</v>
       </c>
       <c r="F3292" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3292" s="1">
-        <v>500</v>
+        <v>1235.8088721629069</v>
       </c>
       <c r="H3292" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3292" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3292" s="1">
         <v>1</v>
@@ -106034,7 +106034,7 @@
         <v>151</v>
       </c>
       <c r="E3293" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3293" t="s">
         <v>198</v>
@@ -106054,7 +106054,7 @@
     </row>
     <row r="3294">
       <c r="A3294" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3294" t="s">
         <v>25</v>
@@ -106063,7 +106063,7 @@
         <v>127</v>
       </c>
       <c r="D3294" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="E3294" t="s">
         <v>195</v>
@@ -106072,10 +106072,10 @@
         <v>198</v>
       </c>
       <c r="G3294" s="1">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="H3294" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3294" s="1">
         <v>3</v>
@@ -106095,19 +106095,19 @@
         <v>127</v>
       </c>
       <c r="D3295" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3295" t="s">
         <v>195</v>
       </c>
       <c r="F3295" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3295" s="1">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="H3295" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3295" s="1">
         <v>3</v>
@@ -106133,10 +106133,10 @@
         <v>195</v>
       </c>
       <c r="F3296" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3296" s="1">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="H3296" s="1">
         <v>1</v>
@@ -106159,7 +106159,7 @@
         <v>127</v>
       </c>
       <c r="D3297" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3297" t="s">
         <v>195</v>
@@ -106168,7 +106168,7 @@
         <v>198</v>
       </c>
       <c r="G3297" s="1">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="H3297" s="1">
         <v>1</v>
@@ -106182,7 +106182,7 @@
     </row>
     <row r="3298">
       <c r="A3298" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3298" t="s">
         <v>25</v>
@@ -106191,7 +106191,7 @@
         <v>127</v>
       </c>
       <c r="D3298" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3298" t="s">
         <v>195</v>
@@ -106200,16 +106200,16 @@
         <v>198</v>
       </c>
       <c r="G3298" s="1">
-        <v>379.3140661960025</v>
+        <v>450</v>
       </c>
       <c r="H3298" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3298" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3298" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3299">
@@ -106223,7 +106223,7 @@
         <v>127</v>
       </c>
       <c r="D3299" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3299" t="s">
         <v>195</v>
@@ -106232,10 +106232,10 @@
         <v>198</v>
       </c>
       <c r="G3299" s="1">
-        <v>758.628132392005</v>
+        <v>379.3140661960025</v>
       </c>
       <c r="H3299" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3299" s="1">
         <v>2</v>
@@ -106246,7 +106246,7 @@
     </row>
     <row r="3300">
       <c r="A3300" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3300" t="s">
         <v>25</v>
@@ -106255,25 +106255,25 @@
         <v>127</v>
       </c>
       <c r="D3300" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3300" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3300" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3300" s="1">
-        <v>600</v>
+        <v>758.628132392005</v>
       </c>
       <c r="H3300" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3300" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3300" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3301">
@@ -106287,16 +106287,16 @@
         <v>127</v>
       </c>
       <c r="D3301" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3301" t="s">
         <v>194</v>
       </c>
       <c r="F3301" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3301" s="1">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="H3301" s="1">
         <v>1</v>
@@ -106319,16 +106319,16 @@
         <v>127</v>
       </c>
       <c r="D3302" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3302" t="s">
         <v>194</v>
       </c>
       <c r="F3302" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3302" s="1">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="H3302" s="1">
         <v>1</v>
@@ -106342,7 +106342,7 @@
     </row>
     <row r="3303">
       <c r="A3303" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3303" t="s">
         <v>25</v>
@@ -106351,22 +106351,22 @@
         <v>127</v>
       </c>
       <c r="D3303" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E3303" t="s">
         <v>194</v>
       </c>
       <c r="F3303" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3303" s="1">
-        <v>60.17454279119319</v>
+        <v>400</v>
       </c>
       <c r="H3303" s="1">
         <v>1</v>
       </c>
       <c r="I3303" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3303" s="1">
         <v>1</v>
@@ -106383,7 +106383,7 @@
         <v>127</v>
       </c>
       <c r="D3304" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3304" t="s">
         <v>194</v>
@@ -106392,16 +106392,16 @@
         <v>198</v>
       </c>
       <c r="G3304" s="1">
-        <v>250.72726162997162</v>
+        <v>60.17454279119319</v>
       </c>
       <c r="H3304" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3304" s="1">
         <v>2</v>
       </c>
       <c r="J3304" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3305">
@@ -106415,7 +106415,7 @@
         <v>127</v>
       </c>
       <c r="D3305" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E3305" t="s">
         <v>194</v>
@@ -106438,16 +106438,16 @@
     </row>
     <row r="3306">
       <c r="A3306" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3306" t="s">
         <v>25</v>
       </c>
       <c r="C3306" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D3306" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E3306" t="s">
         <v>194</v>
@@ -106456,10 +106456,10 @@
         <v>198</v>
       </c>
       <c r="G3306" s="1">
-        <v>425</v>
+        <v>250.72726162997162</v>
       </c>
       <c r="H3306" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3306" s="1">
         <v>2</v>
@@ -106470,7 +106470,7 @@
     </row>
     <row r="3307">
       <c r="A3307" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3307" t="s">
         <v>25</v>
@@ -106479,7 +106479,7 @@
         <v>128</v>
       </c>
       <c r="D3307" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E3307" t="s">
         <v>194</v>
@@ -106488,10 +106488,10 @@
         <v>198</v>
       </c>
       <c r="G3307" s="1">
-        <v>95</v>
+        <v>425</v>
       </c>
       <c r="H3307" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3307" s="1">
         <v>2</v>
@@ -106502,7 +106502,7 @@
     </row>
     <row r="3308">
       <c r="A3308" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3308" t="s">
         <v>25</v>
@@ -106511,22 +106511,22 @@
         <v>128</v>
       </c>
       <c r="D3308" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E3308" t="s">
         <v>194</v>
       </c>
       <c r="F3308" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3308" s="1">
-        <v>535</v>
+        <v>95</v>
       </c>
       <c r="H3308" s="1">
         <v>3</v>
       </c>
       <c r="I3308" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3308" s="1">
         <v>0</v>
@@ -106534,7 +106534,7 @@
     </row>
     <row r="3309">
       <c r="A3309" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3309" t="s">
         <v>25</v>
@@ -106543,22 +106543,22 @@
         <v>128</v>
       </c>
       <c r="D3309" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3309" t="s">
         <v>194</v>
       </c>
       <c r="F3309" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3309" s="1">
-        <v>137.5</v>
+        <v>535</v>
       </c>
       <c r="H3309" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3309" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3309" s="1">
         <v>0</v>
@@ -106566,7 +106566,7 @@
     </row>
     <row r="3310">
       <c r="A3310" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3310" t="s">
         <v>25</v>
@@ -106581,19 +106581,19 @@
         <v>194</v>
       </c>
       <c r="F3310" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3310" s="1">
-        <v>35</v>
+        <v>137.5</v>
       </c>
       <c r="H3310" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3310" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3310" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3311">
@@ -106613,13 +106613,13 @@
         <v>194</v>
       </c>
       <c r="F3311" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3311" s="1">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H3311" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3311" s="1">
         <v>3</v>
@@ -106642,16 +106642,16 @@
         <v>130</v>
       </c>
       <c r="E3312" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3312" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3312" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H3312" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3312" s="1">
         <v>3</v>
@@ -106671,7 +106671,7 @@
         <v>128</v>
       </c>
       <c r="D3313" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E3313" t="s">
         <v>195</v>
@@ -106680,7 +106680,7 @@
         <v>197</v>
       </c>
       <c r="G3313" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H3313" s="1">
         <v>1</v>
@@ -106694,7 +106694,7 @@
     </row>
     <row r="3314">
       <c r="A3314" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3314" t="s">
         <v>25</v>
@@ -106703,22 +106703,22 @@
         <v>128</v>
       </c>
       <c r="D3314" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E3314" t="s">
         <v>195</v>
       </c>
       <c r="F3314" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3314" s="1">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="H3314" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3314" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3314" s="1">
         <v>1</v>
@@ -106735,7 +106735,7 @@
         <v>128</v>
       </c>
       <c r="D3315" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3315" t="s">
         <v>195</v>
@@ -106744,7 +106744,7 @@
         <v>198</v>
       </c>
       <c r="G3315" s="1">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="H3315" s="1">
         <v>2</v>
@@ -106758,7 +106758,7 @@
     </row>
     <row r="3316">
       <c r="A3316" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3316" t="s">
         <v>25</v>
@@ -106767,22 +106767,22 @@
         <v>128</v>
       </c>
       <c r="D3316" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3316" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3316" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G3316" s="1">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="H3316" s="1">
         <v>2</v>
       </c>
       <c r="I3316" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3316" s="1">
         <v>1</v>
@@ -106799,25 +106799,25 @@
         <v>128</v>
       </c>
       <c r="D3317" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3317" t="s">
         <v>194</v>
       </c>
       <c r="F3317" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3317" s="1">
-        <v>480</v>
+        <v>650</v>
       </c>
       <c r="H3317" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3317" s="1">
         <v>3</v>
       </c>
       <c r="J3317" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3318">
@@ -106831,16 +106831,16 @@
         <v>128</v>
       </c>
       <c r="D3318" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3318" t="s">
         <v>194</v>
       </c>
       <c r="F3318" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3318" s="1">
-        <v>220</v>
+        <v>480</v>
       </c>
       <c r="H3318" s="1">
         <v>3</v>
@@ -106854,7 +106854,7 @@
     </row>
     <row r="3319">
       <c r="A3319" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B3319" t="s">
         <v>25</v>
@@ -106863,22 +106863,22 @@
         <v>128</v>
       </c>
       <c r="D3319" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E3319" t="s">
         <v>194</v>
       </c>
       <c r="F3319" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G3319" s="1">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="H3319" s="1">
         <v>3</v>
       </c>
       <c r="I3319" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3319" s="1">
         <v>0</v>
@@ -106886,7 +106886,7 @@
     </row>
     <row r="3320">
       <c r="A3320" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3320" t="s">
         <v>25</v>
@@ -106895,7 +106895,7 @@
         <v>128</v>
       </c>
       <c r="D3320" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E3320" t="s">
         <v>194</v>
@@ -106904,7 +106904,7 @@
         <v>198</v>
       </c>
       <c r="G3320" s="1">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="H3320" s="1">
         <v>3</v>
@@ -106918,7 +106918,7 @@
     </row>
     <row r="3321">
       <c r="A3321" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3321" t="s">
         <v>25</v>
@@ -106927,7 +106927,7 @@
         <v>128</v>
       </c>
       <c r="D3321" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E3321" t="s">
         <v>194</v>
@@ -106936,16 +106936,16 @@
         <v>198</v>
       </c>
       <c r="G3321" s="1">
-        <v>147.5</v>
+        <v>245</v>
       </c>
       <c r="H3321" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3321" s="1">
         <v>2</v>
       </c>
       <c r="J3321" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3322">
@@ -106959,24 +106959,56 @@
         <v>128</v>
       </c>
       <c r="D3322" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3322" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3322" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3322" s="1">
+        <v>160</v>
+      </c>
+      <c r="H3322" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3322" s="1">
+        <v>2</v>
+      </c>
+      <c r="J3322" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3323" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3323" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3323" t="s">
         <v>134</v>
       </c>
-      <c r="E3322" t="s">
-        <v>194</v>
-      </c>
-      <c r="F3322" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3322" s="1">
+      <c r="E3323" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3323" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3323" s="1">
         <v>285</v>
       </c>
-      <c r="H3322" s="1">
-        <v>1</v>
-      </c>
-      <c r="I3322" s="1">
-        <v>2</v>
-      </c>
-      <c r="J3322" s="1">
+      <c r="H3323" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3323" s="1">
+        <v>2</v>
+      </c>
+      <c r="J3323" s="1">
         <v>1</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -1336,7 +1336,7 @@
         <v>198</v>
       </c>
       <c r="G21" s="1">
-        <v>722.46638321679279</v>
+        <v>750</v>
       </c>
       <c r="H21" s="1">
         <v>4</v>
@@ -1528,7 +1528,7 @@
         <v>198</v>
       </c>
       <c r="G27" s="1">
-        <v>69.414035983033955</v>
+        <v>70</v>
       </c>
       <c r="H27" s="1">
         <v>3</v>
@@ -2360,7 +2360,7 @@
         <v>198</v>
       </c>
       <c r="G53" s="1">
-        <v>356.98647076988891</v>
+        <v>360</v>
       </c>
       <c r="H53" s="1">
         <v>1</v>
@@ -6552,7 +6552,7 @@
         <v>198</v>
       </c>
       <c r="G184" s="1">
-        <v>123.95363568398921</v>
+        <v>125</v>
       </c>
       <c r="H184" s="1">
         <v>2</v>
@@ -6584,7 +6584,7 @@
         <v>198</v>
       </c>
       <c r="G185" s="1">
-        <v>304.92594378261344</v>
+        <v>307.5</v>
       </c>
       <c r="H185" s="1">
         <v>6</v>
@@ -7288,7 +7288,7 @@
         <v>198</v>
       </c>
       <c r="G207" s="1">
-        <v>54.573957783625062</v>
+        <v>54</v>
       </c>
       <c r="H207" s="1">
         <v>4</v>
@@ -7640,7 +7640,7 @@
         <v>198</v>
       </c>
       <c r="G218" s="1">
-        <v>327.2375982057315</v>
+        <v>330</v>
       </c>
       <c r="H218" s="1">
         <v>6</v>
@@ -8504,7 +8504,7 @@
         <v>198</v>
       </c>
       <c r="G245" s="1">
-        <v>306.13972638918597</v>
+        <v>307.5</v>
       </c>
       <c r="H245" s="1">
         <v>8</v>
@@ -9400,7 +9400,7 @@
         <v>198</v>
       </c>
       <c r="G273" s="1">
-        <v>234.70701799151698</v>
+        <v>235</v>
       </c>
       <c r="H273" s="1">
         <v>2</v>
@@ -9464,7 +9464,7 @@
         <v>198</v>
       </c>
       <c r="G275" s="1">
-        <v>495.81454273595682</v>
+        <v>500</v>
       </c>
       <c r="H275" s="1">
         <v>7</v>
@@ -10456,7 +10456,7 @@
         <v>198</v>
       </c>
       <c r="G306" s="1">
-        <v>198.32581709438273</v>
+        <v>200</v>
       </c>
       <c r="H306" s="1">
         <v>3</v>
@@ -12888,7 +12888,7 @@
         <v>198</v>
       </c>
       <c r="G382" s="1">
-        <v>295.31234179003718</v>
+        <v>302.5</v>
       </c>
       <c r="H382" s="1">
         <v>4</v>
@@ -13336,7 +13336,7 @@
         <v>198</v>
       </c>
       <c r="G396" s="1">
-        <v>111.47881046271796</v>
+        <v>110</v>
       </c>
       <c r="H396" s="1">
         <v>4</v>
@@ -13720,7 +13720,7 @@
         <v>199</v>
       </c>
       <c r="G408" s="1">
-        <v>517.16375764568477</v>
+        <v>517.5</v>
       </c>
       <c r="H408" s="1">
         <v>6</v>
@@ -22424,7 +22424,7 @@
         <v>198</v>
       </c>
       <c r="G680" s="1">
-        <v>92.419871666265749</v>
+        <v>90</v>
       </c>
       <c r="H680" s="1">
         <v>3</v>
@@ -32088,7 +32088,7 @@
         <v>198</v>
       </c>
       <c r="G982" s="1">
-        <v>777.99938490630962</v>
+        <v>780</v>
       </c>
       <c r="H982" s="1">
         <v>1</v>
@@ -34712,7 +34712,7 @@
         <v>198</v>
       </c>
       <c r="G1064" s="1">
-        <v>149.25020029718445</v>
+        <v>145</v>
       </c>
       <c r="H1064" s="1">
         <v>1</v>
@@ -43992,7 +43992,7 @@
         <v>198</v>
       </c>
       <c r="G1354" s="1">
-        <v>31.014989527815743</v>
+        <v>31</v>
       </c>
       <c r="H1354" s="1">
         <v>1</v>
@@ -44024,7 +44024,7 @@
         <v>198</v>
       </c>
       <c r="G1355" s="1">
-        <v>300.14505994660397</v>
+        <v>300</v>
       </c>
       <c r="H1355" s="1">
         <v>1</v>
@@ -44472,7 +44472,7 @@
         <v>198</v>
       </c>
       <c r="G1369" s="1">
-        <v>377.14309350740183</v>
+        <v>375</v>
       </c>
       <c r="H1369" s="1">
         <v>1</v>
@@ -45592,7 +45592,7 @@
         <v>198</v>
       </c>
       <c r="G1404" s="1">
-        <v>152.02645652939546</v>
+        <v>135</v>
       </c>
       <c r="H1404" s="1">
         <v>1</v>
@@ -45720,7 +45720,7 @@
         <v>198</v>
       </c>
       <c r="G1408" s="1">
-        <v>143.67079949850094</v>
+        <v>140</v>
       </c>
       <c r="H1408" s="1">
         <v>2</v>
@@ -45816,7 +45816,7 @@
         <v>198</v>
       </c>
       <c r="G1411" s="1">
-        <v>122.98188905877497</v>
+        <v>130</v>
       </c>
       <c r="H1411" s="1">
         <v>1</v>
@@ -46104,7 +46104,7 @@
         <v>198</v>
       </c>
       <c r="G1420" s="1">
-        <v>615.79061890072751</v>
+        <v>620</v>
       </c>
       <c r="H1420" s="1">
         <v>1</v>
@@ -46712,7 +46712,7 @@
         <v>198</v>
       </c>
       <c r="G1439" s="1">
-        <v>259.25312414371018</v>
+        <v>250</v>
       </c>
       <c r="H1439" s="1">
         <v>1</v>
@@ -48408,7 +48408,7 @@
         <v>198</v>
       </c>
       <c r="G1492" s="1">
-        <v>326.57535106314578</v>
+        <v>290</v>
       </c>
       <c r="H1492" s="1">
         <v>5</v>
@@ -50200,7 +50200,7 @@
         <v>198</v>
       </c>
       <c r="G1548" s="1">
-        <v>441.63112318135489</v>
+        <v>445</v>
       </c>
       <c r="H1548" s="1">
         <v>3</v>
@@ -52344,7 +52344,7 @@
         <v>198</v>
       </c>
       <c r="G1615" s="1">
-        <v>155.33762567787119</v>
+        <v>175</v>
       </c>
       <c r="H1615" s="1">
         <v>3</v>
@@ -52984,7 +52984,7 @@
         <v>197</v>
       </c>
       <c r="G1635" s="1">
-        <v>304.11448044876499</v>
+        <v>305</v>
       </c>
       <c r="H1635" s="1">
         <v>2</v>
@@ -53016,7 +53016,7 @@
         <v>198</v>
       </c>
       <c r="G1636" s="1">
-        <v>593.27251103939398</v>
+        <v>595</v>
       </c>
       <c r="H1636" s="1">
         <v>2</v>
@@ -53048,7 +53048,7 @@
         <v>199</v>
       </c>
       <c r="G1637" s="1">
-        <v>889.90876655909096</v>
+        <v>892.5</v>
       </c>
       <c r="H1637" s="1">
         <v>2</v>
@@ -53432,7 +53432,7 @@
         <v>198</v>
       </c>
       <c r="G1649" s="1">
-        <v>290.36349904095539</v>
+        <v>280</v>
       </c>
       <c r="H1649" s="1">
         <v>3</v>
@@ -53880,7 +53880,7 @@
         <v>198</v>
       </c>
       <c r="G1663" s="1">
-        <v>121.98856987777854</v>
+        <v>110</v>
       </c>
       <c r="H1663" s="1">
         <v>3</v>
@@ -54712,7 +54712,7 @@
         <v>198</v>
       </c>
       <c r="G1689" s="1">
-        <v>195.37770223384973</v>
+        <v>197.5</v>
       </c>
       <c r="H1689" s="1">
         <v>2</v>
@@ -54744,7 +54744,7 @@
         <v>199</v>
       </c>
       <c r="G1690" s="1">
-        <v>257.20608901671358</v>
+        <v>260</v>
       </c>
       <c r="H1690" s="1">
         <v>2</v>
@@ -58520,7 +58520,7 @@
         <v>198</v>
       </c>
       <c r="G1808" s="1">
-        <v>266.75417567629307</v>
+        <v>272.5</v>
       </c>
       <c r="H1808" s="1">
         <v>4</v>
@@ -60920,7 +60920,7 @@
         <v>198</v>
       </c>
       <c r="G1883" s="1">
-        <v>481.0876038880869</v>
+        <v>487.5</v>
       </c>
       <c r="H1883" s="1">
         <v>2</v>
@@ -67576,7 +67576,7 @@
         <v>198</v>
       </c>
       <c r="G2091" s="1">
-        <v>2044.4047500080699</v>
+        <v>2060</v>
       </c>
       <c r="H2091" s="1">
         <v>1</v>
@@ -69112,7 +69112,7 @@
         <v>198</v>
       </c>
       <c r="G2139" s="1">
-        <v>915.28496975168446</v>
+        <v>935</v>
       </c>
       <c r="H2139" s="1">
         <v>3</v>
@@ -81624,7 +81624,7 @@
         <v>198</v>
       </c>
       <c r="G2530" s="1">
-        <v>213.37234041346361</v>
+        <v>215</v>
       </c>
       <c r="H2530" s="1">
         <v>7</v>
@@ -83832,7 +83832,7 @@
         <v>198</v>
       </c>
       <c r="G2599" s="1">
-        <v>129.50401852504058</v>
+        <v>115</v>
       </c>
       <c r="H2599" s="1">
         <v>3</v>
@@ -86040,7 +86040,7 @@
         <v>198</v>
       </c>
       <c r="G2668" s="1">
-        <v>106.98158052068568</v>
+        <v>95</v>
       </c>
       <c r="H2668" s="1">
         <v>3</v>
@@ -88280,7 +88280,7 @@
         <v>197</v>
       </c>
       <c r="G2738" s="1">
-        <v>281.53047505443601</v>
+        <v>250</v>
       </c>
       <c r="H2738" s="1">
         <v>5</v>
@@ -88312,7 +88312,7 @@
         <v>198</v>
       </c>
       <c r="G2739" s="1">
-        <v>624.99765462084792</v>
+        <v>555</v>
       </c>
       <c r="H2739" s="1">
         <v>5</v>
@@ -88344,7 +88344,7 @@
         <v>199</v>
       </c>
       <c r="G2740" s="1">
-        <v>838.96081566221938</v>
+        <v>745</v>
       </c>
       <c r="H2740" s="1">
         <v>4</v>
@@ -88536,7 +88536,7 @@
         <v>198</v>
       </c>
       <c r="G2746" s="1">
-        <v>141.39584235833422</v>
+        <v>127.5</v>
       </c>
       <c r="H2746" s="1">
         <v>4</v>
@@ -88824,7 +88824,7 @@
         <v>198</v>
       </c>
       <c r="G2755" s="1">
-        <v>528.46122832080471</v>
+        <v>530</v>
       </c>
       <c r="H2755" s="1">
         <v>7</v>
@@ -88856,7 +88856,7 @@
         <v>198</v>
       </c>
       <c r="G2756" s="1">
-        <v>164.52094843949581</v>
+        <v>165</v>
       </c>
       <c r="H2756" s="1">
         <v>7</v>
@@ -88888,7 +88888,7 @@
         <v>199</v>
       </c>
       <c r="G2757" s="1">
-        <v>403.82414616967151</v>
+        <v>405</v>
       </c>
       <c r="H2757" s="1">
         <v>7</v>
@@ -89784,7 +89784,7 @@
         <v>198</v>
       </c>
       <c r="G2785" s="1">
-        <v>98.535666269052598</v>
+        <v>87.5</v>
       </c>
       <c r="H2785" s="1">
         <v>2</v>
@@ -89816,7 +89816,7 @@
         <v>198</v>
       </c>
       <c r="G2786" s="1">
-        <v>416.6651030805653</v>
+        <v>370</v>
       </c>
       <c r="H2786" s="1">
         <v>7</v>
@@ -89848,7 +89848,7 @@
         <v>198</v>
       </c>
       <c r="G2787" s="1">
-        <v>73.197923514153359</v>
+        <v>65</v>
       </c>
       <c r="H2787" s="1">
         <v>1</v>
@@ -89880,7 +89880,7 @@
         <v>198</v>
       </c>
       <c r="G2788" s="1">
-        <v>123.14639957014366</v>
+        <v>120</v>
       </c>
       <c r="H2788" s="1">
         <v>5</v>
@@ -89912,7 +89912,7 @@
         <v>198</v>
       </c>
       <c r="G2789" s="1">
-        <v>192.41624932834947</v>
+        <v>187.5</v>
       </c>
       <c r="H2789" s="1">
         <v>6</v>
@@ -89944,7 +89944,7 @@
         <v>198</v>
       </c>
       <c r="G2790" s="1">
-        <v>163.28767553157289</v>
+        <v>145</v>
       </c>
       <c r="H2790" s="1">
         <v>9</v>
@@ -89976,7 +89976,7 @@
         <v>198</v>
       </c>
       <c r="G2791" s="1">
-        <v>216.77846579191572</v>
+        <v>192.5</v>
       </c>
       <c r="H2791" s="1">
         <v>8</v>
@@ -90104,7 +90104,7 @@
         <v>198</v>
       </c>
       <c r="G2795" s="1">
-        <v>94.263894905556143</v>
+        <v>85</v>
       </c>
       <c r="H2795" s="1">
         <v>3</v>
@@ -90232,7 +90232,7 @@
         <v>198</v>
       </c>
       <c r="G2799" s="1">
-        <v>655.87265212152784</v>
+        <v>670</v>
       </c>
       <c r="H2799" s="1">
         <v>4</v>
@@ -90264,7 +90264,7 @@
         <v>198</v>
       </c>
       <c r="G2800" s="1">
-        <v>119.91701475356294</v>
+        <v>122.5</v>
       </c>
       <c r="H2800" s="1">
         <v>2</v>
@@ -90680,7 +90680,7 @@
         <v>197</v>
       </c>
       <c r="G2813" s="1">
-        <v>104.69514900695188</v>
+        <v>105</v>
       </c>
       <c r="H2813" s="1">
         <v>3</v>
@@ -90712,7 +90712,7 @@
         <v>198</v>
       </c>
       <c r="G2814" s="1">
-        <v>294.14351387667432</v>
+        <v>295</v>
       </c>
       <c r="H2814" s="1">
         <v>3</v>
@@ -90744,7 +90744,7 @@
         <v>199</v>
       </c>
       <c r="G2815" s="1">
-        <v>423.76607931385286</v>
+        <v>425</v>
       </c>
       <c r="H2815" s="1">
         <v>3</v>
@@ -91576,7 +91576,7 @@
         <v>198</v>
       </c>
       <c r="G2841" s="1">
-        <v>139.99668703760349</v>
+        <v>135</v>
       </c>
       <c r="H2841" s="1">
         <v>3</v>
@@ -91992,7 +91992,7 @@
         <v>198</v>
       </c>
       <c r="G2854" s="1">
-        <v>247.7468180479037</v>
+        <v>220</v>
       </c>
       <c r="H2854" s="1">
         <v>3</v>
@@ -92984,7 +92984,7 @@
         <v>198</v>
       </c>
       <c r="G2885" s="1">
-        <v>194.25602778756084</v>
+        <v>172.5</v>
       </c>
       <c r="H2885" s="1">
         <v>4</v>
@@ -93016,7 +93016,7 @@
         <v>198</v>
       </c>
       <c r="G2886" s="1">
-        <v>127.53350487222302</v>
+        <v>115</v>
       </c>
       <c r="H2886" s="1">
         <v>5</v>
@@ -93144,7 +93144,7 @@
         <v>198</v>
       </c>
       <c r="G2890" s="1">
-        <v>48.945720307576707</v>
+        <v>50</v>
       </c>
       <c r="H2890" s="1">
         <v>4</v>
@@ -93496,7 +93496,7 @@
         <v>198</v>
       </c>
       <c r="G2901" s="1">
-        <v>186.66224938347131</v>
+        <v>180</v>
       </c>
       <c r="H2901" s="1">
         <v>4</v>
@@ -94232,7 +94232,7 @@
         <v>198</v>
       </c>
       <c r="G2924" s="1">
-        <v>491.88822671326102</v>
+        <v>495</v>
       </c>
       <c r="H2924" s="1">
         <v>6</v>
@@ -94296,7 +94296,7 @@
         <v>198</v>
       </c>
       <c r="G2926" s="1">
-        <v>81.297859128126802</v>
+        <v>85</v>
       </c>
       <c r="H2926" s="1">
         <v>6</v>
@@ -94328,7 +94328,7 @@
         <v>198</v>
       </c>
       <c r="G2927" s="1">
-        <v>1146.1130669252766</v>
+        <v>1150</v>
       </c>
       <c r="H2927" s="1">
         <v>3</v>
@@ -94456,7 +94456,7 @@
         <v>198</v>
       </c>
       <c r="G2931" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H2931" s="1">
         <v>5</v>
@@ -94488,7 +94488,7 @@
         <v>198</v>
       </c>
       <c r="G2932" s="1">
-        <v>758.628132392005</v>
+        <v>750</v>
       </c>
       <c r="H2932" s="1">
         <v>5</v>
@@ -94584,7 +94584,7 @@
         <v>198</v>
       </c>
       <c r="G2935" s="1">
-        <v>303.03513397062204</v>
+        <v>300</v>
       </c>
       <c r="H2935" s="1">
         <v>4</v>
@@ -94616,7 +94616,7 @@
         <v>198</v>
       </c>
       <c r="G2936" s="1">
-        <v>65.189088023792621</v>
+        <v>65</v>
       </c>
       <c r="H2936" s="1">
         <v>1</v>
@@ -94648,7 +94648,7 @@
         <v>198</v>
       </c>
       <c r="G2937" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H2937" s="1">
         <v>3</v>
@@ -94680,7 +94680,7 @@
         <v>198</v>
       </c>
       <c r="G2938" s="1">
-        <v>596.22815359183153</v>
+        <v>600</v>
       </c>
       <c r="H2938" s="1">
         <v>3</v>
@@ -94712,7 +94712,7 @@
         <v>198</v>
       </c>
       <c r="G2939" s="1">
-        <v>144.08847045135929</v>
+        <v>145</v>
       </c>
       <c r="H2939" s="1">
         <v>1</v>
@@ -94744,7 +94744,7 @@
         <v>198</v>
       </c>
       <c r="G2940" s="1">
-        <v>95.644540150737413</v>
+        <v>100</v>
       </c>
       <c r="H2940" s="1">
         <v>3</v>
@@ -94776,7 +94776,7 @@
         <v>198</v>
       </c>
       <c r="G2941" s="1">
-        <v>1076.3496628515641</v>
+        <v>1080</v>
       </c>
       <c r="H2941" s="1">
         <v>1</v>
@@ -94808,7 +94808,7 @@
         <v>199</v>
       </c>
       <c r="G2942" s="1">
-        <v>1385.3018808922907</v>
+        <v>1390</v>
       </c>
       <c r="H2942" s="1">
         <v>1</v>
@@ -94840,7 +94840,7 @@
         <v>198</v>
       </c>
       <c r="G2943" s="1">
-        <v>1121.1975654703792</v>
+        <v>1125</v>
       </c>
       <c r="H2943" s="1">
         <v>1</v>
@@ -94872,7 +94872,7 @@
         <v>199</v>
       </c>
       <c r="G2944" s="1">
-        <v>1415.2004826381676</v>
+        <v>1420</v>
       </c>
       <c r="H2944" s="1">
         <v>1</v>
@@ -94936,7 +94936,7 @@
         <v>198</v>
       </c>
       <c r="G2946" s="1">
-        <v>454.57282704464313</v>
+        <v>460</v>
       </c>
       <c r="H2946" s="1">
         <v>1</v>
@@ -95064,7 +95064,7 @@
         <v>198</v>
       </c>
       <c r="G2950" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H2950" s="1">
         <v>4</v>
@@ -95224,7 +95224,7 @@
         <v>198</v>
       </c>
       <c r="G2955" s="1">
-        <v>212.71856654960359</v>
+        <v>210</v>
       </c>
       <c r="H2955" s="1">
         <v>1</v>
@@ -95256,7 +95256,7 @@
         <v>198</v>
       </c>
       <c r="G2956" s="1">
-        <v>62.681815407492905</v>
+        <v>62.5</v>
       </c>
       <c r="H2956" s="1">
         <v>2</v>
@@ -95288,7 +95288,7 @@
         <v>198</v>
       </c>
       <c r="G2957" s="1">
-        <v>215.62544500177558</v>
+        <v>215</v>
       </c>
       <c r="H2957" s="1">
         <v>2</v>
@@ -95320,7 +95320,7 @@
         <v>199</v>
       </c>
       <c r="G2958" s="1">
-        <v>264.76798828125004</v>
+        <v>264</v>
       </c>
       <c r="H2958" s="1">
         <v>2</v>
@@ -95352,7 +95352,7 @@
         <v>198</v>
       </c>
       <c r="G2959" s="1">
-        <v>700.56808047040204</v>
+        <v>705</v>
       </c>
       <c r="H2959" s="1">
         <v>3</v>
@@ -95384,7 +95384,7 @@
         <v>198</v>
       </c>
       <c r="G2960" s="1">
-        <v>151.28092551583831</v>
+        <v>150</v>
       </c>
       <c r="H2960" s="1">
         <v>2</v>
@@ -95512,7 +95512,7 @@
         <v>198</v>
       </c>
       <c r="G2964" s="1">
-        <v>133.90235621103238</v>
+        <v>140</v>
       </c>
       <c r="H2964" s="1">
         <v>3</v>
@@ -95544,7 +95544,7 @@
         <v>198</v>
       </c>
       <c r="G2965" s="1">
-        <v>1357.8948292919035</v>
+        <v>1362.5</v>
       </c>
       <c r="H2965" s="1">
         <v>2</v>
@@ -95576,7 +95576,7 @@
         <v>197</v>
       </c>
       <c r="G2966" s="1">
-        <v>859.58480019395734</v>
+        <v>862.5</v>
       </c>
       <c r="H2966" s="1">
         <v>2</v>
@@ -95608,7 +95608,7 @@
         <v>198</v>
       </c>
       <c r="G2967" s="1">
-        <v>1098.7736141609717</v>
+        <v>1102.5</v>
       </c>
       <c r="H2967" s="1">
         <v>2</v>
@@ -95640,7 +95640,7 @@
         <v>199</v>
       </c>
       <c r="G2968" s="1">
-        <v>1355.4032791464138</v>
+        <v>1360</v>
       </c>
       <c r="H2968" s="1">
         <v>2</v>
@@ -95800,7 +95800,7 @@
         <v>198</v>
       </c>
       <c r="G2973" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H2973" s="1">
         <v>5</v>
@@ -95832,7 +95832,7 @@
         <v>198</v>
       </c>
       <c r="G2974" s="1">
-        <v>758.628132392005</v>
+        <v>750</v>
       </c>
       <c r="H2974" s="1">
         <v>5</v>
@@ -95960,7 +95960,7 @@
         <v>198</v>
       </c>
       <c r="G2978" s="1">
-        <v>263.36584429950921</v>
+        <v>260</v>
       </c>
       <c r="H2978" s="1">
         <v>3</v>
@@ -95992,7 +95992,7 @@
         <v>198</v>
       </c>
       <c r="G2979" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H2979" s="1">
         <v>4</v>
@@ -96792,7 +96792,7 @@
         <v>198</v>
       </c>
       <c r="G3004" s="1">
-        <v>150.43635697798297</v>
+        <v>150</v>
       </c>
       <c r="H3004" s="1">
         <v>5</v>
@@ -97816,7 +97816,7 @@
         <v>198</v>
       </c>
       <c r="G3036" s="1">
-        <v>100.42676715827429</v>
+        <v>105</v>
       </c>
       <c r="H3036" s="1">
         <v>3</v>
@@ -97848,7 +97848,7 @@
         <v>197</v>
       </c>
       <c r="G3037" s="1">
-        <v>906.92425295826229</v>
+        <v>910</v>
       </c>
       <c r="H3037" s="1">
         <v>1</v>
@@ -97880,7 +97880,7 @@
         <v>198</v>
       </c>
       <c r="G3038" s="1">
-        <v>1048.9426112511769</v>
+        <v>1052.5</v>
       </c>
       <c r="H3038" s="1">
         <v>2</v>
@@ -97912,7 +97912,7 @@
         <v>199</v>
       </c>
       <c r="G3039" s="1">
-        <v>1131.1637660523381</v>
+        <v>1135</v>
       </c>
       <c r="H3039" s="1">
         <v>1</v>
@@ -98168,7 +98168,7 @@
         <v>198</v>
       </c>
       <c r="G3047" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H3047" s="1">
         <v>2</v>
@@ -98200,7 +98200,7 @@
         <v>198</v>
       </c>
       <c r="G3048" s="1">
-        <v>758.628132392005</v>
+        <v>750</v>
       </c>
       <c r="H3048" s="1">
         <v>2</v>
@@ -98328,7 +98328,7 @@
         <v>198</v>
       </c>
       <c r="G3052" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H3052" s="1">
         <v>1</v>
@@ -98360,7 +98360,7 @@
         <v>198</v>
       </c>
       <c r="G3053" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H3053" s="1">
         <v>4</v>
@@ -99672,7 +99672,7 @@
         <v>198</v>
       </c>
       <c r="G3094" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H3094" s="1">
         <v>3</v>
@@ -99704,7 +99704,7 @@
         <v>198</v>
       </c>
       <c r="G3095" s="1">
-        <v>758.628132392005</v>
+        <v>750</v>
       </c>
       <c r="H3095" s="1">
         <v>4</v>
@@ -102136,7 +102136,7 @@
         <v>198</v>
       </c>
       <c r="G3171" s="1">
-        <v>250.36363081498581</v>
+        <v>250</v>
       </c>
       <c r="H3171" s="1">
         <v>2</v>
@@ -104536,7 +104536,7 @@
         <v>198</v>
       </c>
       <c r="G3246" s="1">
-        <v>76.515632120589927</v>
+        <v>80</v>
       </c>
       <c r="H3246" s="1">
         <v>4</v>
@@ -104568,7 +104568,7 @@
         <v>197</v>
       </c>
       <c r="G3247" s="1">
-        <v>946.78905528609801</v>
+        <v>950</v>
       </c>
       <c r="H3247" s="1">
         <v>1</v>
@@ -104600,7 +104600,7 @@
         <v>198</v>
       </c>
       <c r="G3248" s="1">
-        <v>981.67075732295427</v>
+        <v>985</v>
       </c>
       <c r="H3248" s="1">
         <v>1</v>
@@ -104696,7 +104696,7 @@
         <v>198</v>
       </c>
       <c r="G3251" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H3251" s="1">
         <v>1</v>
@@ -104824,7 +104824,7 @@
         <v>198</v>
       </c>
       <c r="G3255" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H3255" s="1">
         <v>2</v>
@@ -104856,7 +104856,7 @@
         <v>198</v>
       </c>
       <c r="G3256" s="1">
-        <v>175.50908314098012</v>
+        <v>175</v>
       </c>
       <c r="H3256" s="1">
         <v>1</v>
@@ -104888,7 +104888,7 @@
         <v>198</v>
       </c>
       <c r="G3257" s="1">
-        <v>215.62544500177558</v>
+        <v>215</v>
       </c>
       <c r="H3257" s="1">
         <v>2</v>
@@ -105944,7 +105944,7 @@
         <v>198</v>
       </c>
       <c r="G3290" s="1">
-        <v>100.42676715827429</v>
+        <v>105</v>
       </c>
       <c r="H3290" s="1">
         <v>3</v>
@@ -105976,7 +105976,7 @@
         <v>198</v>
       </c>
       <c r="G3291" s="1">
-        <v>899.44960252179317</v>
+        <v>902.5</v>
       </c>
       <c r="H3291" s="1">
         <v>2</v>
@@ -106008,7 +106008,7 @@
         <v>199</v>
       </c>
       <c r="G3292" s="1">
-        <v>1235.8088721629069</v>
+        <v>1240</v>
       </c>
       <c r="H3292" s="1">
         <v>2</v>
@@ -106232,7 +106232,7 @@
         <v>198</v>
       </c>
       <c r="G3299" s="1">
-        <v>379.3140661960025</v>
+        <v>375</v>
       </c>
       <c r="H3299" s="1">
         <v>4</v>
@@ -106264,7 +106264,7 @@
         <v>198</v>
       </c>
       <c r="G3300" s="1">
-        <v>758.628132392005</v>
+        <v>750</v>
       </c>
       <c r="H3300" s="1">
         <v>5</v>
@@ -106392,7 +106392,7 @@
         <v>198</v>
       </c>
       <c r="G3304" s="1">
-        <v>60.17454279119319</v>
+        <v>60</v>
       </c>
       <c r="H3304" s="1">
         <v>1</v>
@@ -106424,7 +106424,7 @@
         <v>198</v>
       </c>
       <c r="G3305" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H3305" s="1">
         <v>4</v>
@@ -106456,7 +106456,7 @@
         <v>198</v>
       </c>
       <c r="G3306" s="1">
-        <v>250.72726162997162</v>
+        <v>250</v>
       </c>
       <c r="H3306" s="1">
         <v>4</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -4251,7 +4251,7 @@
         <v>194</v>
       </c>
       <c r="F112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G112" s="1">
         <v>375</v>
@@ -14747,7 +14747,7 @@
         <v>193</v>
       </c>
       <c r="F440" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G440" s="1">
         <v>250</v>
@@ -35259,7 +35259,7 @@
         <v>193</v>
       </c>
       <c r="F1081" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1081" s="1">
         <v>48</v>
@@ -38267,7 +38267,7 @@
         <v>193</v>
       </c>
       <c r="F1175" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1175" s="1">
         <v>250</v>
@@ -42267,7 +42267,7 @@
         <v>194</v>
       </c>
       <c r="F1300" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1300" s="1">
         <v>375</v>
@@ -47739,7 +47739,7 @@
         <v>193</v>
       </c>
       <c r="F1471" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1471" s="1">
         <v>85</v>
@@ -47803,7 +47803,7 @@
         <v>194</v>
       </c>
       <c r="F1473" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1473" s="1">
         <v>60</v>
@@ -52059,7 +52059,7 @@
         <v>194</v>
       </c>
       <c r="F1606" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1606" s="1">
         <v>375</v>
@@ -59323,7 +59323,7 @@
         <v>194</v>
       </c>
       <c r="F1833" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1833" s="1">
         <v>375</v>
@@ -60731,7 +60731,7 @@
         <v>194</v>
       </c>
       <c r="F1877" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1877" s="1">
         <v>375</v>
@@ -63163,7 +63163,7 @@
         <v>194</v>
       </c>
       <c r="F1953" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1953" s="1">
         <v>110</v>
@@ -63355,7 +63355,7 @@
         <v>194</v>
       </c>
       <c r="F1959" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1959" s="1">
         <v>375</v>
@@ -68059,7 +68059,7 @@
         <v>194</v>
       </c>
       <c r="F2106" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2106" s="1">
         <v>355</v>
@@ -69531,7 +69531,7 @@
         <v>194</v>
       </c>
       <c r="F2152" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2152" s="1">
         <v>375</v>
@@ -69563,7 +69563,7 @@
         <v>194</v>
       </c>
       <c r="F2153" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2153" s="1">
         <v>750</v>
@@ -73819,7 +73819,7 @@
         <v>194</v>
       </c>
       <c r="F2286" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2286" s="1">
         <v>375</v>
@@ -77147,7 +77147,7 @@
         <v>194</v>
       </c>
       <c r="F2390" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2390" s="1">
         <v>375</v>
@@ -77179,7 +77179,7 @@
         <v>194</v>
       </c>
       <c r="F2391" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2391" s="1">
         <v>750</v>
@@ -78203,7 +78203,7 @@
         <v>194</v>
       </c>
       <c r="F2423" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2423" s="1">
         <v>375</v>
@@ -79739,7 +79739,7 @@
         <v>194</v>
       </c>
       <c r="F2471" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2471" s="1">
         <v>375</v>
@@ -81019,7 +81019,7 @@
         <v>193</v>
       </c>
       <c r="F2511" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2511" s="1">
         <v>110</v>
@@ -84731,7 +84731,7 @@
         <v>194</v>
       </c>
       <c r="F2627" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2627" s="1">
         <v>375</v>
@@ -85083,7 +85083,7 @@
         <v>193</v>
       </c>
       <c r="F2638" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2638" s="1">
         <v>250</v>
@@ -92123,7 +92123,7 @@
         <v>194</v>
       </c>
       <c r="F2858" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2858" s="1">
         <v>355</v>
@@ -93595,7 +93595,7 @@
         <v>193</v>
       </c>
       <c r="F2904" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2904" s="1">
         <v>250</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -56940,7 +56940,7 @@
         <v>190</v>
       </c>
       <c r="G1759" s="1">
-        <v>77.5</v>
+        <v>90</v>
       </c>
       <c r="H1759" s="1">
         <v>6</v>
@@ -56972,7 +56972,7 @@
         <v>191</v>
       </c>
       <c r="G1760" s="1">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H1760" s="1">
         <v>5</v>
@@ -57068,7 +57068,7 @@
         <v>191</v>
       </c>
       <c r="G1763" s="1">
-        <v>237.5</v>
+        <v>217.5</v>
       </c>
       <c r="H1763" s="1">
         <v>4</v>
@@ -57132,7 +57132,7 @@
         <v>192</v>
       </c>
       <c r="G1765" s="1">
-        <v>590</v>
+        <v>775</v>
       </c>
       <c r="H1765" s="1">
         <v>2</v>
@@ -85004,10 +85004,10 @@
         <v>190</v>
       </c>
       <c r="G2636" s="1">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="H2636" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2636" t="s">
         <v>197</v>
@@ -85036,16 +85036,16 @@
         <v>191</v>
       </c>
       <c r="G2637" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H2637" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2637" t="s">
         <v>197</v>
       </c>
       <c r="J2637" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2638">
@@ -85132,10 +85132,10 @@
         <v>190</v>
       </c>
       <c r="G2640" s="1">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="H2640" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2640" t="s">
         <v>197</v>
@@ -85164,16 +85164,16 @@
         <v>191</v>
       </c>
       <c r="G2641" s="1">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="H2641" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2641" t="s">
         <v>197</v>
       </c>
       <c r="J2641" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2642">
@@ -85196,7 +85196,7 @@
         <v>192</v>
       </c>
       <c r="G2642" s="1">
-        <v>720</v>
+        <v>745</v>
       </c>
       <c r="H2642" s="1">
         <v>2</v>
@@ -102124,7 +102124,7 @@
         <v>191</v>
       </c>
       <c r="G3171" s="1">
-        <v>167.5</v>
+        <v>140</v>
       </c>
       <c r="H3171" s="1">
         <v>4</v>
@@ -102156,7 +102156,7 @@
         <v>192</v>
       </c>
       <c r="G3172" s="1">
-        <v>397.5</v>
+        <v>277.5</v>
       </c>
       <c r="H3172" s="1">
         <v>2</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -5100,7 +5100,7 @@
         <v>190</v>
       </c>
       <c r="G139" s="1">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H139" s="1">
         <v>5</v>
@@ -5132,7 +5132,7 @@
         <v>191</v>
       </c>
       <c r="G140" s="1">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H140" s="1">
         <v>5</v>
@@ -5164,7 +5164,7 @@
         <v>192</v>
       </c>
       <c r="G141" s="1">
-        <v>552.5</v>
+        <v>475</v>
       </c>
       <c r="H141" s="1">
         <v>4</v>
@@ -7116,7 +7116,7 @@
         <v>190</v>
       </c>
       <c r="G202" s="1">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="H202" s="1">
         <v>4</v>
@@ -7148,7 +7148,7 @@
         <v>191</v>
       </c>
       <c r="G203" s="1">
-        <v>510</v>
+        <v>475</v>
       </c>
       <c r="H203" s="1">
         <v>5</v>
@@ -8620,7 +8620,7 @@
         <v>190</v>
       </c>
       <c r="G249" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H249" s="1">
         <v>7</v>
@@ -8652,7 +8652,7 @@
         <v>191</v>
       </c>
       <c r="G250" s="1">
-        <v>165</v>
+        <v>182.5</v>
       </c>
       <c r="H250" s="1">
         <v>6</v>
@@ -8684,7 +8684,7 @@
         <v>192</v>
       </c>
       <c r="G251" s="1">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="H251" s="1">
         <v>6</v>
@@ -8716,7 +8716,7 @@
         <v>193</v>
       </c>
       <c r="G252" s="1">
-        <v>242.5</v>
+        <v>252.5</v>
       </c>
       <c r="H252" s="1">
         <v>6</v>
@@ -13708,7 +13708,7 @@
         <v>192</v>
       </c>
       <c r="G408" s="1">
-        <v>435</v>
+        <v>517.5</v>
       </c>
       <c r="H408" s="1">
         <v>6</v>
@@ -16588,7 +16588,7 @@
         <v>193</v>
       </c>
       <c r="G498" s="1">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="H498" s="1">
         <v>9</v>
@@ -17260,7 +17260,7 @@
         <v>190</v>
       </c>
       <c r="G519" s="1">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="H519" s="1">
         <v>8</v>
@@ -17292,7 +17292,7 @@
         <v>191</v>
       </c>
       <c r="G520" s="1">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H520" s="1">
         <v>9</v>
@@ -17324,7 +17324,7 @@
         <v>192</v>
       </c>
       <c r="G521" s="1">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="H521" s="1">
         <v>7</v>
@@ -17580,7 +17580,7 @@
         <v>191</v>
       </c>
       <c r="G529" s="1">
-        <v>140</v>
+        <v>1400</v>
       </c>
       <c r="H529" s="1">
         <v>1</v>
@@ -20844,7 +20844,7 @@
         <v>190</v>
       </c>
       <c r="G631" s="1">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="H631" s="1">
         <v>5</v>
@@ -20908,7 +20908,7 @@
         <v>192</v>
       </c>
       <c r="G633" s="1">
-        <v>310</v>
+        <v>342.5</v>
       </c>
       <c r="H633" s="1">
         <v>4</v>
@@ -22220,7 +22220,7 @@
         <v>193</v>
       </c>
       <c r="G674" s="1">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="H674" s="1">
         <v>9</v>
@@ -23788,7 +23788,7 @@
         <v>192</v>
       </c>
       <c r="G723" s="1">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="H723" s="1">
         <v>4</v>
@@ -34956,7 +34956,7 @@
         <v>191</v>
       </c>
       <c r="G1072" s="1">
-        <v>620.5</v>
+        <v>1165</v>
       </c>
       <c r="H1072" s="1">
         <v>2</v>
@@ -34988,7 +34988,7 @@
         <v>192</v>
       </c>
       <c r="G1073" s="1">
-        <v>1347.5</v>
+        <v>1597.5</v>
       </c>
       <c r="H1073" s="1">
         <v>2</v>
@@ -35116,7 +35116,7 @@
         <v>191</v>
       </c>
       <c r="G1077" s="1">
-        <v>140</v>
+        <v>1400</v>
       </c>
       <c r="H1077" s="1">
         <v>3</v>
@@ -35148,7 +35148,7 @@
         <v>192</v>
       </c>
       <c r="G1078" s="1">
-        <v>185</v>
+        <v>1850</v>
       </c>
       <c r="H1078" s="1">
         <v>2</v>
@@ -35692,7 +35692,7 @@
         <v>191</v>
       </c>
       <c r="G1095" s="1">
-        <v>150</v>
+        <v>1505</v>
       </c>
       <c r="H1095" s="1">
         <v>1</v>
@@ -36236,7 +36236,7 @@
         <v>191</v>
       </c>
       <c r="G1112" s="1">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="H1112" s="1">
         <v>1</v>
@@ -40108,7 +40108,7 @@
         <v>190</v>
       </c>
       <c r="G1233" s="1">
-        <v>280</v>
+        <v>32</v>
       </c>
       <c r="H1233" s="1">
         <v>5</v>
@@ -46028,7 +46028,7 @@
         <v>190</v>
       </c>
       <c r="G1418" s="1">
-        <v>180.5</v>
+        <v>412.5</v>
       </c>
       <c r="H1418" s="1">
         <v>2</v>
@@ -46060,7 +46060,7 @@
         <v>191</v>
       </c>
       <c r="G1419" s="1">
-        <v>560</v>
+        <v>695</v>
       </c>
       <c r="H1419" s="1">
         <v>3</v>
@@ -46092,7 +46092,7 @@
         <v>192</v>
       </c>
       <c r="G1420" s="1">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="H1420" s="1">
         <v>1</v>
@@ -47372,10 +47372,10 @@
         <v>190</v>
       </c>
       <c r="G1460" s="1">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="H1460" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1460" t="s">
         <v>197</v>
@@ -47404,10 +47404,10 @@
         <v>191</v>
       </c>
       <c r="G1461" s="1">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="H1461" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1461" t="s">
         <v>197</v>
@@ -47436,7 +47436,7 @@
         <v>192</v>
       </c>
       <c r="G1462" s="1">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="H1462" s="1">
         <v>6</v>
@@ -53868,7 +53868,7 @@
         <v>190</v>
       </c>
       <c r="G1663" s="1">
-        <v>10.5</v>
+        <v>640</v>
       </c>
       <c r="H1663" s="1">
         <v>2</v>
@@ -53900,7 +53900,7 @@
         <v>191</v>
       </c>
       <c r="G1664" s="1">
-        <v>535</v>
+        <v>1015</v>
       </c>
       <c r="H1664" s="1">
         <v>3</v>
@@ -53932,7 +53932,7 @@
         <v>192</v>
       </c>
       <c r="G1665" s="1">
-        <v>750</v>
+        <v>1395</v>
       </c>
       <c r="H1665" s="1">
         <v>1</v>
@@ -56172,7 +56172,7 @@
         <v>190</v>
       </c>
       <c r="G1735" s="1">
-        <v>40.5</v>
+        <v>35</v>
       </c>
       <c r="H1735" s="1">
         <v>6</v>
@@ -56204,10 +56204,10 @@
         <v>191</v>
       </c>
       <c r="G1736" s="1">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="H1736" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1736" t="s">
         <v>197</v>
@@ -56236,10 +56236,10 @@
         <v>192</v>
       </c>
       <c r="G1737" s="1">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H1737" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1737" t="s">
         <v>197</v>
@@ -56812,10 +56812,10 @@
         <v>190</v>
       </c>
       <c r="G1755" s="1">
-        <v>317.5</v>
+        <v>285</v>
       </c>
       <c r="H1755" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1755" t="s">
         <v>197</v>
@@ -56844,10 +56844,10 @@
         <v>191</v>
       </c>
       <c r="G1756" s="1">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="H1756" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1756" t="s">
         <v>197</v>
@@ -56876,7 +56876,7 @@
         <v>192</v>
       </c>
       <c r="G1757" s="1">
-        <v>932.5</v>
+        <v>892.5</v>
       </c>
       <c r="H1757" s="1">
         <v>6</v>
@@ -58764,7 +58764,7 @@
         <v>190</v>
       </c>
       <c r="G1816" s="1">
-        <v>212.5</v>
+        <v>235</v>
       </c>
       <c r="H1816" s="1">
         <v>6</v>
@@ -58796,7 +58796,7 @@
         <v>191</v>
       </c>
       <c r="G1817" s="1">
-        <v>360</v>
+        <v>377.5</v>
       </c>
       <c r="H1817" s="1">
         <v>6</v>
@@ -58828,7 +58828,7 @@
         <v>192</v>
       </c>
       <c r="G1818" s="1">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="H1818" s="1">
         <v>5</v>
@@ -60108,7 +60108,7 @@
         <v>190</v>
       </c>
       <c r="G1858" s="1">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="H1858" s="1">
         <v>3</v>
@@ -61452,7 +61452,7 @@
         <v>190</v>
       </c>
       <c r="G1900" s="1">
-        <v>209.5</v>
+        <v>465</v>
       </c>
       <c r="H1900" s="1">
         <v>4</v>
@@ -61484,7 +61484,7 @@
         <v>191</v>
       </c>
       <c r="G1901" s="1">
-        <v>630</v>
+        <v>800</v>
       </c>
       <c r="H1901" s="1">
         <v>5</v>
@@ -61516,7 +61516,7 @@
         <v>192</v>
       </c>
       <c r="G1902" s="1">
-        <v>975</v>
+        <v>1030</v>
       </c>
       <c r="H1902" s="1">
         <v>3</v>
@@ -62092,7 +62092,7 @@
         <v>190</v>
       </c>
       <c r="G1920" s="1">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H1920" s="1">
         <v>4</v>
@@ -62124,7 +62124,7 @@
         <v>191</v>
       </c>
       <c r="G1921" s="1">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="H1921" s="1">
         <v>3</v>
@@ -62156,7 +62156,7 @@
         <v>192</v>
       </c>
       <c r="G1922" s="1">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="H1922" s="1">
         <v>3</v>
@@ -63692,7 +63692,7 @@
         <v>190</v>
       </c>
       <c r="G1970" s="1">
-        <v>130</v>
+        <v>1300</v>
       </c>
       <c r="H1970" s="1">
         <v>2</v>
@@ -63724,7 +63724,7 @@
         <v>191</v>
       </c>
       <c r="G1971" s="1">
-        <v>240</v>
+        <v>2400</v>
       </c>
       <c r="H1971" s="1">
         <v>1</v>
@@ -63756,10 +63756,10 @@
         <v>190</v>
       </c>
       <c r="G1972" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1972" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I1972" t="s">
         <v>197</v>
@@ -63820,10 +63820,10 @@
         <v>192</v>
       </c>
       <c r="G1974" s="1">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="H1974" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1974" t="s">
         <v>197</v>
@@ -67660,7 +67660,7 @@
         <v>190</v>
       </c>
       <c r="G2094" s="1">
-        <v>127.5</v>
+        <v>100</v>
       </c>
       <c r="H2094" s="1">
         <v>6</v>
@@ -67692,7 +67692,7 @@
         <v>191</v>
       </c>
       <c r="G2095" s="1">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H2095" s="1">
         <v>7</v>
@@ -67724,7 +67724,7 @@
         <v>192</v>
       </c>
       <c r="G2096" s="1">
-        <v>605</v>
+        <v>680</v>
       </c>
       <c r="H2096" s="1">
         <v>5</v>
@@ -69516,7 +69516,7 @@
         <v>190</v>
       </c>
       <c r="G2152" s="1">
-        <v>337.5</v>
+        <v>267.5</v>
       </c>
       <c r="H2152" s="1">
         <v>6</v>
@@ -69548,10 +69548,10 @@
         <v>191</v>
       </c>
       <c r="G2153" s="1">
-        <v>685</v>
+        <v>617.5</v>
       </c>
       <c r="H2153" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2153" t="s">
         <v>197</v>
@@ -69580,10 +69580,10 @@
         <v>192</v>
       </c>
       <c r="G2154" s="1">
-        <v>1020</v>
+        <v>775</v>
       </c>
       <c r="H2154" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2154" t="s">
         <v>197</v>
@@ -72172,7 +72172,7 @@
         <v>192</v>
       </c>
       <c r="G2235" s="1">
-        <v>106.5</v>
+        <v>1065</v>
       </c>
       <c r="H2235" s="1">
         <v>2</v>
@@ -78476,7 +78476,7 @@
         <v>190</v>
       </c>
       <c r="G2432" s="1">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H2432" s="1">
         <v>5</v>
@@ -78540,7 +78540,7 @@
         <v>192</v>
       </c>
       <c r="G2434" s="1">
-        <v>240</v>
+        <v>217.5</v>
       </c>
       <c r="H2434" s="1">
         <v>4</v>
@@ -83980,7 +83980,7 @@
         <v>190</v>
       </c>
       <c r="G2604" s="1">
-        <v>117.5</v>
+        <v>95</v>
       </c>
       <c r="H2604" s="1">
         <v>8</v>
@@ -84044,7 +84044,7 @@
         <v>192</v>
       </c>
       <c r="G2606" s="1">
-        <v>650</v>
+        <v>740</v>
       </c>
       <c r="H2606" s="1">
         <v>7</v>
@@ -86764,10 +86764,10 @@
         <v>190</v>
       </c>
       <c r="G2691" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H2691" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2691" t="s">
         <v>197</v>
@@ -86796,10 +86796,10 @@
         <v>191</v>
       </c>
       <c r="G2692" s="1">
-        <v>147.5</v>
+        <v>150</v>
       </c>
       <c r="H2692" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2692" t="s">
         <v>197</v>
@@ -86828,7 +86828,7 @@
         <v>192</v>
       </c>
       <c r="G2693" s="1">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="H2693" s="1">
         <v>7</v>
@@ -87724,7 +87724,7 @@
         <v>190</v>
       </c>
       <c r="G2721" s="1">
-        <v>315</v>
+        <v>250</v>
       </c>
       <c r="H2721" s="1">
         <v>5</v>
@@ -88108,10 +88108,10 @@
         <v>190</v>
       </c>
       <c r="G2733" s="1">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="H2733" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2733" t="s">
         <v>197</v>
@@ -88143,7 +88143,7 @@
         <v>30</v>
       </c>
       <c r="H2734" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2734" t="s">
         <v>197</v>
@@ -88172,10 +88172,10 @@
         <v>192</v>
       </c>
       <c r="G2735" s="1">
-        <v>55</v>
+        <v>67.5</v>
       </c>
       <c r="H2735" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2735" t="s">
         <v>197</v>
@@ -90028,7 +90028,7 @@
         <v>190</v>
       </c>
       <c r="G2793" s="1">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="H2793" s="1">
         <v>3</v>
@@ -92492,7 +92492,7 @@
         <v>191</v>
       </c>
       <c r="G2870" s="1">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="H2870" s="1">
         <v>4</v>
@@ -94892,7 +94892,7 @@
         <v>191</v>
       </c>
       <c r="G2945" s="1">
-        <v>136.5</v>
+        <v>1362.5</v>
       </c>
       <c r="H2945" s="1">
         <v>2</v>
@@ -96204,7 +96204,7 @@
         <v>190</v>
       </c>
       <c r="G2986" s="1">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H2986" s="1">
         <v>5</v>
@@ -96236,7 +96236,7 @@
         <v>191</v>
       </c>
       <c r="G2987" s="1">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="H2987" s="1">
         <v>6</v>
@@ -96268,7 +96268,7 @@
         <v>192</v>
       </c>
       <c r="G2988" s="1">
-        <v>1037.5</v>
+        <v>870</v>
       </c>
       <c r="H2988" s="1">
         <v>4</v>
@@ -104236,7 +104236,7 @@
         <v>190</v>
       </c>
       <c r="G3237" s="1">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="H3237" s="1">
         <v>6</v>
@@ -104300,7 +104300,7 @@
         <v>192</v>
       </c>
       <c r="G3239" s="1">
-        <v>965</v>
+        <v>870</v>
       </c>
       <c r="H3239" s="1">
         <v>5</v>
@@ -104364,7 +104364,7 @@
         <v>190</v>
       </c>
       <c r="G3241" s="1">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H3241" s="1">
         <v>5</v>
@@ -104396,7 +104396,7 @@
         <v>191</v>
       </c>
       <c r="G3242" s="1">
-        <v>317.5</v>
+        <v>365</v>
       </c>
       <c r="H3242" s="1">
         <v>6</v>
@@ -104428,7 +104428,7 @@
         <v>192</v>
       </c>
       <c r="G3243" s="1">
-        <v>570</v>
+        <v>597.5</v>
       </c>
       <c r="H3243" s="1">
         <v>4</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -2860,7 +2860,7 @@
         <v>190</v>
       </c>
       <c r="G69" s="1">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="H69" s="1">
         <v>3</v>
@@ -5580,7 +5580,7 @@
         <v>193</v>
       </c>
       <c r="G154" s="1">
-        <v>325</v>
+        <v>455</v>
       </c>
       <c r="H154" s="1">
         <v>3</v>
@@ -9836,7 +9836,7 @@
         <v>190</v>
       </c>
       <c r="G287" s="1">
-        <v>108</v>
+        <v>300</v>
       </c>
       <c r="H287" s="1">
         <v>2</v>
@@ -9868,7 +9868,7 @@
         <v>191</v>
       </c>
       <c r="G288" s="1">
-        <v>525</v>
+        <v>562.5</v>
       </c>
       <c r="H288" s="1">
         <v>2</v>
@@ -9900,7 +9900,7 @@
         <v>192</v>
       </c>
       <c r="G289" s="1">
-        <v>580</v>
+        <v>1210</v>
       </c>
       <c r="H289" s="1">
         <v>1</v>
@@ -11820,7 +11820,7 @@
         <v>190</v>
       </c>
       <c r="G349" s="1">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="H349" s="1">
         <v>1</v>
@@ -11852,7 +11852,7 @@
         <v>191</v>
       </c>
       <c r="G350" s="1">
-        <v>435</v>
+        <v>850</v>
       </c>
       <c r="H350" s="1">
         <v>2</v>
@@ -18284,7 +18284,7 @@
         <v>193</v>
       </c>
       <c r="G551" s="1">
-        <v>252.5</v>
+        <v>632.5</v>
       </c>
       <c r="H551" s="1">
         <v>2</v>
@@ -22764,7 +22764,7 @@
         <v>191</v>
       </c>
       <c r="G691" s="1">
-        <v>332.5</v>
+        <v>62.5</v>
       </c>
       <c r="H691" s="1">
         <v>2</v>
@@ -51724,7 +51724,7 @@
         <v>190</v>
       </c>
       <c r="G1596" s="1">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="H1596" s="1">
         <v>1</v>
@@ -51756,7 +51756,7 @@
         <v>191</v>
       </c>
       <c r="G1597" s="1">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="H1597" s="1">
         <v>1</v>
@@ -52588,7 +52588,7 @@
         <v>191</v>
       </c>
       <c r="G1623" s="1">
-        <v>41</v>
+        <v>280</v>
       </c>
       <c r="H1623" s="1">
         <v>2</v>
@@ -52620,7 +52620,7 @@
         <v>192</v>
       </c>
       <c r="G1624" s="1">
-        <v>160</v>
+        <v>420</v>
       </c>
       <c r="H1624" s="1">
         <v>1</v>
@@ -54732,7 +54732,7 @@
         <v>190</v>
       </c>
       <c r="G1690" s="1">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="H1690" s="1">
         <v>3</v>
@@ -54764,7 +54764,7 @@
         <v>191</v>
       </c>
       <c r="G1691" s="1">
-        <v>247.5</v>
+        <v>412.5</v>
       </c>
       <c r="H1691" s="1">
         <v>2</v>
@@ -54796,7 +54796,7 @@
         <v>192</v>
       </c>
       <c r="G1692" s="1">
-        <v>412.5</v>
+        <v>690</v>
       </c>
       <c r="H1692" s="1">
         <v>2</v>
@@ -57100,7 +57100,7 @@
         <v>191</v>
       </c>
       <c r="G1764" s="1">
-        <v>145</v>
+        <v>775</v>
       </c>
       <c r="H1764" s="1">
         <v>2</v>
@@ -57132,7 +57132,7 @@
         <v>192</v>
       </c>
       <c r="G1765" s="1">
-        <v>775</v>
+        <v>1455</v>
       </c>
       <c r="H1765" s="1">
         <v>2</v>
@@ -58508,7 +58508,7 @@
         <v>190</v>
       </c>
       <c r="G1808" s="1">
-        <v>198.5</v>
+        <v>387.5</v>
       </c>
       <c r="H1808" s="1">
         <v>2</v>
@@ -58540,7 +58540,7 @@
         <v>192</v>
       </c>
       <c r="G1809" s="1">
-        <v>495</v>
+        <v>1170</v>
       </c>
       <c r="H1809" s="1">
         <v>1</v>
@@ -67564,7 +67564,7 @@
         <v>190</v>
       </c>
       <c r="G2091" s="1">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="H2091" s="1">
         <v>4</v>
@@ -67596,7 +67596,7 @@
         <v>191</v>
       </c>
       <c r="G2092" s="1">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="H2092" s="1">
         <v>3</v>
@@ -69932,7 +69932,7 @@
         <v>190</v>
       </c>
       <c r="G2165" s="1">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="H2165" s="1">
         <v>3</v>
@@ -69964,7 +69964,7 @@
         <v>191</v>
       </c>
       <c r="G2166" s="1">
-        <v>325</v>
+        <v>465</v>
       </c>
       <c r="H2166" s="1">
         <v>2</v>
@@ -71020,16 +71020,16 @@
         <v>190</v>
       </c>
       <c r="G2199" s="1">
-        <v>48.5</v>
+        <v>250</v>
       </c>
       <c r="H2199" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2199" t="s">
         <v>197</v>
       </c>
       <c r="J2199" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2200">
@@ -71052,16 +71052,16 @@
         <v>191</v>
       </c>
       <c r="G2200" s="1">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="H2200" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2200" t="s">
         <v>197</v>
       </c>
       <c r="J2200" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2201">
@@ -71084,7 +71084,7 @@
         <v>192</v>
       </c>
       <c r="G2201" s="1">
-        <v>310</v>
+        <v>550</v>
       </c>
       <c r="H2201" s="1">
         <v>1</v>
@@ -78063,7 +78063,7 @@
         <v>200</v>
       </c>
       <c r="H2419" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2419" t="s">
         <v>197</v>
@@ -78092,10 +78092,10 @@
         <v>191</v>
       </c>
       <c r="G2420" s="1">
-        <v>437.5</v>
+        <v>225</v>
       </c>
       <c r="H2420" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2420" t="s">
         <v>197</v>
@@ -82124,7 +82124,7 @@
         <v>190</v>
       </c>
       <c r="G2546" s="1">
-        <v>141.5</v>
+        <v>237.5</v>
       </c>
       <c r="H2546" s="1">
         <v>2</v>
@@ -82156,7 +82156,7 @@
         <v>191</v>
       </c>
       <c r="G2547" s="1">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="H2547" s="1">
         <v>1</v>
@@ -82188,7 +82188,7 @@
         <v>192</v>
       </c>
       <c r="G2548" s="1">
-        <v>280</v>
+        <v>575</v>
       </c>
       <c r="H2548" s="1">
         <v>1</v>
@@ -82508,7 +82508,7 @@
         <v>191</v>
       </c>
       <c r="G2558" s="1">
-        <v>395.5</v>
+        <v>685</v>
       </c>
       <c r="H2558" s="1">
         <v>2</v>
@@ -82540,7 +82540,7 @@
         <v>192</v>
       </c>
       <c r="G2559" s="1">
-        <v>730</v>
+        <v>1510</v>
       </c>
       <c r="H2559" s="1">
         <v>1</v>
@@ -83852,7 +83852,7 @@
         <v>190</v>
       </c>
       <c r="G2600" s="1">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H2600" s="1">
         <v>5</v>
@@ -83884,7 +83884,7 @@
         <v>191</v>
       </c>
       <c r="G2601" s="1">
-        <v>275</v>
+        <v>81.5</v>
       </c>
       <c r="H2601" s="1">
         <v>4</v>
@@ -85420,7 +85420,7 @@
         <v>192</v>
       </c>
       <c r="G2649" s="1">
-        <v>324.5</v>
+        <v>637.5</v>
       </c>
       <c r="H2649" s="1">
         <v>2</v>
@@ -86060,7 +86060,7 @@
         <v>190</v>
       </c>
       <c r="G2669" s="1">
-        <v>152.5</v>
+        <v>40</v>
       </c>
       <c r="H2669" s="1">
         <v>2</v>
@@ -88204,7 +88204,7 @@
         <v>190</v>
       </c>
       <c r="G2736" s="1">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H2736" s="1">
         <v>3</v>
@@ -88236,7 +88236,7 @@
         <v>191</v>
       </c>
       <c r="G2737" s="1">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="H2737" s="1">
         <v>3</v>
@@ -92876,10 +92876,10 @@
         <v>190</v>
       </c>
       <c r="G2882" s="1">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H2882" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2882" t="s">
         <v>197</v>
@@ -92908,16 +92908,16 @@
         <v>191</v>
       </c>
       <c r="G2883" s="1">
-        <v>72.5</v>
+        <v>65</v>
       </c>
       <c r="H2883" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2883" t="s">
         <v>197</v>
       </c>
       <c r="J2883" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2884">
@@ -92940,7 +92940,7 @@
         <v>192</v>
       </c>
       <c r="G2884" s="1">
-        <v>425</v>
+        <v>72.5</v>
       </c>
       <c r="H2884" s="1">
         <v>2</v>
@@ -100972,7 +100972,7 @@
         <v>190</v>
       </c>
       <c r="G3135" s="1">
-        <v>435</v>
+        <v>185</v>
       </c>
       <c r="H3135" s="1">
         <v>1</v>
@@ -101004,7 +101004,7 @@
         <v>191</v>
       </c>
       <c r="G3136" s="1">
-        <v>2025</v>
+        <v>327.5</v>
       </c>
       <c r="H3136" s="1">
         <v>2</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -3052,7 +3052,7 @@
         <v>190</v>
       </c>
       <c r="G75" s="1">
-        <v>65</v>
+        <v>650</v>
       </c>
       <c r="H75" s="1">
         <v>2</v>
@@ -5228,7 +5228,7 @@
         <v>190</v>
       </c>
       <c r="G143" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H143" s="1">
         <v>3</v>
@@ -10060,7 +10060,7 @@
         <v>191</v>
       </c>
       <c r="G294" s="1">
-        <v>485</v>
+        <v>530</v>
       </c>
       <c r="H294" s="1">
         <v>3</v>
@@ -10092,7 +10092,7 @@
         <v>192</v>
       </c>
       <c r="G295" s="1">
-        <v>1735</v>
+        <v>4850</v>
       </c>
       <c r="H295" s="1">
         <v>1</v>
@@ -10156,7 +10156,7 @@
         <v>190</v>
       </c>
       <c r="G297" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H297" s="1">
         <v>3</v>
@@ -10860,7 +10860,7 @@
         <v>190</v>
       </c>
       <c r="G319" s="1">
-        <v>65</v>
+        <v>650</v>
       </c>
       <c r="H319" s="1">
         <v>4</v>
@@ -14348,7 +14348,7 @@
         <v>190</v>
       </c>
       <c r="G428" s="1">
-        <v>70</v>
+        <v>385</v>
       </c>
       <c r="H428" s="1">
         <v>2</v>
@@ -15692,7 +15692,7 @@
         <v>190</v>
       </c>
       <c r="G470" s="1">
-        <v>62.5</v>
+        <v>625</v>
       </c>
       <c r="H470" s="1">
         <v>2</v>
@@ -18028,7 +18028,7 @@
         <v>193</v>
       </c>
       <c r="G543" s="1">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="H543" s="1">
         <v>5</v>
@@ -20428,7 +20428,7 @@
         <v>191</v>
       </c>
       <c r="G618" s="1">
-        <v>64</v>
+        <v>645</v>
       </c>
       <c r="H618" s="1">
         <v>1</v>
@@ -26380,7 +26380,7 @@
         <v>191</v>
       </c>
       <c r="G804" s="1">
-        <v>1095</v>
+        <v>1517.5</v>
       </c>
       <c r="H804" s="1">
         <v>2</v>
@@ -26412,7 +26412,7 @@
         <v>192</v>
       </c>
       <c r="G805" s="1">
-        <v>1695</v>
+        <v>2862.5</v>
       </c>
       <c r="H805" s="1">
         <v>2</v>
@@ -26444,7 +26444,7 @@
         <v>193</v>
       </c>
       <c r="G806" s="1">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H806" s="1">
         <v>5</v>
@@ -28716,7 +28716,7 @@
         <v>191</v>
       </c>
       <c r="G877" s="1">
-        <v>40</v>
+        <v>395</v>
       </c>
       <c r="H877" s="1">
         <v>1</v>
@@ -28748,7 +28748,7 @@
         <v>191</v>
       </c>
       <c r="G878" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H878" s="1">
         <v>3</v>
@@ -31628,7 +31628,7 @@
         <v>190</v>
       </c>
       <c r="G968" s="1">
-        <v>78.5</v>
+        <v>87.5</v>
       </c>
       <c r="H968" s="1">
         <v>2</v>
@@ -31660,7 +31660,7 @@
         <v>191</v>
       </c>
       <c r="G969" s="1">
-        <v>225</v>
+        <v>465</v>
       </c>
       <c r="H969" s="1">
         <v>2</v>
@@ -31692,7 +31692,7 @@
         <v>192</v>
       </c>
       <c r="G970" s="1">
-        <v>575</v>
+        <v>770</v>
       </c>
       <c r="H970" s="1">
         <v>1</v>
@@ -33100,7 +33100,7 @@
         <v>191</v>
       </c>
       <c r="G1014" s="1">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="H1014" s="1">
         <v>1</v>
@@ -34508,7 +34508,7 @@
         <v>193</v>
       </c>
       <c r="G1058" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H1058" s="1">
         <v>1</v>
@@ -37004,7 +37004,7 @@
         <v>191</v>
       </c>
       <c r="G1136" s="1">
-        <v>345</v>
+        <v>475</v>
       </c>
       <c r="H1136" s="1">
         <v>3</v>
@@ -37708,7 +37708,7 @@
         <v>190</v>
       </c>
       <c r="G1158" s="1">
-        <v>75</v>
+        <v>457.5</v>
       </c>
       <c r="H1158" s="1">
         <v>2</v>
@@ -48844,16 +48844,16 @@
         <v>190</v>
       </c>
       <c r="G1506" s="1">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="H1506" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1506" t="s">
         <v>197</v>
       </c>
       <c r="J1506" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1507">
@@ -48876,21 +48876,21 @@
         <v>191</v>
       </c>
       <c r="G1507" s="1">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="H1507" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1507" t="s">
         <v>197</v>
       </c>
       <c r="J1507" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1508">
       <c r="A1508" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1508" t="s">
         <v>24</v>
@@ -48899,25 +48899,25 @@
         <v>73</v>
       </c>
       <c r="D1508" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E1508" t="s">
         <v>188</v>
       </c>
       <c r="F1508" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G1508" s="1">
-        <v>480</v>
+        <v>375</v>
       </c>
       <c r="H1508" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I1508" t="s">
         <v>197</v>
       </c>
       <c r="J1508" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1509">
@@ -48937,10 +48937,10 @@
         <v>188</v>
       </c>
       <c r="F1509" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1509" s="1">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="H1509" s="1">
         <v>5</v>
@@ -48954,7 +48954,7 @@
     </row>
     <row r="1510">
       <c r="A1510" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1510" t="s">
         <v>24</v>
@@ -48963,19 +48963,19 @@
         <v>73</v>
       </c>
       <c r="D1510" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E1510" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F1510" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1510" s="1">
-        <v>750</v>
+        <v>360</v>
       </c>
       <c r="H1510" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1510" t="s">
         <v>197</v>
@@ -49001,13 +49001,13 @@
         <v>187</v>
       </c>
       <c r="F1511" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1511" s="1">
-        <v>360</v>
+        <v>560</v>
       </c>
       <c r="H1511" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1511" t="s">
         <v>197</v>
@@ -49033,24 +49033,24 @@
         <v>187</v>
       </c>
       <c r="F1512" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1512" s="1">
-        <v>560</v>
+        <v>670</v>
       </c>
       <c r="H1512" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1512" t="s">
         <v>197</v>
       </c>
       <c r="J1512" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B1513" t="s">
         <v>24</v>
@@ -49059,16 +49059,16 @@
         <v>73</v>
       </c>
       <c r="D1513" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E1513" t="s">
         <v>187</v>
       </c>
       <c r="F1513" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1513" s="1">
-        <v>670</v>
+        <v>205</v>
       </c>
       <c r="H1513" s="1">
         <v>2</v>
@@ -49097,19 +49097,19 @@
         <v>187</v>
       </c>
       <c r="F1514" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1514" s="1">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="H1514" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1514" t="s">
         <v>197</v>
       </c>
       <c r="J1514" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1515">
@@ -49129,51 +49129,51 @@
         <v>187</v>
       </c>
       <c r="F1515" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1515" s="1">
-        <v>285</v>
+        <v>545</v>
       </c>
       <c r="H1515" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1515" t="s">
         <v>197</v>
       </c>
       <c r="J1515" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B1516" t="s">
         <v>24</v>
       </c>
       <c r="C1516" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1516" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="E1516" t="s">
         <v>187</v>
       </c>
       <c r="F1516" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1516" s="1">
-        <v>545</v>
+        <v>275</v>
       </c>
       <c r="H1516" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I1516" t="s">
         <v>197</v>
       </c>
       <c r="J1516" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1517">
@@ -49187,7 +49187,7 @@
         <v>74</v>
       </c>
       <c r="D1517" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="E1517" t="s">
         <v>187</v>
@@ -49196,10 +49196,10 @@
         <v>190</v>
       </c>
       <c r="G1517" s="1">
-        <v>275</v>
+        <v>585</v>
       </c>
       <c r="H1517" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1517" t="s">
         <v>197</v>
@@ -49225,10 +49225,10 @@
         <v>187</v>
       </c>
       <c r="F1518" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1518" s="1">
-        <v>585</v>
+        <v>765</v>
       </c>
       <c r="H1518" s="1">
         <v>3</v>
@@ -49257,24 +49257,24 @@
         <v>187</v>
       </c>
       <c r="F1519" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1519" s="1">
-        <v>765</v>
+        <v>1355</v>
       </c>
       <c r="H1519" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1519" t="s">
         <v>197</v>
       </c>
       <c r="J1519" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B1520" t="s">
         <v>24</v>
@@ -49283,25 +49283,25 @@
         <v>74</v>
       </c>
       <c r="D1520" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E1520" t="s">
         <v>187</v>
       </c>
       <c r="F1520" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1520" s="1">
-        <v>1355</v>
+        <v>120</v>
       </c>
       <c r="H1520" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1520" t="s">
         <v>197</v>
       </c>
       <c r="J1520" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1521">
@@ -49321,10 +49321,10 @@
         <v>187</v>
       </c>
       <c r="F1521" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1521" s="1">
-        <v>120</v>
+        <v>255</v>
       </c>
       <c r="H1521" s="1">
         <v>3</v>
@@ -49353,24 +49353,24 @@
         <v>187</v>
       </c>
       <c r="F1522" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1522" s="1">
-        <v>255</v>
+        <v>382.5</v>
       </c>
       <c r="H1522" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1522" t="s">
         <v>197</v>
       </c>
       <c r="J1522" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B1523" t="s">
         <v>24</v>
@@ -49379,25 +49379,25 @@
         <v>74</v>
       </c>
       <c r="D1523" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E1523" t="s">
         <v>187</v>
       </c>
       <c r="F1523" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1523" s="1">
-        <v>382.5</v>
+        <v>117.5</v>
       </c>
       <c r="H1523" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1523" t="s">
         <v>197</v>
       </c>
       <c r="J1523" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1524">
@@ -49411,30 +49411,30 @@
         <v>74</v>
       </c>
       <c r="D1524" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E1524" t="s">
         <v>187</v>
       </c>
       <c r="F1524" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G1524" s="1">
-        <v>117.5</v>
+        <v>1445</v>
       </c>
       <c r="H1524" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I1524" t="s">
         <v>197</v>
       </c>
       <c r="J1524" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1525" t="s">
         <v>24</v>
@@ -49443,25 +49443,25 @@
         <v>74</v>
       </c>
       <c r="D1525" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E1525" t="s">
         <v>187</v>
       </c>
       <c r="F1525" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1525" s="1">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="H1525" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I1525" t="s">
         <v>197</v>
       </c>
       <c r="J1525" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1526">
@@ -49481,19 +49481,19 @@
         <v>187</v>
       </c>
       <c r="F1526" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1526" s="1">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="H1526" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I1526" t="s">
         <v>197</v>
       </c>
       <c r="J1526" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1527">
@@ -49513,24 +49513,24 @@
         <v>187</v>
       </c>
       <c r="F1527" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1527" s="1">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="H1527" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1527" t="s">
         <v>197</v>
       </c>
       <c r="J1527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1528" t="s">
         <v>24</v>
@@ -49539,25 +49539,25 @@
         <v>74</v>
       </c>
       <c r="D1528" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E1528" t="s">
         <v>187</v>
       </c>
       <c r="F1528" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G1528" s="1">
-        <v>200</v>
+        <v>887.5</v>
       </c>
       <c r="H1528" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1528" t="s">
         <v>197</v>
       </c>
       <c r="J1528" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1529">
@@ -49577,13 +49577,13 @@
         <v>187</v>
       </c>
       <c r="F1529" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1529" s="1">
-        <v>887.5</v>
+        <v>1175</v>
       </c>
       <c r="H1529" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1529" t="s">
         <v>197</v>
@@ -49594,7 +49594,7 @@
     </row>
     <row r="1530">
       <c r="A1530" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1530" t="s">
         <v>24</v>
@@ -49603,25 +49603,25 @@
         <v>74</v>
       </c>
       <c r="D1530" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E1530" t="s">
         <v>187</v>
       </c>
       <c r="F1530" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1530" s="1">
-        <v>1175</v>
+        <v>30</v>
       </c>
       <c r="H1530" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I1530" t="s">
         <v>197</v>
       </c>
       <c r="J1530" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1531">
@@ -49635,7 +49635,7 @@
         <v>74</v>
       </c>
       <c r="D1531" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E1531" t="s">
         <v>187</v>
@@ -49644,7 +49644,7 @@
         <v>190</v>
       </c>
       <c r="G1531" s="1">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="H1531" s="1">
         <v>5</v>
@@ -49658,7 +49658,7 @@
     </row>
     <row r="1532">
       <c r="A1532" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1532" t="s">
         <v>24</v>
@@ -49667,7 +49667,7 @@
         <v>74</v>
       </c>
       <c r="D1532" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E1532" t="s">
         <v>187</v>
@@ -49676,16 +49676,16 @@
         <v>190</v>
       </c>
       <c r="G1532" s="1">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="H1532" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I1532" t="s">
         <v>197</v>
       </c>
       <c r="J1532" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1533">
@@ -49699,7 +49699,7 @@
         <v>74</v>
       </c>
       <c r="D1533" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E1533" t="s">
         <v>187</v>
@@ -49708,10 +49708,10 @@
         <v>190</v>
       </c>
       <c r="G1533" s="1">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="H1533" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1533" t="s">
         <v>197</v>
@@ -49731,7 +49731,7 @@
         <v>74</v>
       </c>
       <c r="D1534" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E1534" t="s">
         <v>187</v>
@@ -49740,21 +49740,21 @@
         <v>190</v>
       </c>
       <c r="G1534" s="1">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H1534" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1534" t="s">
         <v>197</v>
       </c>
       <c r="J1534" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1535" t="s">
         <v>24</v>
@@ -49763,16 +49763,16 @@
         <v>74</v>
       </c>
       <c r="D1535" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="E1535" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F1535" t="s">
         <v>190</v>
       </c>
       <c r="G1535" s="1">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="H1535" s="1">
         <v>3</v>
@@ -49795,16 +49795,16 @@
         <v>74</v>
       </c>
       <c r="D1536" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="E1536" t="s">
         <v>188</v>
       </c>
       <c r="F1536" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1536" s="1">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="H1536" s="1">
         <v>3</v>
@@ -49827,19 +49827,19 @@
         <v>74</v>
       </c>
       <c r="D1537" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E1537" t="s">
         <v>188</v>
       </c>
       <c r="F1537" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1537" s="1">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="H1537" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1537" t="s">
         <v>197</v>
@@ -49850,7 +49850,7 @@
     </row>
     <row r="1538">
       <c r="A1538" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1538" t="s">
         <v>24</v>
@@ -49859,16 +49859,16 @@
         <v>74</v>
       </c>
       <c r="D1538" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E1538" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F1538" t="s">
         <v>192</v>
       </c>
       <c r="G1538" s="1">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="H1538" s="1">
         <v>4</v>
@@ -49891,19 +49891,19 @@
         <v>74</v>
       </c>
       <c r="D1539" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E1539" t="s">
         <v>187</v>
       </c>
       <c r="F1539" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G1539" s="1">
-        <v>680</v>
+        <v>420</v>
       </c>
       <c r="H1539" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1539" t="s">
         <v>197</v>
@@ -49914,7 +49914,7 @@
     </row>
     <row r="1540">
       <c r="A1540" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1540" t="s">
         <v>24</v>
@@ -49923,7 +49923,7 @@
         <v>74</v>
       </c>
       <c r="D1540" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1540" t="s">
         <v>187</v>
@@ -49932,13 +49932,13 @@
         <v>191</v>
       </c>
       <c r="G1540" s="1">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="H1540" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1540" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J1540" s="1">
         <v>0</v>
@@ -49946,7 +49946,7 @@
     </row>
     <row r="1541">
       <c r="A1541" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1541" t="s">
         <v>24</v>
@@ -49955,22 +49955,22 @@
         <v>74</v>
       </c>
       <c r="D1541" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E1541" t="s">
         <v>187</v>
       </c>
       <c r="F1541" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G1541" s="1">
-        <v>445</v>
+        <v>200</v>
       </c>
       <c r="H1541" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1541" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J1541" s="1">
         <v>0</v>
@@ -49978,16 +49978,16 @@
     </row>
     <row r="1542">
       <c r="A1542" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B1542" t="s">
         <v>24</v>
       </c>
       <c r="C1542" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1542" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E1542" t="s">
         <v>187</v>
@@ -49996,7 +49996,7 @@
         <v>190</v>
       </c>
       <c r="G1542" s="1">
-        <v>200</v>
+        <v>592.5</v>
       </c>
       <c r="H1542" s="1">
         <v>4</v>
@@ -50025,19 +50025,19 @@
         <v>187</v>
       </c>
       <c r="F1543" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1543" s="1">
-        <v>592.5</v>
+        <v>762.5</v>
       </c>
       <c r="H1543" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1543" t="s">
         <v>197</v>
       </c>
       <c r="J1543" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1544">
@@ -50057,10 +50057,10 @@
         <v>187</v>
       </c>
       <c r="F1544" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1544" s="1">
-        <v>762.5</v>
+        <v>1192.5</v>
       </c>
       <c r="H1544" s="1">
         <v>2</v>
@@ -50074,7 +50074,7 @@
     </row>
     <row r="1545">
       <c r="A1545" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B1545" t="s">
         <v>24</v>
@@ -50083,19 +50083,19 @@
         <v>75</v>
       </c>
       <c r="D1545" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E1545" t="s">
         <v>187</v>
       </c>
       <c r="F1545" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1545" s="1">
-        <v>1192.5</v>
+        <v>115</v>
       </c>
       <c r="H1545" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1545" t="s">
         <v>197</v>
@@ -50121,13 +50121,13 @@
         <v>187</v>
       </c>
       <c r="F1546" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1546" s="1">
-        <v>115</v>
+        <v>237.5</v>
       </c>
       <c r="H1546" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1546" t="s">
         <v>197</v>
@@ -50138,7 +50138,7 @@
     </row>
     <row r="1547">
       <c r="A1547" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B1547" t="s">
         <v>24</v>
@@ -50147,25 +50147,25 @@
         <v>75</v>
       </c>
       <c r="D1547" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E1547" t="s">
         <v>187</v>
       </c>
       <c r="F1547" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G1547" s="1">
-        <v>237.5</v>
+        <v>155</v>
       </c>
       <c r="H1547" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1547" t="s">
         <v>197</v>
       </c>
       <c r="J1547" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1548">
@@ -50179,7 +50179,7 @@
         <v>75</v>
       </c>
       <c r="D1548" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E1548" t="s">
         <v>187</v>
@@ -50188,21 +50188,21 @@
         <v>190</v>
       </c>
       <c r="G1548" s="1">
-        <v>155</v>
+        <v>267.5</v>
       </c>
       <c r="H1548" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1548" t="s">
         <v>197</v>
       </c>
       <c r="J1548" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1549" t="s">
         <v>24</v>
@@ -50211,7 +50211,7 @@
         <v>75</v>
       </c>
       <c r="D1549" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E1549" t="s">
         <v>187</v>
@@ -50220,16 +50220,16 @@
         <v>190</v>
       </c>
       <c r="G1549" s="1">
-        <v>267.5</v>
+        <v>100</v>
       </c>
       <c r="H1549" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I1549" t="s">
         <v>197</v>
       </c>
       <c r="J1549" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1550">
@@ -50249,13 +50249,13 @@
         <v>187</v>
       </c>
       <c r="F1550" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1550" s="1">
-        <v>100</v>
+        <v>147.5</v>
       </c>
       <c r="H1550" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1550" t="s">
         <v>197</v>
@@ -50281,10 +50281,10 @@
         <v>187</v>
       </c>
       <c r="F1551" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1551" s="1">
-        <v>147.5</v>
+        <v>222.5</v>
       </c>
       <c r="H1551" s="1">
         <v>4</v>
@@ -50298,7 +50298,7 @@
     </row>
     <row r="1552">
       <c r="A1552" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1552" t="s">
         <v>24</v>
@@ -50307,7 +50307,7 @@
         <v>75</v>
       </c>
       <c r="D1552" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E1552" t="s">
         <v>187</v>
@@ -50316,10 +50316,10 @@
         <v>192</v>
       </c>
       <c r="G1552" s="1">
-        <v>222.5</v>
+        <v>1295</v>
       </c>
       <c r="H1552" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1552" t="s">
         <v>197</v>
@@ -50330,7 +50330,7 @@
     </row>
     <row r="1553">
       <c r="A1553" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1553" t="s">
         <v>24</v>
@@ -50339,25 +50339,25 @@
         <v>75</v>
       </c>
       <c r="D1553" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E1553" t="s">
         <v>187</v>
       </c>
       <c r="F1553" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G1553" s="1">
-        <v>1295</v>
+        <v>20</v>
       </c>
       <c r="H1553" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1553" t="s">
         <v>197</v>
       </c>
       <c r="J1553" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1554">
@@ -50377,13 +50377,13 @@
         <v>187</v>
       </c>
       <c r="F1554" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G1554" s="1">
         <v>200</v>
       </c>
       <c r="H1554" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1554" t="s">
         <v>197</v>
@@ -50540,7 +50540,7 @@
         <v>190</v>
       </c>
       <c r="G1559" s="1">
-        <v>52.5</v>
+        <v>322.5</v>
       </c>
       <c r="H1559" s="1">
         <v>2</v>
@@ -51436,7 +51436,7 @@
         <v>191</v>
       </c>
       <c r="G1587" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1587" s="1">
         <v>3</v>
@@ -51468,7 +51468,7 @@
         <v>192</v>
       </c>
       <c r="G1588" s="1">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="H1588" s="1">
         <v>3</v>
@@ -52556,16 +52556,16 @@
         <v>190</v>
       </c>
       <c r="G1622" s="1">
-        <v>42</v>
+        <v>37.5</v>
       </c>
       <c r="H1622" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1622" t="s">
         <v>197</v>
       </c>
       <c r="J1622" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1623">
@@ -52588,10 +52588,10 @@
         <v>192</v>
       </c>
       <c r="G1623" s="1">
-        <v>48</v>
+        <v>234</v>
       </c>
       <c r="H1623" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1623" t="s">
         <v>197</v>
@@ -53740,10 +53740,10 @@
         <v>190</v>
       </c>
       <c r="G1659" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H1659" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1659" t="s">
         <v>197</v>
@@ -53772,10 +53772,10 @@
         <v>192</v>
       </c>
       <c r="G1660" s="1">
-        <v>30</v>
+        <v>260</v>
       </c>
       <c r="H1660" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1660" t="s">
         <v>197</v>
@@ -54028,7 +54028,7 @@
         <v>190</v>
       </c>
       <c r="G1668" s="1">
-        <v>72.5</v>
+        <v>550</v>
       </c>
       <c r="H1668" s="1">
         <v>2</v>
@@ -54060,7 +54060,7 @@
         <v>192</v>
       </c>
       <c r="G1669" s="1">
-        <v>550</v>
+        <v>725</v>
       </c>
       <c r="H1669" s="1">
         <v>2</v>
@@ -54092,7 +54092,7 @@
         <v>190</v>
       </c>
       <c r="G1670" s="1">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="H1670" s="1">
         <v>1</v>
@@ -55084,10 +55084,10 @@
         <v>190</v>
       </c>
       <c r="G1701" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="H1701" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1701" t="s">
         <v>197</v>
@@ -55116,10 +55116,10 @@
         <v>191</v>
       </c>
       <c r="G1702" s="1">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="H1702" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1702" t="s">
         <v>197</v>
@@ -55308,7 +55308,7 @@
         <v>190</v>
       </c>
       <c r="G1708" s="1">
-        <v>57.5</v>
+        <v>575</v>
       </c>
       <c r="H1708" s="1">
         <v>2</v>
@@ -56556,7 +56556,7 @@
         <v>190</v>
       </c>
       <c r="G1747" s="1">
-        <v>77.5</v>
+        <v>775</v>
       </c>
       <c r="H1747" s="1">
         <v>2</v>
@@ -57804,7 +57804,7 @@
         <v>192</v>
       </c>
       <c r="G1786" s="1">
-        <v>55</v>
+        <v>550</v>
       </c>
       <c r="H1786" s="1">
         <v>1</v>
@@ -60332,7 +60332,7 @@
         <v>190</v>
       </c>
       <c r="G1865" s="1">
-        <v>48</v>
+        <v>480</v>
       </c>
       <c r="H1865" s="1">
         <v>1</v>
@@ -64044,7 +64044,7 @@
         <v>190</v>
       </c>
       <c r="G1981" s="1">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="H1981" s="1">
         <v>1</v>
@@ -64076,7 +64076,7 @@
         <v>190</v>
       </c>
       <c r="G1982" s="1">
-        <v>55</v>
+        <v>550</v>
       </c>
       <c r="H1982" s="1">
         <v>4</v>
@@ -65868,7 +65868,7 @@
         <v>190</v>
       </c>
       <c r="G2038" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H2038" s="1">
         <v>3</v>
@@ -66572,7 +66572,7 @@
         <v>190</v>
       </c>
       <c r="G2060" s="1">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="H2060" s="1">
         <v>6</v>
@@ -69100,7 +69100,7 @@
         <v>190</v>
       </c>
       <c r="G2139" s="1">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="H2139" s="1">
         <v>5</v>
@@ -73388,7 +73388,7 @@
         <v>190</v>
       </c>
       <c r="G2273" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H2273" s="1">
         <v>5</v>
@@ -74092,7 +74092,7 @@
         <v>192</v>
       </c>
       <c r="G2295" s="1">
-        <v>104</v>
+        <v>1040</v>
       </c>
       <c r="H2295" s="1">
         <v>1</v>
@@ -79724,16 +79724,16 @@
         <v>190</v>
       </c>
       <c r="G2471" s="1">
-        <v>200</v>
+        <v>42.5</v>
       </c>
       <c r="H2471" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2471" t="s">
         <v>197</v>
       </c>
       <c r="J2471" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2472">
@@ -79756,10 +79756,10 @@
         <v>191</v>
       </c>
       <c r="G2472" s="1">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H2472" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2472" t="s">
         <v>197</v>
@@ -84812,7 +84812,7 @@
         <v>190</v>
       </c>
       <c r="G2630" s="1">
-        <v>152.5</v>
+        <v>175</v>
       </c>
       <c r="H2630" s="1">
         <v>4</v>
@@ -84844,7 +84844,7 @@
         <v>192</v>
       </c>
       <c r="G2631" s="1">
-        <v>360</v>
+        <v>1175</v>
       </c>
       <c r="H2631" s="1">
         <v>3</v>
@@ -85900,7 +85900,7 @@
         <v>190</v>
       </c>
       <c r="G2664" s="1">
-        <v>1950</v>
+        <v>195</v>
       </c>
       <c r="H2664" s="1">
         <v>3</v>
@@ -86252,7 +86252,7 @@
         <v>190</v>
       </c>
       <c r="G2675" s="1">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H2675" s="1">
         <v>3</v>
@@ -86284,7 +86284,7 @@
         <v>191</v>
       </c>
       <c r="G2676" s="1">
-        <v>67.5</v>
+        <v>284.5</v>
       </c>
       <c r="H2676" s="1">
         <v>2</v>
@@ -86316,7 +86316,7 @@
         <v>192</v>
       </c>
       <c r="G2677" s="1">
-        <v>92.5</v>
+        <v>680</v>
       </c>
       <c r="H2677" s="1">
         <v>2</v>
@@ -87340,7 +87340,7 @@
         <v>190</v>
       </c>
       <c r="G2709" s="1">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="H2709" s="1">
         <v>3</v>
@@ -87372,7 +87372,7 @@
         <v>191</v>
       </c>
       <c r="G2710" s="1">
-        <v>192.5</v>
+        <v>750</v>
       </c>
       <c r="H2710" s="1">
         <v>2</v>
@@ -88524,7 +88524,7 @@
         <v>190</v>
       </c>
       <c r="G2746" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H2746" s="1">
         <v>1</v>
@@ -90476,7 +90476,7 @@
         <v>190</v>
       </c>
       <c r="G2807" s="1">
-        <v>52</v>
+        <v>57.5</v>
       </c>
       <c r="H2807" s="1">
         <v>2</v>
@@ -90508,7 +90508,7 @@
         <v>192</v>
       </c>
       <c r="G2808" s="1">
-        <v>65</v>
+        <v>277.5</v>
       </c>
       <c r="H2808" s="1">
         <v>2</v>
@@ -101292,7 +101292,7 @@
         <v>191</v>
       </c>
       <c r="G3145" s="1">
-        <v>59</v>
+        <v>585</v>
       </c>
       <c r="H3145" s="1">
         <v>1</v>
@@ -101324,7 +101324,7 @@
         <v>192</v>
       </c>
       <c r="G3146" s="1">
-        <v>70</v>
+        <v>695</v>
       </c>
       <c r="H3146" s="1">
         <v>1</v>
@@ -105580,7 +105580,7 @@
         <v>190</v>
       </c>
       <c r="G3279" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H3279" s="1">
         <v>1</v>
@@ -105612,7 +105612,7 @@
         <v>191</v>
       </c>
       <c r="G3280" s="1">
-        <v>85</v>
+        <v>850</v>
       </c>
       <c r="H3280" s="1">
         <v>1</v>
@@ -105644,7 +105644,7 @@
         <v>191</v>
       </c>
       <c r="G3281" s="1">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="H3281" s="1">
         <v>1</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -104933,10 +104933,10 @@
         <v>191</v>
       </c>
       <c r="G2543" s="1">
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="H2543" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2543" t="s">
         <v>200</v>
@@ -105056,10 +105056,10 @@
         <v>191</v>
       </c>
       <c r="G2546" s="1">
-        <v>137.5</v>
+        <v>150</v>
       </c>
       <c r="H2546" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2546" t="s">
         <v>200</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -104933,10 +104933,10 @@
         <v>191</v>
       </c>
       <c r="G2543" s="1">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="H2543" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2543" t="s">
         <v>200</v>
@@ -105056,10 +105056,10 @@
         <v>191</v>
       </c>
       <c r="G2546" s="1">
-        <v>150</v>
+        <v>137.5</v>
       </c>
       <c r="H2546" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I2546" t="s">
         <v>200</v>

--- a/outputs/master_rename_build/tables/nsu_reference_set.xlsx
+++ b/outputs/master_rename_build/tables/nsu_reference_set.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23026" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23044" uniqueCount="210">
   <si>
     <t>item</t>
   </si>
@@ -688,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2558"/>
+  <dimension ref="A1:M2560"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104930,13 +104930,13 @@
         <v>187</v>
       </c>
       <c r="F2543" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G2543" s="1">
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="H2543" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2543" t="s">
         <v>200</v>
@@ -104956,7 +104956,7 @@
     </row>
     <row r="2544">
       <c r="A2544" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B2544" t="s">
         <v>25</v>
@@ -104965,16 +104965,16 @@
         <v>128</v>
       </c>
       <c r="D2544" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E2544" t="s">
         <v>187</v>
       </c>
       <c r="F2544" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G2544" s="1">
-        <v>95</v>
+        <v>780</v>
       </c>
       <c r="H2544" s="1">
         <v>3</v>
@@ -104997,7 +104997,7 @@
     </row>
     <row r="2545">
       <c r="A2545" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B2545" t="s">
         <v>25</v>
@@ -105006,25 +105006,25 @@
         <v>128</v>
       </c>
       <c r="D2545" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E2545" t="s">
         <v>187</v>
       </c>
       <c r="F2545" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G2545" s="1">
-        <v>535</v>
+        <v>95</v>
       </c>
       <c r="H2545" s="1">
         <v>3</v>
       </c>
       <c r="I2545" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J2545" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K2545" s="1">
         <v>0</v>
@@ -105038,7 +105038,7 @@
     </row>
     <row r="2546">
       <c r="A2546" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2546" t="s">
         <v>25</v>
@@ -105047,25 +105047,25 @@
         <v>128</v>
       </c>
       <c r="D2546" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2546" t="s">
         <v>187</v>
       </c>
       <c r="F2546" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G2546" s="1">
-        <v>137.5</v>
+        <v>535</v>
       </c>
       <c r="H2546" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2546" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J2546" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K2546" s="1">
         <v>0</v>
@@ -105079,7 +105079,7 @@
     </row>
     <row r="2547">
       <c r="A2547" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2547" t="s">
         <v>25</v>
@@ -105094,25 +105094,25 @@
         <v>187</v>
       </c>
       <c r="F2547" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G2547" s="1">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="H2547" s="1">
         <v>3</v>
       </c>
       <c r="I2547" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J2547" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K2547" s="1">
         <v>0</v>
       </c>
       <c r="L2547" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M2547" s="1">
         <v>0</v>
@@ -105120,7 +105120,7 @@
     </row>
     <row r="2548">
       <c r="A2548" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2548" t="s">
         <v>25</v>
@@ -105132,31 +105132,31 @@
         <v>130</v>
       </c>
       <c r="E2548" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F2548" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G2548" s="1">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="H2548" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2548" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J2548" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K2548" s="1">
         <v>0</v>
       </c>
       <c r="L2548" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M2548" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2549">
@@ -105170,19 +105170,19 @@
         <v>128</v>
       </c>
       <c r="D2549" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E2549" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F2549" t="s">
         <v>190</v>
       </c>
       <c r="G2549" s="1">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="H2549" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2549" t="s">
         <v>198</v>
@@ -105197,12 +105197,12 @@
         <v>207</v>
       </c>
       <c r="M2549" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2550">
       <c r="A2550" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2550" t="s">
         <v>25</v>
@@ -105211,7 +105211,7 @@
         <v>128</v>
       </c>
       <c r="D2550" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E2550" t="s">
         <v>188</v>
@@ -105220,16 +105220,16 @@
         <v>190</v>
       </c>
       <c r="G2550" s="1">
-        <v>375</v>
+        <v>32</v>
       </c>
       <c r="H2550" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2550" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J2550" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K2550" s="1">
         <v>0</v>
@@ -105243,7 +105243,7 @@
     </row>
     <row r="2551">
       <c r="A2551" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2551" t="s">
         <v>25</v>
@@ -105252,7 +105252,7 @@
         <v>128</v>
       </c>
       <c r="D2551" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E2551" t="s">
         <v>188</v>
@@ -105261,16 +105261,16 @@
         <v>190</v>
       </c>
       <c r="G2551" s="1">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="H2551" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2551" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J2551" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K2551" s="1">
         <v>0</v>
@@ -105284,7 +105284,7 @@
     </row>
     <row r="2552">
       <c r="A2552" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2552" t="s">
         <v>25</v>
@@ -105293,25 +105293,25 @@
         <v>128</v>
       </c>
       <c r="D2552" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E2552" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F2552" t="s">
         <v>190</v>
       </c>
       <c r="G2552" s="1">
-        <v>650</v>
+        <v>375</v>
       </c>
       <c r="H2552" s="1">
         <v>2</v>
       </c>
       <c r="I2552" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J2552" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K2552" s="1">
         <v>0</v>
@@ -105325,7 +105325,7 @@
     </row>
     <row r="2553">
       <c r="A2553" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2553" t="s">
         <v>25</v>
@@ -105334,34 +105334,34 @@
         <v>128</v>
       </c>
       <c r="D2553" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E2553" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F2553" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2553" s="1">
-        <v>480</v>
+        <v>750</v>
       </c>
       <c r="H2553" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2553" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J2553" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K2553" s="1">
         <v>0</v>
       </c>
       <c r="L2553" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M2553" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2554">
@@ -105375,19 +105375,19 @@
         <v>128</v>
       </c>
       <c r="D2554" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E2554" t="s">
         <v>187</v>
       </c>
       <c r="F2554" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G2554" s="1">
-        <v>220</v>
+        <v>650</v>
       </c>
       <c r="H2554" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2554" t="s">
         <v>198</v>
@@ -105399,15 +105399,15 @@
         <v>0</v>
       </c>
       <c r="L2554" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M2554" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2555">
       <c r="A2555" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2555" t="s">
         <v>25</v>
@@ -105416,7 +105416,7 @@
         <v>128</v>
       </c>
       <c r="D2555" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E2555" t="s">
         <v>187</v>
@@ -105425,16 +105425,16 @@
         <v>191</v>
       </c>
       <c r="G2555" s="1">
-        <v>205</v>
+        <v>480</v>
       </c>
       <c r="H2555" s="1">
         <v>3</v>
       </c>
       <c r="I2555" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J2555" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K2555" s="1">
         <v>0</v>
@@ -105448,7 +105448,7 @@
     </row>
     <row r="2556">
       <c r="A2556" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2556" t="s">
         <v>25</v>
@@ -105457,25 +105457,25 @@
         <v>128</v>
       </c>
       <c r="D2556" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2556" t="s">
         <v>187</v>
       </c>
       <c r="F2556" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G2556" s="1">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="H2556" s="1">
         <v>3</v>
       </c>
       <c r="I2556" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J2556" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K2556" s="1">
         <v>0</v>
@@ -105489,7 +105489,7 @@
     </row>
     <row r="2557">
       <c r="A2557" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2557" t="s">
         <v>25</v>
@@ -105498,19 +105498,19 @@
         <v>128</v>
       </c>
       <c r="D2557" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E2557" t="s">
         <v>187</v>
       </c>
       <c r="F2557" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G2557" s="1">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="H2557" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2557" t="s">
         <v>200</v>
@@ -105522,15 +105522,15 @@
         <v>0</v>
       </c>
       <c r="L2557" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M2557" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2558">
       <c r="A2558" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2558" t="s">
         <v>25</v>
@@ -105539,19 +105539,19 @@
         <v>128</v>
       </c>
       <c r="D2558" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E2558" t="s">
         <v>187</v>
       </c>
       <c r="F2558" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G2558" s="1">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="H2558" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2558" t="s">
         <v>200</v>
@@ -105563,9 +105563,91 @@
         <v>0</v>
       </c>
       <c r="L2558" t="s">
+        <v>208</v>
+      </c>
+      <c r="M2558" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2559" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2559" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2559" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2559" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2559" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2559" s="1">
+        <v>160</v>
+      </c>
+      <c r="H2559" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2559" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2559" t="s">
+        <v>203</v>
+      </c>
+      <c r="K2559" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2559" t="s">
         <v>207</v>
       </c>
-      <c r="M2558" s="1">
+      <c r="M2559" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2560" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2560" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2560" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2560" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2560" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2560" s="1">
+        <v>285</v>
+      </c>
+      <c r="H2560" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2560" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2560" t="s">
+        <v>203</v>
+      </c>
+      <c r="K2560" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2560" t="s">
+        <v>207</v>
+      </c>
+      <c r="M2560" s="1">
         <v>1</v>
       </c>
     </row>
